--- a/research/traditional_assets/database/data/israel/israel_software_entertainment.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_software_entertainment.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="tase_tgtr" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,22 +590,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.6636363636363636</v>
+        <v>-0.2712127943136384</v>
       </c>
       <c r="H2">
-        <v>-0.6636363636363636</v>
+        <v>-0.2712127943136384</v>
       </c>
       <c r="I2">
-        <v>-2.050454545454545</v>
+        <v>0.04198134162594402</v>
       </c>
       <c r="J2">
-        <v>-2.050454545454545</v>
+        <v>0.04198134162594402</v>
       </c>
       <c r="K2">
-        <v>-8.220000000000001</v>
+        <v>-4.87</v>
       </c>
       <c r="L2">
-        <v>-1.868181818181818</v>
+        <v>-0.2704353620613061</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +629,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.08</v>
+        <v>1.485</v>
       </c>
       <c r="V2">
-        <v>0.5014807502467917</v>
+        <v>0.1234413965087282</v>
       </c>
       <c r="W2">
-        <v>-0.6152844361703029</v>
+        <v>-0.652562676478138</v>
       </c>
       <c r="X2">
-        <v>0.2571680666265502</v>
+        <v>0.1593831752512146</v>
       </c>
       <c r="Y2">
-        <v>-0.872452502796853</v>
+        <v>-0.8119458517293526</v>
       </c>
       <c r="Z2">
-        <v>0.2078511030280127</v>
+        <v>1.475581776466732</v>
       </c>
       <c r="AA2">
-        <v>-0.4498194415046609</v>
+        <v>-0.1662351003441471</v>
       </c>
       <c r="AB2">
-        <v>0.138154323754149</v>
+        <v>0.1122867707091848</v>
       </c>
       <c r="AC2">
-        <v>-0.58797376525881</v>
+        <v>-0.2785218710533319</v>
       </c>
       <c r="AD2">
-        <v>14.974</v>
+        <v>15.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>14.974</v>
+        <v>15.4</v>
       </c>
       <c r="AG2">
-        <v>9.894</v>
+        <v>13.915</v>
       </c>
       <c r="AH2">
-        <v>0.5964786488209051</v>
+        <v>0.5614290922347794</v>
       </c>
       <c r="AI2">
-        <v>0.6601128548756834</v>
+        <v>0.8301886792452831</v>
       </c>
       <c r="AJ2">
-        <v>0.494107071514183</v>
+        <v>0.5363268452495664</v>
       </c>
       <c r="AK2">
-        <v>0.5620313565098841</v>
+        <v>0.8154116612950484</v>
       </c>
       <c r="AL2">
-        <v>3.46</v>
+        <v>5.33</v>
       </c>
       <c r="AM2">
-        <v>-0.03100000000000014</v>
+        <v>5.195</v>
       </c>
       <c r="AN2">
-        <v>-2.030372881355932</v>
+        <v>5.780780780780781</v>
       </c>
       <c r="AO2">
-        <v>-2.607514450867052</v>
+        <v>0.1418386491557223</v>
       </c>
       <c r="AP2">
-        <v>-1.341559322033898</v>
+        <v>5.223348348348348</v>
       </c>
       <c r="AQ2">
-        <v>291.0322580645148</v>
+        <v>0.1455245428296439</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +715,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.4</v>
+        <v>-0.2272222222222222</v>
       </c>
       <c r="H3">
-        <v>-0.4</v>
+        <v>-0.2272222222222222</v>
       </c>
       <c r="I3">
-        <v>-1.829545454545455</v>
+        <v>0.07777777777777778</v>
       </c>
       <c r="J3">
-        <v>-1.829545454545455</v>
+        <v>0.07777777777777778</v>
       </c>
       <c r="K3">
-        <v>-6.61</v>
+        <v>-3.87</v>
       </c>
       <c r="L3">
-        <v>-1.502272727272727</v>
+        <v>-0.215</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +754,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.5</v>
+        <v>0.877</v>
       </c>
       <c r="V3">
-        <v>0.6603773584905661</v>
+        <v>0.08598039215686275</v>
       </c>
       <c r="W3">
-        <v>-0.8944519621109608</v>
+        <v>-0.9602977667493796</v>
       </c>
       <c r="X3">
-        <v>0.3697329813933714</v>
+        <v>0.203709397959656</v>
       </c>
       <c r="Y3">
-        <v>-1.264184943504332</v>
+        <v>-1.164007164709036</v>
       </c>
       <c r="Z3">
-        <v>0.2298850574712644</v>
+        <v>1.665124884366328</v>
       </c>
       <c r="AA3">
-        <v>-0.4205851619644723</v>
+        <v>0.1295097132284921</v>
       </c>
       <c r="AB3">
-        <v>0.1331482127581754</v>
+        <v>0.1095165888755965</v>
       </c>
       <c r="AC3">
-        <v>-0.5537333747226477</v>
+        <v>0.01999312435289563</v>
       </c>
       <c r="AD3">
-        <v>14.9</v>
+        <v>15.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>14.9</v>
+        <v>15.4</v>
       </c>
       <c r="AG3">
-        <v>11.4</v>
+        <v>14.523</v>
       </c>
       <c r="AH3">
-        <v>0.7376237623762376</v>
+        <v>0.6015625</v>
       </c>
       <c r="AI3">
-        <v>0.7559614408929477</v>
+        <v>0.9172126265634307</v>
       </c>
       <c r="AJ3">
-        <v>0.6826347305389222</v>
+        <v>0.5874287101079966</v>
       </c>
       <c r="AK3">
-        <v>0.703269586674892</v>
+        <v>0.9126500345629359</v>
       </c>
       <c r="AL3">
-        <v>3.46</v>
+        <v>5.33</v>
       </c>
       <c r="AM3">
-        <v>-0.02000000000000002</v>
+        <v>5.33</v>
       </c>
       <c r="AN3">
-        <v>-2.320872274143302</v>
+        <v>4.652567975830816</v>
       </c>
       <c r="AO3">
-        <v>-2.326589595375723</v>
+        <v>0.2626641651031895</v>
       </c>
       <c r="AP3">
-        <v>-1.775700934579439</v>
+        <v>4.387613293051359</v>
       </c>
       <c r="AQ3">
-        <v>402.4999999999997</v>
+        <v>0.2626641651031895</v>
       </c>
     </row>
     <row r="4">
@@ -837,8 +839,23 @@
           <t>Software (Entertainment)</t>
         </is>
       </c>
+      <c r="G4">
+        <v>-99.25</v>
+      </c>
+      <c r="H4">
+        <v>-99.25</v>
+      </c>
+      <c r="I4">
+        <v>-80.5</v>
+      </c>
+      <c r="J4">
+        <v>-80.5</v>
+      </c>
       <c r="K4">
-        <v>-1.61</v>
+        <v>-1</v>
+      </c>
+      <c r="L4">
+        <v>-125</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -862,70 +879,8842 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.58</v>
+        <v>0.608</v>
       </c>
       <c r="V4">
-        <v>0.3271221532091098</v>
+        <v>0.3322404371584699</v>
       </c>
       <c r="W4">
-        <v>-0.3361169102296451</v>
+        <v>-0.3448275862068966</v>
       </c>
       <c r="X4">
-        <v>0.144603151859729</v>
+        <v>0.1150569525427732</v>
       </c>
       <c r="Y4">
-        <v>-0.4807200620893741</v>
+        <v>-0.4598845387496697</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>0.005738880918220948</v>
       </c>
       <c r="AA4">
-        <v>-0.4790537210448496</v>
+        <v>-0.4619799139167863</v>
       </c>
       <c r="AB4">
-        <v>0.1431604347501226</v>
+        <v>0.1150569525427732</v>
       </c>
       <c r="AC4">
-        <v>-0.6222141557949721</v>
+        <v>-0.5770368664595595</v>
       </c>
       <c r="AD4">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-1.506</v>
+        <v>-0.608</v>
       </c>
       <c r="AH4">
-        <v>0.01508972267536705</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.02488231338264963</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.4530685920577617</v>
+        <v>-0.497545008183306</v>
       </c>
       <c r="AK4">
-        <v>-1.080344332855093</v>
+        <v>-0.5277777777777777</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.011</v>
+        <v>-0.135</v>
       </c>
       <c r="AN4">
-        <v>-0.0774869109947644</v>
+        <v>-0</v>
       </c>
       <c r="AP4">
-        <v>1.57696335078534</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="AQ4">
-        <v>88.36363636363636</v>
+        <v>4.770370370370371</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Together Pharma Ltd (TASE:TGTR)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TASE:TGTR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Software (Entertainment)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.262664165103189</v>
+      </c>
+      <c r="F2">
+        <v>4.51828032907662</v>
+      </c>
+      <c r="G2">
+        <v>4.65256797583082</v>
+      </c>
+      <c r="H2">
+        <v>6.18731117824774</v>
+      </c>
+      <c r="I2">
+        <v>0.6015625</v>
+      </c>
+      <c r="J2">
+        <v>0.8</v>
+      </c>
+      <c r="K2">
+        <v>10.2</v>
+      </c>
+      <c r="L2">
+        <v>8.35229546449969</v>
+      </c>
+      <c r="M2">
+        <v>24.723</v>
+      </c>
+      <c r="N2">
+        <v>27.9552954644997</v>
+      </c>
+      <c r="O2">
+        <v>15.4</v>
+      </c>
+      <c r="P2">
+        <v>20.48</v>
+      </c>
+      <c r="Q2">
+        <v>0.109516588875597</v>
+      </c>
+      <c r="R2">
+        <v>0.101340073274903</v>
+      </c>
+      <c r="S2">
+        <v>0.0471291438978428</v>
+      </c>
+      <c r="T2">
+        <v>0.039193</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.203709397959656</v>
+      </c>
+      <c r="X2">
+        <v>0.349928366374515</v>
+      </c>
+      <c r="Y2">
+        <v>2.92841499035988</v>
+      </c>
+      <c r="Z2">
+        <v>5.52493055756717</v>
+      </c>
+      <c r="AA2">
+        <v>15.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.06120668038680883</v>
+      </c>
+      <c r="AC2">
+        <v>0.2626641651031895</v>
+      </c>
+      <c r="AD2">
+        <v>15.4</v>
+      </c>
+      <c r="AE2">
+        <v>5.33</v>
+      </c>
+      <c r="AF2">
+        <v>1.91</v>
+      </c>
+      <c r="AG2">
+        <v>3.31</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>10.2</v>
+      </c>
+      <c r="AK2">
+        <v>0.05631353428476683</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.23</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>1.983</v>
+      </c>
+      <c r="AR2">
+        <v>5.33</v>
+      </c>
+      <c r="AS2">
+        <v>15.4</v>
+      </c>
+      <c r="AT2">
+        <v>0.877</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1150569525427732</v>
+      </c>
+      <c r="C2">
+        <v>23.80377806381944</v>
+      </c>
+      <c r="D2">
+        <v>22.92677806381944</v>
+      </c>
+      <c r="E2">
+        <v>-15.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.877</v>
+      </c>
+      <c r="H2">
+        <v>10.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>6.62</v>
+      </c>
+      <c r="K2">
+        <v>1.91</v>
+      </c>
+      <c r="L2">
+        <v>4.71</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>4.71</v>
+      </c>
+      <c r="O2">
+        <v>1.0833</v>
+      </c>
+      <c r="P2">
+        <v>3.6267</v>
+      </c>
+      <c r="Q2">
+        <v>5.5367</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1150569525427732</v>
+      </c>
+      <c r="T2">
+        <v>1.354149646462541</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.23</v>
+      </c>
+      <c r="W2">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1148377515519248</v>
+      </c>
+      <c r="C3">
+        <v>23.61387118685343</v>
+      </c>
+      <c r="D3">
+        <v>22.99287118685344</v>
+      </c>
+      <c r="E3">
+        <v>-15.144</v>
+      </c>
+      <c r="F3">
+        <v>0.256</v>
+      </c>
+      <c r="G3">
+        <v>0.877</v>
+      </c>
+      <c r="H3">
+        <v>10.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>6.62</v>
+      </c>
+      <c r="K3">
+        <v>1.91</v>
+      </c>
+      <c r="L3">
+        <v>4.71</v>
+      </c>
+      <c r="M3">
+        <v>0.0114432</v>
+      </c>
+      <c r="N3">
+        <v>4.6985568</v>
+      </c>
+      <c r="O3">
+        <v>1.080668064</v>
+      </c>
+      <c r="P3">
+        <v>3.617888735999999</v>
+      </c>
+      <c r="Q3">
+        <v>5.527888736</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1156500621736615</v>
+      </c>
+      <c r="T3">
+        <v>1.364681921490583</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.23</v>
+      </c>
+      <c r="W3">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>411.598154362416</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1146185505610764</v>
+      </c>
+      <c r="C4">
+        <v>23.4243464769943</v>
+      </c>
+      <c r="D4">
+        <v>23.0593464769943</v>
+      </c>
+      <c r="E4">
+        <v>-14.888</v>
+      </c>
+      <c r="F4">
+        <v>0.512</v>
+      </c>
+      <c r="G4">
+        <v>0.877</v>
+      </c>
+      <c r="H4">
+        <v>10.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>6.62</v>
+      </c>
+      <c r="K4">
+        <v>1.91</v>
+      </c>
+      <c r="L4">
+        <v>4.71</v>
+      </c>
+      <c r="M4">
+        <v>0.0228864</v>
+      </c>
+      <c r="N4">
+        <v>4.6871136</v>
+      </c>
+      <c r="O4">
+        <v>1.078036128</v>
+      </c>
+      <c r="P4">
+        <v>3.609077472</v>
+      </c>
+      <c r="Q4">
+        <v>5.519077472</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1162552760827311</v>
+      </c>
+      <c r="T4">
+        <v>1.375429140906953</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.23</v>
+      </c>
+      <c r="W4">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>205.799077181208</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1143993495702281</v>
+      </c>
+      <c r="C5">
+        <v>23.23520725853287</v>
+      </c>
+      <c r="D5">
+        <v>23.12620725853288</v>
+      </c>
+      <c r="E5">
+        <v>-14.632</v>
+      </c>
+      <c r="F5">
+        <v>0.768</v>
+      </c>
+      <c r="G5">
+        <v>0.877</v>
+      </c>
+      <c r="H5">
+        <v>10.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>6.62</v>
+      </c>
+      <c r="K5">
+        <v>1.91</v>
+      </c>
+      <c r="L5">
+        <v>4.71</v>
+      </c>
+      <c r="M5">
+        <v>0.0343296</v>
+      </c>
+      <c r="N5">
+        <v>4.6756704</v>
+      </c>
+      <c r="O5">
+        <v>1.075404192</v>
+      </c>
+      <c r="P5">
+        <v>3.600266208</v>
+      </c>
+      <c r="Q5">
+        <v>5.510266208</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1168729686291011</v>
+      </c>
+      <c r="T5">
+        <v>1.386397952476237</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.23</v>
+      </c>
+      <c r="W5">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>137.199384787472</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1141801485793797</v>
+      </c>
+      <c r="C6">
+        <v>23.04645689442736</v>
+      </c>
+      <c r="D6">
+        <v>23.19345689442736</v>
+      </c>
+      <c r="E6">
+        <v>-14.376</v>
+      </c>
+      <c r="F6">
+        <v>1.024</v>
+      </c>
+      <c r="G6">
+        <v>0.877</v>
+      </c>
+      <c r="H6">
+        <v>10.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>6.62</v>
+      </c>
+      <c r="K6">
+        <v>1.91</v>
+      </c>
+      <c r="L6">
+        <v>4.71</v>
+      </c>
+      <c r="M6">
+        <v>0.0457728</v>
+      </c>
+      <c r="N6">
+        <v>4.6642272</v>
+      </c>
+      <c r="O6">
+        <v>1.072772256</v>
+      </c>
+      <c r="P6">
+        <v>3.591454944</v>
+      </c>
+      <c r="Q6">
+        <v>5.501454944</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1175035297701872</v>
+      </c>
+      <c r="T6">
+        <v>1.397595280953214</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.23</v>
+      </c>
+      <c r="W6">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>102.899538590604</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1139609475885313</v>
+      </c>
+      <c r="C7">
+        <v>22.85809878686717</v>
+      </c>
+      <c r="D7">
+        <v>23.26109878686717</v>
+      </c>
+      <c r="E7">
+        <v>-14.12</v>
+      </c>
+      <c r="F7">
+        <v>1.28</v>
+      </c>
+      <c r="G7">
+        <v>0.877</v>
+      </c>
+      <c r="H7">
+        <v>10.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>6.62</v>
+      </c>
+      <c r="K7">
+        <v>1.91</v>
+      </c>
+      <c r="L7">
+        <v>4.71</v>
+      </c>
+      <c r="M7">
+        <v>0.05721600000000002</v>
+      </c>
+      <c r="N7">
+        <v>4.652784</v>
+      </c>
+      <c r="O7">
+        <v>1.07014032</v>
+      </c>
+      <c r="P7">
+        <v>3.582643679999999</v>
+      </c>
+      <c r="Q7">
+        <v>5.49264368</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1181473658826645</v>
+      </c>
+      <c r="T7">
+        <v>1.409028342661286</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.23</v>
+      </c>
+      <c r="W7">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>82.31963087248319</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1137417465976829</v>
+      </c>
+      <c r="C8">
+        <v>22.67013637784668</v>
+      </c>
+      <c r="D8">
+        <v>23.32913637784668</v>
+      </c>
+      <c r="E8">
+        <v>-13.864</v>
+      </c>
+      <c r="F8">
+        <v>1.536</v>
+      </c>
+      <c r="G8">
+        <v>0.877</v>
+      </c>
+      <c r="H8">
+        <v>10.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>6.62</v>
+      </c>
+      <c r="K8">
+        <v>1.91</v>
+      </c>
+      <c r="L8">
+        <v>4.71</v>
+      </c>
+      <c r="M8">
+        <v>0.0686592</v>
+      </c>
+      <c r="N8">
+        <v>4.6413408</v>
+      </c>
+      <c r="O8">
+        <v>1.067508384</v>
+      </c>
+      <c r="P8">
+        <v>3.573832416</v>
+      </c>
+      <c r="Q8">
+        <v>5.483832416</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1188049006358329</v>
+      </c>
+      <c r="T8">
+        <v>1.420704661001445</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.23</v>
+      </c>
+      <c r="W8">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>68.59969239373602</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1135225456068345</v>
+      </c>
+      <c r="C9">
+        <v>22.48257314974907</v>
+      </c>
+      <c r="D9">
+        <v>23.39757314974907</v>
+      </c>
+      <c r="E9">
+        <v>-13.608</v>
+      </c>
+      <c r="F9">
+        <v>1.792</v>
+      </c>
+      <c r="G9">
+        <v>0.877</v>
+      </c>
+      <c r="H9">
+        <v>10.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>6.62</v>
+      </c>
+      <c r="K9">
+        <v>1.91</v>
+      </c>
+      <c r="L9">
+        <v>4.71</v>
+      </c>
+      <c r="M9">
+        <v>0.08010240000000002</v>
+      </c>
+      <c r="N9">
+        <v>4.6298976</v>
+      </c>
+      <c r="O9">
+        <v>1.064876448</v>
+      </c>
+      <c r="P9">
+        <v>3.565021152</v>
+      </c>
+      <c r="Q9">
+        <v>5.475021152</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1194765759213275</v>
+      </c>
+      <c r="T9">
+        <v>1.432632082961822</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.23</v>
+      </c>
+      <c r="W9">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>58.799736337488</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1133033446159862</v>
+      </c>
+      <c r="C10">
+        <v>22.29541262594048</v>
+      </c>
+      <c r="D10">
+        <v>23.46641262594048</v>
+      </c>
+      <c r="E10">
+        <v>-13.352</v>
+      </c>
+      <c r="F10">
+        <v>2.048</v>
+      </c>
+      <c r="G10">
+        <v>0.877</v>
+      </c>
+      <c r="H10">
+        <v>10.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>6.62</v>
+      </c>
+      <c r="K10">
+        <v>1.91</v>
+      </c>
+      <c r="L10">
+        <v>4.71</v>
+      </c>
+      <c r="M10">
+        <v>0.0915456</v>
+      </c>
+      <c r="N10">
+        <v>4.6184544</v>
+      </c>
+      <c r="O10">
+        <v>1.062244512</v>
+      </c>
+      <c r="P10">
+        <v>3.556209888</v>
+      </c>
+      <c r="Q10">
+        <v>5.466209888</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1201628528434632</v>
+      </c>
+      <c r="T10">
+        <v>1.444818796703946</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.23</v>
+      </c>
+      <c r="W10">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>51.44976929530201</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1130841436251378</v>
+      </c>
+      <c r="C11">
+        <v>22.10865837137467</v>
+      </c>
+      <c r="D11">
+        <v>23.53565837137467</v>
+      </c>
+      <c r="E11">
+        <v>-13.096</v>
+      </c>
+      <c r="F11">
+        <v>2.304</v>
+      </c>
+      <c r="G11">
+        <v>0.877</v>
+      </c>
+      <c r="H11">
+        <v>10.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>6.62</v>
+      </c>
+      <c r="K11">
+        <v>1.91</v>
+      </c>
+      <c r="L11">
+        <v>4.71</v>
+      </c>
+      <c r="M11">
+        <v>0.1029888</v>
+      </c>
+      <c r="N11">
+        <v>4.6070112</v>
+      </c>
+      <c r="O11">
+        <v>1.059612576</v>
+      </c>
+      <c r="P11">
+        <v>3.547398624</v>
+      </c>
+      <c r="Q11">
+        <v>5.457398624</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1208642127748767</v>
+      </c>
+      <c r="T11">
+        <v>1.457273350308535</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.23</v>
+      </c>
+      <c r="W11">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>45.73312826249067</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1128649426342894</v>
+      </c>
+      <c r="C12">
+        <v>21.92231399320843</v>
+      </c>
+      <c r="D12">
+        <v>23.60531399320844</v>
+      </c>
+      <c r="E12">
+        <v>-12.84</v>
+      </c>
+      <c r="F12">
+        <v>2.56</v>
+      </c>
+      <c r="G12">
+        <v>0.877</v>
+      </c>
+      <c r="H12">
+        <v>10.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>6.62</v>
+      </c>
+      <c r="K12">
+        <v>1.91</v>
+      </c>
+      <c r="L12">
+        <v>4.71</v>
+      </c>
+      <c r="M12">
+        <v>0.114432</v>
+      </c>
+      <c r="N12">
+        <v>4.595568</v>
+      </c>
+      <c r="O12">
+        <v>1.05698064</v>
+      </c>
+      <c r="P12">
+        <v>3.53858736</v>
+      </c>
+      <c r="Q12">
+        <v>5.44858736</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1215811584825438</v>
+      </c>
+      <c r="T12">
+        <v>1.470004671771003</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.23</v>
+      </c>
+      <c r="W12">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>41.1598154362416</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1126457416434411</v>
+      </c>
+      <c r="C13">
+        <v>21.73638314142801</v>
+      </c>
+      <c r="D13">
+        <v>23.67538314142801</v>
+      </c>
+      <c r="E13">
+        <v>-12.584</v>
+      </c>
+      <c r="F13">
+        <v>2.816</v>
+      </c>
+      <c r="G13">
+        <v>0.877</v>
+      </c>
+      <c r="H13">
+        <v>10.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>6.62</v>
+      </c>
+      <c r="K13">
+        <v>1.91</v>
+      </c>
+      <c r="L13">
+        <v>4.71</v>
+      </c>
+      <c r="M13">
+        <v>0.1258752</v>
+      </c>
+      <c r="N13">
+        <v>4.5841248</v>
+      </c>
+      <c r="O13">
+        <v>1.054348704</v>
+      </c>
+      <c r="P13">
+        <v>3.529776096</v>
+      </c>
+      <c r="Q13">
+        <v>5.439776096</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.122314215329709</v>
+      </c>
+      <c r="T13">
+        <v>1.483022090344988</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.23</v>
+      </c>
+      <c r="W13">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>37.41801403294691</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1124265406525927</v>
+      </c>
+      <c r="C14">
+        <v>21.55086950948655</v>
+      </c>
+      <c r="D14">
+        <v>23.74586950948655</v>
+      </c>
+      <c r="E14">
+        <v>-12.328</v>
+      </c>
+      <c r="F14">
+        <v>3.072</v>
+      </c>
+      <c r="G14">
+        <v>0.877</v>
+      </c>
+      <c r="H14">
+        <v>10.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>6.62</v>
+      </c>
+      <c r="K14">
+        <v>1.91</v>
+      </c>
+      <c r="L14">
+        <v>4.71</v>
+      </c>
+      <c r="M14">
+        <v>0.1373184</v>
+      </c>
+      <c r="N14">
+        <v>4.5726816</v>
+      </c>
+      <c r="O14">
+        <v>1.051716768</v>
+      </c>
+      <c r="P14">
+        <v>3.520964832</v>
+      </c>
+      <c r="Q14">
+        <v>5.430964832</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1230639325597644</v>
+      </c>
+      <c r="T14">
+        <v>1.496335359341108</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.23</v>
+      </c>
+      <c r="W14">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>34.29984619686801</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1122073396617443</v>
+      </c>
+      <c r="C15">
+        <v>21.3657768349532</v>
+      </c>
+      <c r="D15">
+        <v>23.8167768349532</v>
+      </c>
+      <c r="E15">
+        <v>-12.072</v>
+      </c>
+      <c r="F15">
+        <v>3.328</v>
+      </c>
+      <c r="G15">
+        <v>0.877</v>
+      </c>
+      <c r="H15">
+        <v>10.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>6.62</v>
+      </c>
+      <c r="K15">
+        <v>1.91</v>
+      </c>
+      <c r="L15">
+        <v>4.71</v>
+      </c>
+      <c r="M15">
+        <v>0.1487616</v>
+      </c>
+      <c r="N15">
+        <v>4.5612384</v>
+      </c>
+      <c r="O15">
+        <v>1.049084832</v>
+      </c>
+      <c r="P15">
+        <v>3.512153568</v>
+      </c>
+      <c r="Q15">
+        <v>5.422153568</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1238308846686716</v>
+      </c>
+      <c r="T15">
+        <v>1.509954680498059</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.23</v>
+      </c>
+      <c r="W15">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>31.66139648941662</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1119881386708959</v>
+      </c>
+      <c r="C16">
+        <v>21.18110890017366</v>
+      </c>
+      <c r="D16">
+        <v>23.88810890017366</v>
+      </c>
+      <c r="E16">
+        <v>-11.816</v>
+      </c>
+      <c r="F16">
+        <v>3.584000000000001</v>
+      </c>
+      <c r="G16">
+        <v>0.877</v>
+      </c>
+      <c r="H16">
+        <v>10.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>6.62</v>
+      </c>
+      <c r="K16">
+        <v>1.91</v>
+      </c>
+      <c r="L16">
+        <v>4.71</v>
+      </c>
+      <c r="M16">
+        <v>0.1602048</v>
+      </c>
+      <c r="N16">
+        <v>4.5497952</v>
+      </c>
+      <c r="O16">
+        <v>1.046452896</v>
+      </c>
+      <c r="P16">
+        <v>3.503342304</v>
+      </c>
+      <c r="Q16">
+        <v>5.413342304</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1246156728731348</v>
+      </c>
+      <c r="T16">
+        <v>1.523890730054009</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.23</v>
+      </c>
+      <c r="W16">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>29.399868168744</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1117689376800475</v>
+      </c>
+      <c r="C17">
+        <v>20.9968695329428</v>
+      </c>
+      <c r="D17">
+        <v>23.9598695329428</v>
+      </c>
+      <c r="E17">
+        <v>-11.56</v>
+      </c>
+      <c r="F17">
+        <v>3.84</v>
+      </c>
+      <c r="G17">
+        <v>0.877</v>
+      </c>
+      <c r="H17">
+        <v>10.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>6.62</v>
+      </c>
+      <c r="K17">
+        <v>1.91</v>
+      </c>
+      <c r="L17">
+        <v>4.71</v>
+      </c>
+      <c r="M17">
+        <v>0.171648</v>
+      </c>
+      <c r="N17">
+        <v>4.538352</v>
+      </c>
+      <c r="O17">
+        <v>1.04382096</v>
+      </c>
+      <c r="P17">
+        <v>3.49453104</v>
+      </c>
+      <c r="Q17">
+        <v>5.40453104</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1254189266824089</v>
+      </c>
+      <c r="T17">
+        <v>1.538154686658334</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.23</v>
+      </c>
+      <c r="W17">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>27.43987695749441</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1115497366891992</v>
+      </c>
+      <c r="C18">
+        <v>20.81306260718933</v>
+      </c>
+      <c r="D18">
+        <v>24.03206260718933</v>
+      </c>
+      <c r="E18">
+        <v>-11.304</v>
+      </c>
+      <c r="F18">
+        <v>4.096</v>
+      </c>
+      <c r="G18">
+        <v>0.877</v>
+      </c>
+      <c r="H18">
+        <v>10.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>6.62</v>
+      </c>
+      <c r="K18">
+        <v>1.91</v>
+      </c>
+      <c r="L18">
+        <v>4.71</v>
+      </c>
+      <c r="M18">
+        <v>0.1830912</v>
+      </c>
+      <c r="N18">
+        <v>4.5269088</v>
+      </c>
+      <c r="O18">
+        <v>1.041189024</v>
+      </c>
+      <c r="P18">
+        <v>3.485719776</v>
+      </c>
+      <c r="Q18">
+        <v>5.395719776</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1262413055823799</v>
+      </c>
+      <c r="T18">
+        <v>1.552758261277047</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.23</v>
+      </c>
+      <c r="W18">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>25.72488464765101</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1113305356983508</v>
+      </c>
+      <c r="C19">
+        <v>20.62969204367295</v>
+      </c>
+      <c r="D19">
+        <v>24.10469204367295</v>
+      </c>
+      <c r="E19">
+        <v>-11.048</v>
+      </c>
+      <c r="F19">
+        <v>4.352</v>
+      </c>
+      <c r="G19">
+        <v>0.877</v>
+      </c>
+      <c r="H19">
+        <v>10.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>6.62</v>
+      </c>
+      <c r="K19">
+        <v>1.91</v>
+      </c>
+      <c r="L19">
+        <v>4.71</v>
+      </c>
+      <c r="M19">
+        <v>0.1945344</v>
+      </c>
+      <c r="N19">
+        <v>4.5154656</v>
+      </c>
+      <c r="O19">
+        <v>1.038557088</v>
+      </c>
+      <c r="P19">
+        <v>3.476908512</v>
+      </c>
+      <c r="Q19">
+        <v>5.386908512</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1270835008413865</v>
+      </c>
+      <c r="T19">
+        <v>1.567713729260067</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.23</v>
+      </c>
+      <c r="W19">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>24.21165613896565</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1111113347075024</v>
+      </c>
+      <c r="C20">
+        <v>20.44676181069413</v>
+      </c>
+      <c r="D20">
+        <v>24.17776181069413</v>
+      </c>
+      <c r="E20">
+        <v>-10.792</v>
+      </c>
+      <c r="F20">
+        <v>4.608</v>
+      </c>
+      <c r="G20">
+        <v>0.877</v>
+      </c>
+      <c r="H20">
+        <v>10.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>6.62</v>
+      </c>
+      <c r="K20">
+        <v>1.91</v>
+      </c>
+      <c r="L20">
+        <v>4.71</v>
+      </c>
+      <c r="M20">
+        <v>0.2059776</v>
+      </c>
+      <c r="N20">
+        <v>4.5040224</v>
+      </c>
+      <c r="O20">
+        <v>1.035925152</v>
+      </c>
+      <c r="P20">
+        <v>3.468097248</v>
+      </c>
+      <c r="Q20">
+        <v>5.378097248</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1279462374481737</v>
+      </c>
+      <c r="T20">
+        <v>1.583033964754868</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.23</v>
+      </c>
+      <c r="W20">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>22.86656413124534</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.110892133716654</v>
+      </c>
+      <c r="C21">
+        <v>20.2642759248169</v>
+      </c>
+      <c r="D21">
+        <v>24.2512759248169</v>
+      </c>
+      <c r="E21">
+        <v>-10.536</v>
+      </c>
+      <c r="F21">
+        <v>4.864000000000001</v>
+      </c>
+      <c r="G21">
+        <v>0.877</v>
+      </c>
+      <c r="H21">
+        <v>10.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>6.62</v>
+      </c>
+      <c r="K21">
+        <v>1.91</v>
+      </c>
+      <c r="L21">
+        <v>4.71</v>
+      </c>
+      <c r="M21">
+        <v>0.2174208000000001</v>
+      </c>
+      <c r="N21">
+        <v>4.4925792</v>
+      </c>
+      <c r="O21">
+        <v>1.033293216</v>
+      </c>
+      <c r="P21">
+        <v>3.459285984</v>
+      </c>
+      <c r="Q21">
+        <v>5.369285984</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1288302761934</v>
+      </c>
+      <c r="T21">
+        <v>1.598732477669294</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.23</v>
+      </c>
+      <c r="W21">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>21.66306075591663</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1106729327258056</v>
+      </c>
+      <c r="C22">
+        <v>20.0822384516048</v>
+      </c>
+      <c r="D22">
+        <v>24.3252384516048</v>
+      </c>
+      <c r="E22">
+        <v>-10.28</v>
+      </c>
+      <c r="F22">
+        <v>5.120000000000001</v>
+      </c>
+      <c r="G22">
+        <v>0.877</v>
+      </c>
+      <c r="H22">
+        <v>10.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>6.62</v>
+      </c>
+      <c r="K22">
+        <v>1.91</v>
+      </c>
+      <c r="L22">
+        <v>4.71</v>
+      </c>
+      <c r="M22">
+        <v>0.2288640000000001</v>
+      </c>
+      <c r="N22">
+        <v>4.481136</v>
+      </c>
+      <c r="O22">
+        <v>1.03066128</v>
+      </c>
+      <c r="P22">
+        <v>3.45047472</v>
+      </c>
+      <c r="Q22">
+        <v>5.36047472</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.129736415907257</v>
+      </c>
+      <c r="T22">
+        <v>1.61482345340658</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.23</v>
+      </c>
+      <c r="W22">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>20.5799077181208</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1104537317349573</v>
+      </c>
+      <c r="C23">
+        <v>19.90065350637038</v>
+      </c>
+      <c r="D23">
+        <v>24.39965350637038</v>
+      </c>
+      <c r="E23">
+        <v>-10.024</v>
+      </c>
+      <c r="F23">
+        <v>5.376</v>
+      </c>
+      <c r="G23">
+        <v>0.877</v>
+      </c>
+      <c r="H23">
+        <v>10.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>6.62</v>
+      </c>
+      <c r="K23">
+        <v>1.91</v>
+      </c>
+      <c r="L23">
+        <v>4.71</v>
+      </c>
+      <c r="M23">
+        <v>0.2403072</v>
+      </c>
+      <c r="N23">
+        <v>4.4696928</v>
+      </c>
+      <c r="O23">
+        <v>1.028029344</v>
+      </c>
+      <c r="P23">
+        <v>3.441663456</v>
+      </c>
+      <c r="Q23">
+        <v>5.351663456</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1306654958670345</v>
+      </c>
+      <c r="T23">
+        <v>1.631321795618229</v>
+      </c>
+      <c r="U23">
+        <v>0.0447</v>
+      </c>
+      <c r="V23">
+        <v>0.23</v>
+      </c>
+      <c r="W23">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>19.599912112496</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1102345307441089</v>
+      </c>
+      <c r="C24">
+        <v>19.71952525493848</v>
+      </c>
+      <c r="D24">
+        <v>24.47452525493848</v>
+      </c>
+      <c r="E24">
+        <v>-9.768000000000001</v>
+      </c>
+      <c r="F24">
+        <v>5.632000000000001</v>
+      </c>
+      <c r="G24">
+        <v>0.877</v>
+      </c>
+      <c r="H24">
+        <v>10.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>6.62</v>
+      </c>
+      <c r="K24">
+        <v>1.91</v>
+      </c>
+      <c r="L24">
+        <v>4.71</v>
+      </c>
+      <c r="M24">
+        <v>0.2517504</v>
+      </c>
+      <c r="N24">
+        <v>4.4582496</v>
+      </c>
+      <c r="O24">
+        <v>1.025397408</v>
+      </c>
+      <c r="P24">
+        <v>3.432852192</v>
+      </c>
+      <c r="Q24">
+        <v>5.342852192</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1316183983898832</v>
+      </c>
+      <c r="T24">
+        <v>1.64824317224556</v>
+      </c>
+      <c r="U24">
+        <v>0.0447</v>
+      </c>
+      <c r="V24">
+        <v>0.23</v>
+      </c>
+      <c r="W24">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>18.70900701647346</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1100153297532605</v>
+      </c>
+      <c r="C25">
+        <v>19.53885791442364</v>
+      </c>
+      <c r="D25">
+        <v>24.54985791442364</v>
+      </c>
+      <c r="E25">
+        <v>-9.512</v>
+      </c>
+      <c r="F25">
+        <v>5.888000000000001</v>
+      </c>
+      <c r="G25">
+        <v>0.877</v>
+      </c>
+      <c r="H25">
+        <v>10.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>6.62</v>
+      </c>
+      <c r="K25">
+        <v>1.91</v>
+      </c>
+      <c r="L25">
+        <v>4.71</v>
+      </c>
+      <c r="M25">
+        <v>0.2631936000000001</v>
+      </c>
+      <c r="N25">
+        <v>4.4468064</v>
+      </c>
+      <c r="O25">
+        <v>1.022765472</v>
+      </c>
+      <c r="P25">
+        <v>3.424040928</v>
+      </c>
+      <c r="Q25">
+        <v>5.334040928</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1325960516276111</v>
+      </c>
+      <c r="T25">
+        <v>1.665604065148926</v>
+      </c>
+      <c r="U25">
+        <v>0.0447</v>
+      </c>
+      <c r="V25">
+        <v>0.23</v>
+      </c>
+      <c r="W25">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>17.8955719288007</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1097961287624121</v>
+      </c>
+      <c r="C26">
+        <v>19.35865575402189</v>
+      </c>
+      <c r="D26">
+        <v>24.62565575402189</v>
+      </c>
+      <c r="E26">
+        <v>-9.256</v>
+      </c>
+      <c r="F26">
+        <v>6.144</v>
+      </c>
+      <c r="G26">
+        <v>0.877</v>
+      </c>
+      <c r="H26">
+        <v>10.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>6.62</v>
+      </c>
+      <c r="K26">
+        <v>1.91</v>
+      </c>
+      <c r="L26">
+        <v>4.71</v>
+      </c>
+      <c r="M26">
+        <v>0.2746368</v>
+      </c>
+      <c r="N26">
+        <v>4.4353632</v>
+      </c>
+      <c r="O26">
+        <v>1.020133536</v>
+      </c>
+      <c r="P26">
+        <v>3.415229664</v>
+      </c>
+      <c r="Q26">
+        <v>5.325229664</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1335994325821212</v>
+      </c>
+      <c r="T26">
+        <v>1.683421823655012</v>
+      </c>
+      <c r="U26">
+        <v>0.0447</v>
+      </c>
+      <c r="V26">
+        <v>0.23</v>
+      </c>
+      <c r="W26">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>17.14992309843401</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1095769277715637</v>
+      </c>
+      <c r="C27">
+        <v>19.17892309581715</v>
+      </c>
+      <c r="D27">
+        <v>24.70192309581715</v>
+      </c>
+      <c r="E27">
+        <v>-9</v>
+      </c>
+      <c r="F27">
+        <v>6.4</v>
+      </c>
+      <c r="G27">
+        <v>0.877</v>
+      </c>
+      <c r="H27">
+        <v>10.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>6.62</v>
+      </c>
+      <c r="K27">
+        <v>1.91</v>
+      </c>
+      <c r="L27">
+        <v>4.71</v>
+      </c>
+      <c r="M27">
+        <v>0.2860800000000001</v>
+      </c>
+      <c r="N27">
+        <v>4.42392</v>
+      </c>
+      <c r="O27">
+        <v>1.0175016</v>
+      </c>
+      <c r="P27">
+        <v>3.4064184</v>
+      </c>
+      <c r="Q27">
+        <v>5.3164184</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.134629570362085</v>
+      </c>
+      <c r="T27">
+        <v>1.701714722387927</v>
+      </c>
+      <c r="U27">
+        <v>0.0447</v>
+      </c>
+      <c r="V27">
+        <v>0.23</v>
+      </c>
+      <c r="W27">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>16.46392617449664</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1093577267807154</v>
+      </c>
+      <c r="C28">
+        <v>18.99966431560292</v>
+      </c>
+      <c r="D28">
+        <v>24.77866431560292</v>
+      </c>
+      <c r="E28">
+        <v>-8.744</v>
+      </c>
+      <c r="F28">
+        <v>6.656000000000001</v>
+      </c>
+      <c r="G28">
+        <v>0.877</v>
+      </c>
+      <c r="H28">
+        <v>10.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>6.62</v>
+      </c>
+      <c r="K28">
+        <v>1.91</v>
+      </c>
+      <c r="L28">
+        <v>4.71</v>
+      </c>
+      <c r="M28">
+        <v>0.2975232</v>
+      </c>
+      <c r="N28">
+        <v>4.4124768</v>
+      </c>
+      <c r="O28">
+        <v>1.014869664</v>
+      </c>
+      <c r="P28">
+        <v>3.397607136</v>
+      </c>
+      <c r="Q28">
+        <v>5.307607136000001</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1356875497036694</v>
+      </c>
+      <c r="T28">
+        <v>1.720502023789299</v>
+      </c>
+      <c r="U28">
+        <v>0.0447</v>
+      </c>
+      <c r="V28">
+        <v>0.23</v>
+      </c>
+      <c r="W28">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>15.83069824470831</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.109138525789867</v>
+      </c>
+      <c r="C29">
+        <v>18.82088384371907</v>
+      </c>
+      <c r="D29">
+        <v>24.85588384371907</v>
+      </c>
+      <c r="E29">
+        <v>-8.488</v>
+      </c>
+      <c r="F29">
+        <v>6.912000000000001</v>
+      </c>
+      <c r="G29">
+        <v>0.877</v>
+      </c>
+      <c r="H29">
+        <v>10.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>6.62</v>
+      </c>
+      <c r="K29">
+        <v>1.91</v>
+      </c>
+      <c r="L29">
+        <v>4.71</v>
+      </c>
+      <c r="M29">
+        <v>0.3089664000000001</v>
+      </c>
+      <c r="N29">
+        <v>4.4010336</v>
+      </c>
+      <c r="O29">
+        <v>1.012237728</v>
+      </c>
+      <c r="P29">
+        <v>3.388795872</v>
+      </c>
+      <c r="Q29">
+        <v>5.298795871999999</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1367745147806397</v>
+      </c>
+      <c r="T29">
+        <v>1.73980404577701</v>
+      </c>
+      <c r="U29">
+        <v>0.0447</v>
+      </c>
+      <c r="V29">
+        <v>0.23</v>
+      </c>
+      <c r="W29">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>15.24437608749689</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1089193247990186</v>
+      </c>
+      <c r="C30">
+        <v>18.64258616590446</v>
+      </c>
+      <c r="D30">
+        <v>24.93358616590446</v>
+      </c>
+      <c r="E30">
+        <v>-8.231999999999999</v>
+      </c>
+      <c r="F30">
+        <v>7.168000000000001</v>
+      </c>
+      <c r="G30">
+        <v>0.877</v>
+      </c>
+      <c r="H30">
+        <v>10.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>6.62</v>
+      </c>
+      <c r="K30">
+        <v>1.91</v>
+      </c>
+      <c r="L30">
+        <v>4.71</v>
+      </c>
+      <c r="M30">
+        <v>0.3204096000000001</v>
+      </c>
+      <c r="N30">
+        <v>4.389590399999999</v>
+      </c>
+      <c r="O30">
+        <v>1.009605792</v>
+      </c>
+      <c r="P30">
+        <v>3.379984608</v>
+      </c>
+      <c r="Q30">
+        <v>5.289984607999999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1378916733319703</v>
+      </c>
+      <c r="T30">
+        <v>1.759642235042158</v>
+      </c>
+      <c r="U30">
+        <v>0.0447</v>
+      </c>
+      <c r="V30">
+        <v>0.23</v>
+      </c>
+      <c r="W30">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>14.699934084372</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1087001238081702</v>
+      </c>
+      <c r="C31">
+        <v>18.46477582416558</v>
+      </c>
+      <c r="D31">
+        <v>25.01177582416558</v>
+      </c>
+      <c r="E31">
+        <v>-7.976000000000001</v>
+      </c>
+      <c r="F31">
+        <v>7.423999999999999</v>
+      </c>
+      <c r="G31">
+        <v>0.877</v>
+      </c>
+      <c r="H31">
+        <v>10.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>6.62</v>
+      </c>
+      <c r="K31">
+        <v>1.91</v>
+      </c>
+      <c r="L31">
+        <v>4.71</v>
+      </c>
+      <c r="M31">
+        <v>0.3318528</v>
+      </c>
+      <c r="N31">
+        <v>4.3781472</v>
+      </c>
+      <c r="O31">
+        <v>1.006973856</v>
+      </c>
+      <c r="P31">
+        <v>3.371173344</v>
+      </c>
+      <c r="Q31">
+        <v>5.281173344</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1390403011382679</v>
+      </c>
+      <c r="T31">
+        <v>1.780039246540127</v>
+      </c>
+      <c r="U31">
+        <v>0.0447</v>
+      </c>
+      <c r="V31">
+        <v>0.23</v>
+      </c>
+      <c r="W31">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>14.19303980560056</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1084809228173219</v>
+      </c>
+      <c r="C32">
+        <v>18.28745741766151</v>
+      </c>
+      <c r="D32">
+        <v>25.09045741766151</v>
+      </c>
+      <c r="E32">
+        <v>-7.720000000000001</v>
+      </c>
+      <c r="F32">
+        <v>7.68</v>
+      </c>
+      <c r="G32">
+        <v>0.877</v>
+      </c>
+      <c r="H32">
+        <v>10.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>6.62</v>
+      </c>
+      <c r="K32">
+        <v>1.91</v>
+      </c>
+      <c r="L32">
+        <v>4.71</v>
+      </c>
+      <c r="M32">
+        <v>0.343296</v>
+      </c>
+      <c r="N32">
+        <v>4.366704</v>
+      </c>
+      <c r="O32">
+        <v>1.00434192</v>
+      </c>
+      <c r="P32">
+        <v>3.36236208</v>
+      </c>
+      <c r="Q32">
+        <v>5.272362080000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1402217468818884</v>
+      </c>
+      <c r="T32">
+        <v>1.80101902979518</v>
+      </c>
+      <c r="U32">
+        <v>0.0447</v>
+      </c>
+      <c r="V32">
+        <v>0.23</v>
+      </c>
+      <c r="W32">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>13.7199384787472</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1082617218264735</v>
+      </c>
+      <c r="C33">
+        <v>18.11063560360585</v>
+      </c>
+      <c r="D33">
+        <v>25.16963560360585</v>
+      </c>
+      <c r="E33">
+        <v>-7.464</v>
+      </c>
+      <c r="F33">
+        <v>7.936</v>
+      </c>
+      <c r="G33">
+        <v>0.877</v>
+      </c>
+      <c r="H33">
+        <v>10.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>6.62</v>
+      </c>
+      <c r="K33">
+        <v>1.91</v>
+      </c>
+      <c r="L33">
+        <v>4.71</v>
+      </c>
+      <c r="M33">
+        <v>0.3547392</v>
+      </c>
+      <c r="N33">
+        <v>4.3552608</v>
+      </c>
+      <c r="O33">
+        <v>1.001709984</v>
+      </c>
+      <c r="P33">
+        <v>3.353550816</v>
+      </c>
+      <c r="Q33">
+        <v>5.263550816</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1414374374296717</v>
+      </c>
+      <c r="T33">
+        <v>1.8226069227098</v>
+      </c>
+      <c r="U33">
+        <v>0.0447</v>
+      </c>
+      <c r="V33">
+        <v>0.23</v>
+      </c>
+      <c r="W33">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>13.27735981814245</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1080425208356251</v>
+      </c>
+      <c r="C34">
+        <v>17.9343150981855</v>
+      </c>
+      <c r="D34">
+        <v>25.24931509818551</v>
+      </c>
+      <c r="E34">
+        <v>-7.208</v>
+      </c>
+      <c r="F34">
+        <v>8.192</v>
+      </c>
+      <c r="G34">
+        <v>0.877</v>
+      </c>
+      <c r="H34">
+        <v>10.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>6.62</v>
+      </c>
+      <c r="K34">
+        <v>1.91</v>
+      </c>
+      <c r="L34">
+        <v>4.71</v>
+      </c>
+      <c r="M34">
+        <v>0.3661824</v>
+      </c>
+      <c r="N34">
+        <v>4.3438176</v>
+      </c>
+      <c r="O34">
+        <v>0.9990780479999999</v>
+      </c>
+      <c r="P34">
+        <v>3.344739552</v>
+      </c>
+      <c r="Q34">
+        <v>5.254739552</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1426888835818016</v>
+      </c>
+      <c r="T34">
+        <v>1.844829753651321</v>
+      </c>
+      <c r="U34">
+        <v>0.0447</v>
+      </c>
+      <c r="V34">
+        <v>0.23</v>
+      </c>
+      <c r="W34">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>12.8624423238255</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1081028298447767</v>
+      </c>
+      <c r="C35">
+        <v>17.65634252969531</v>
+      </c>
+      <c r="D35">
+        <v>25.22734252969531</v>
+      </c>
+      <c r="E35">
+        <v>-6.952</v>
+      </c>
+      <c r="F35">
+        <v>8.448</v>
+      </c>
+      <c r="G35">
+        <v>0.877</v>
+      </c>
+      <c r="H35">
+        <v>10.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>6.62</v>
+      </c>
+      <c r="K35">
+        <v>1.91</v>
+      </c>
+      <c r="L35">
+        <v>4.71</v>
+      </c>
+      <c r="M35">
+        <v>0.3869184</v>
+      </c>
+      <c r="N35">
+        <v>4.3230816</v>
+      </c>
+      <c r="O35">
+        <v>0.994308768</v>
+      </c>
+      <c r="P35">
+        <v>3.328772832</v>
+      </c>
+      <c r="Q35">
+        <v>5.238772832</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1439776863354876</v>
+      </c>
+      <c r="T35">
+        <v>1.867715952680648</v>
+      </c>
+      <c r="U35">
+        <v>0.0458</v>
+      </c>
+      <c r="V35">
+        <v>0.23</v>
+      </c>
+      <c r="W35">
+        <v>0.035266</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>12.17310936879714</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1078920988539283</v>
+      </c>
+      <c r="C36">
+        <v>17.47728595703268</v>
+      </c>
+      <c r="D36">
+        <v>25.30428595703268</v>
+      </c>
+      <c r="E36">
+        <v>-6.696</v>
+      </c>
+      <c r="F36">
+        <v>8.704000000000001</v>
+      </c>
+      <c r="G36">
+        <v>0.877</v>
+      </c>
+      <c r="H36">
+        <v>10.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>6.62</v>
+      </c>
+      <c r="K36">
+        <v>1.91</v>
+      </c>
+      <c r="L36">
+        <v>4.71</v>
+      </c>
+      <c r="M36">
+        <v>0.3986432</v>
+      </c>
+      <c r="N36">
+        <v>4.3113568</v>
+      </c>
+      <c r="O36">
+        <v>0.9916120639999999</v>
+      </c>
+      <c r="P36">
+        <v>3.319744736</v>
+      </c>
+      <c r="Q36">
+        <v>5.229744736</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1453055437180732</v>
+      </c>
+      <c r="T36">
+        <v>1.891295672892683</v>
+      </c>
+      <c r="U36">
+        <v>0.0458</v>
+      </c>
+      <c r="V36">
+        <v>0.23</v>
+      </c>
+      <c r="W36">
+        <v>0.035266</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>11.81507674030311</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1076813678630799</v>
+      </c>
+      <c r="C37">
+        <v>17.29870017538903</v>
+      </c>
+      <c r="D37">
+        <v>25.38170017538904</v>
+      </c>
+      <c r="E37">
+        <v>-6.44</v>
+      </c>
+      <c r="F37">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="G37">
+        <v>0.877</v>
+      </c>
+      <c r="H37">
+        <v>10.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>6.62</v>
+      </c>
+      <c r="K37">
+        <v>1.91</v>
+      </c>
+      <c r="L37">
+        <v>4.71</v>
+      </c>
+      <c r="M37">
+        <v>0.4103680000000001</v>
+      </c>
+      <c r="N37">
+        <v>4.299632</v>
+      </c>
+      <c r="O37">
+        <v>0.98891536</v>
+      </c>
+      <c r="P37">
+        <v>3.31071664</v>
+      </c>
+      <c r="Q37">
+        <v>5.22071664</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1466742582508923</v>
+      </c>
+      <c r="T37">
+        <v>1.915600922957395</v>
+      </c>
+      <c r="U37">
+        <v>0.0458</v>
+      </c>
+      <c r="V37">
+        <v>0.23</v>
+      </c>
+      <c r="W37">
+        <v>0.035266</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>11.47750311915159</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1074706368722316</v>
+      </c>
+      <c r="C38">
+        <v>17.12058951894248</v>
+      </c>
+      <c r="D38">
+        <v>25.45958951894248</v>
+      </c>
+      <c r="E38">
+        <v>-6.184000000000001</v>
+      </c>
+      <c r="F38">
+        <v>9.215999999999999</v>
+      </c>
+      <c r="G38">
+        <v>0.877</v>
+      </c>
+      <c r="H38">
+        <v>10.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>6.62</v>
+      </c>
+      <c r="K38">
+        <v>1.91</v>
+      </c>
+      <c r="L38">
+        <v>4.71</v>
+      </c>
+      <c r="M38">
+        <v>0.4220928</v>
+      </c>
+      <c r="N38">
+        <v>4.2879072</v>
+      </c>
+      <c r="O38">
+        <v>0.9862186560000001</v>
+      </c>
+      <c r="P38">
+        <v>3.301688544</v>
+      </c>
+      <c r="Q38">
+        <v>5.211688544</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1480857451128618</v>
+      </c>
+      <c r="T38">
+        <v>1.94066571208663</v>
+      </c>
+      <c r="U38">
+        <v>0.0458</v>
+      </c>
+      <c r="V38">
+        <v>0.23</v>
+      </c>
+      <c r="W38">
+        <v>0.035266</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>11.15868358806405</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1072599058813832</v>
+      </c>
+      <c r="C39">
+        <v>16.94295837523649</v>
+      </c>
+      <c r="D39">
+        <v>25.5379583752365</v>
+      </c>
+      <c r="E39">
+        <v>-5.928000000000001</v>
+      </c>
+      <c r="F39">
+        <v>9.472</v>
+      </c>
+      <c r="G39">
+        <v>0.877</v>
+      </c>
+      <c r="H39">
+        <v>10.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>6.62</v>
+      </c>
+      <c r="K39">
+        <v>1.91</v>
+      </c>
+      <c r="L39">
+        <v>4.71</v>
+      </c>
+      <c r="M39">
+        <v>0.4338176</v>
+      </c>
+      <c r="N39">
+        <v>4.2761824</v>
+      </c>
+      <c r="O39">
+        <v>0.983521952</v>
+      </c>
+      <c r="P39">
+        <v>3.292660447999999</v>
+      </c>
+      <c r="Q39">
+        <v>5.202660448</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1495420410815607</v>
+      </c>
+      <c r="T39">
+        <v>1.966526208807268</v>
+      </c>
+      <c r="U39">
+        <v>0.0458</v>
+      </c>
+      <c r="V39">
+        <v>0.23</v>
+      </c>
+      <c r="W39">
+        <v>0.035266</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>10.8570975451434</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1070491748905348</v>
+      </c>
+      <c r="C40">
+        <v>16.76581118600366</v>
+      </c>
+      <c r="D40">
+        <v>25.61681118600366</v>
+      </c>
+      <c r="E40">
+        <v>-5.671999999999999</v>
+      </c>
+      <c r="F40">
+        <v>9.728000000000002</v>
+      </c>
+      <c r="G40">
+        <v>0.877</v>
+      </c>
+      <c r="H40">
+        <v>10.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>6.62</v>
+      </c>
+      <c r="K40">
+        <v>1.91</v>
+      </c>
+      <c r="L40">
+        <v>4.71</v>
+      </c>
+      <c r="M40">
+        <v>0.4455424000000001</v>
+      </c>
+      <c r="N40">
+        <v>4.2644576</v>
+      </c>
+      <c r="O40">
+        <v>0.980825248</v>
+      </c>
+      <c r="P40">
+        <v>3.283632352</v>
+      </c>
+      <c r="Q40">
+        <v>5.193632352</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1510453143395723</v>
+      </c>
+      <c r="T40">
+        <v>1.993220915099541</v>
+      </c>
+      <c r="U40">
+        <v>0.0458</v>
+      </c>
+      <c r="V40">
+        <v>0.23</v>
+      </c>
+      <c r="W40">
+        <v>0.035266</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>10.57138445185015</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1068384438996865</v>
+      </c>
+      <c r="C41">
+        <v>16.5891524480049</v>
+      </c>
+      <c r="D41">
+        <v>25.69615244800491</v>
+      </c>
+      <c r="E41">
+        <v>-5.415999999999999</v>
+      </c>
+      <c r="F41">
+        <v>9.984000000000002</v>
+      </c>
+      <c r="G41">
+        <v>0.877</v>
+      </c>
+      <c r="H41">
+        <v>10.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>6.62</v>
+      </c>
+      <c r="K41">
+        <v>1.91</v>
+      </c>
+      <c r="L41">
+        <v>4.71</v>
+      </c>
+      <c r="M41">
+        <v>0.4572672000000001</v>
+      </c>
+      <c r="N41">
+        <v>4.2527328</v>
+      </c>
+      <c r="O41">
+        <v>0.9781285439999999</v>
+      </c>
+      <c r="P41">
+        <v>3.274604255999999</v>
+      </c>
+      <c r="Q41">
+        <v>5.184604256</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1525978752453876</v>
+      </c>
+      <c r="T41">
+        <v>2.020790857663691</v>
+      </c>
+      <c r="U41">
+        <v>0.0458</v>
+      </c>
+      <c r="V41">
+        <v>0.23</v>
+      </c>
+      <c r="W41">
+        <v>0.035266</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>10.30032331205912</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1066277129088381</v>
+      </c>
+      <c r="C42">
+        <v>16.41298671388435</v>
+      </c>
+      <c r="D42">
+        <v>25.77598671388435</v>
+      </c>
+      <c r="E42">
+        <v>-5.159999999999998</v>
+      </c>
+      <c r="F42">
+        <v>10.24</v>
+      </c>
+      <c r="G42">
+        <v>0.877</v>
+      </c>
+      <c r="H42">
+        <v>10.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>6.62</v>
+      </c>
+      <c r="K42">
+        <v>1.91</v>
+      </c>
+      <c r="L42">
+        <v>4.71</v>
+      </c>
+      <c r="M42">
+        <v>0.4689920000000001</v>
+      </c>
+      <c r="N42">
+        <v>4.241008</v>
+      </c>
+      <c r="O42">
+        <v>0.97543184</v>
+      </c>
+      <c r="P42">
+        <v>3.26557616</v>
+      </c>
+      <c r="Q42">
+        <v>5.17557616</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1542021881813968</v>
+      </c>
+      <c r="T42">
+        <v>2.049279798313313</v>
+      </c>
+      <c r="U42">
+        <v>0.0458</v>
+      </c>
+      <c r="V42">
+        <v>0.23</v>
+      </c>
+      <c r="W42">
+        <v>0.035266</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>10.04281522925764</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1071115219179897</v>
+      </c>
+      <c r="C43">
+        <v>15.97443105940894</v>
+      </c>
+      <c r="D43">
+        <v>25.59343105940895</v>
+      </c>
+      <c r="E43">
+        <v>-4.903999999999998</v>
+      </c>
+      <c r="F43">
+        <v>10.496</v>
+      </c>
+      <c r="G43">
+        <v>0.877</v>
+      </c>
+      <c r="H43">
+        <v>10.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>6.62</v>
+      </c>
+      <c r="K43">
+        <v>1.91</v>
+      </c>
+      <c r="L43">
+        <v>4.71</v>
+      </c>
+      <c r="M43">
+        <v>0.5038080000000001</v>
+      </c>
+      <c r="N43">
+        <v>4.206192</v>
+      </c>
+      <c r="O43">
+        <v>0.96742416</v>
+      </c>
+      <c r="P43">
+        <v>3.23876784</v>
+      </c>
+      <c r="Q43">
+        <v>5.14876784</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1558608846067622</v>
+      </c>
+      <c r="T43">
+        <v>2.078734465764617</v>
+      </c>
+      <c r="U43">
+        <v>0.048</v>
+      </c>
+      <c r="V43">
+        <v>0.23</v>
+      </c>
+      <c r="W43">
+        <v>0.03696</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>9.348799542682924</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1069177309271413</v>
+      </c>
+      <c r="C44">
+        <v>15.79124288529783</v>
+      </c>
+      <c r="D44">
+        <v>25.66624288529783</v>
+      </c>
+      <c r="E44">
+        <v>-4.648</v>
+      </c>
+      <c r="F44">
+        <v>10.752</v>
+      </c>
+      <c r="G44">
+        <v>0.877</v>
+      </c>
+      <c r="H44">
+        <v>10.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>6.62</v>
+      </c>
+      <c r="K44">
+        <v>1.91</v>
+      </c>
+      <c r="L44">
+        <v>4.71</v>
+      </c>
+      <c r="M44">
+        <v>0.516096</v>
+      </c>
+      <c r="N44">
+        <v>4.193904</v>
+      </c>
+      <c r="O44">
+        <v>0.96459792</v>
+      </c>
+      <c r="P44">
+        <v>3.22930608</v>
+      </c>
+      <c r="Q44">
+        <v>5.13930608</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1575767774605885</v>
+      </c>
+      <c r="T44">
+        <v>2.109204811403896</v>
+      </c>
+      <c r="U44">
+        <v>0.048</v>
+      </c>
+      <c r="V44">
+        <v>0.23</v>
+      </c>
+      <c r="W44">
+        <v>0.03696</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>9.126209077380953</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.106723939936293</v>
+      </c>
+      <c r="C45">
+        <v>15.60847018401992</v>
+      </c>
+      <c r="D45">
+        <v>25.73947018401992</v>
+      </c>
+      <c r="E45">
+        <v>-4.391999999999999</v>
+      </c>
+      <c r="F45">
+        <v>11.008</v>
+      </c>
+      <c r="G45">
+        <v>0.877</v>
+      </c>
+      <c r="H45">
+        <v>10.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>6.62</v>
+      </c>
+      <c r="K45">
+        <v>1.91</v>
+      </c>
+      <c r="L45">
+        <v>4.71</v>
+      </c>
+      <c r="M45">
+        <v>0.5283840000000001</v>
+      </c>
+      <c r="N45">
+        <v>4.181616</v>
+      </c>
+      <c r="O45">
+        <v>0.96177168</v>
+      </c>
+      <c r="P45">
+        <v>3.21984432</v>
+      </c>
+      <c r="Q45">
+        <v>5.12984432</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1593528770812157</v>
+      </c>
+      <c r="T45">
+        <v>2.140744291977888</v>
+      </c>
+      <c r="U45">
+        <v>0.048</v>
+      </c>
+      <c r="V45">
+        <v>0.23</v>
+      </c>
+      <c r="W45">
+        <v>0.03696</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>8.913971656976743</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1065301489454446</v>
+      </c>
+      <c r="C46">
+        <v>15.42611652185526</v>
+      </c>
+      <c r="D46">
+        <v>25.81311652185526</v>
+      </c>
+      <c r="E46">
+        <v>-4.135999999999999</v>
+      </c>
+      <c r="F46">
+        <v>11.264</v>
+      </c>
+      <c r="G46">
+        <v>0.877</v>
+      </c>
+      <c r="H46">
+        <v>10.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>6.62</v>
+      </c>
+      <c r="K46">
+        <v>1.91</v>
+      </c>
+      <c r="L46">
+        <v>4.71</v>
+      </c>
+      <c r="M46">
+        <v>0.540672</v>
+      </c>
+      <c r="N46">
+        <v>4.169328</v>
+      </c>
+      <c r="O46">
+        <v>0.95894544</v>
+      </c>
+      <c r="P46">
+        <v>3.21038256</v>
+      </c>
+      <c r="Q46">
+        <v>5.12038256</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.161192408831151</v>
+      </c>
+      <c r="T46">
+        <v>2.173410182572379</v>
+      </c>
+      <c r="U46">
+        <v>0.048</v>
+      </c>
+      <c r="V46">
+        <v>0.23</v>
+      </c>
+      <c r="W46">
+        <v>0.03696</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>8.711381392045453</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1063363579545962</v>
+      </c>
+      <c r="C47">
+        <v>15.24418550601662</v>
+      </c>
+      <c r="D47">
+        <v>25.88718550601662</v>
+      </c>
+      <c r="E47">
+        <v>-3.879999999999999</v>
+      </c>
+      <c r="F47">
+        <v>11.52</v>
+      </c>
+      <c r="G47">
+        <v>0.877</v>
+      </c>
+      <c r="H47">
+        <v>10.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>6.62</v>
+      </c>
+      <c r="K47">
+        <v>1.91</v>
+      </c>
+      <c r="L47">
+        <v>4.71</v>
+      </c>
+      <c r="M47">
+        <v>0.5529600000000001</v>
+      </c>
+      <c r="N47">
+        <v>4.15704</v>
+      </c>
+      <c r="O47">
+        <v>0.9561192000000001</v>
+      </c>
+      <c r="P47">
+        <v>3.2009208</v>
+      </c>
+      <c r="Q47">
+        <v>5.110920800000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1630988326447203</v>
+      </c>
+      <c r="T47">
+        <v>2.207263923733942</v>
+      </c>
+      <c r="U47">
+        <v>0.048</v>
+      </c>
+      <c r="V47">
+        <v>0.23</v>
+      </c>
+      <c r="W47">
+        <v>0.03696</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>8.517795138888888</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1061425669637478</v>
+      </c>
+      <c r="C48">
+        <v>15.06268078523855</v>
+      </c>
+      <c r="D48">
+        <v>25.96168078523856</v>
+      </c>
+      <c r="E48">
+        <v>-3.623999999999999</v>
+      </c>
+      <c r="F48">
+        <v>11.776</v>
+      </c>
+      <c r="G48">
+        <v>0.877</v>
+      </c>
+      <c r="H48">
+        <v>10.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>6.62</v>
+      </c>
+      <c r="K48">
+        <v>1.91</v>
+      </c>
+      <c r="L48">
+        <v>4.71</v>
+      </c>
+      <c r="M48">
+        <v>0.5652480000000001</v>
+      </c>
+      <c r="N48">
+        <v>4.144752</v>
+      </c>
+      <c r="O48">
+        <v>0.95329296</v>
+      </c>
+      <c r="P48">
+        <v>3.19145904</v>
+      </c>
+      <c r="Q48">
+        <v>5.10145904</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1650758647476811</v>
+      </c>
+      <c r="T48">
+        <v>2.242371507160749</v>
+      </c>
+      <c r="U48">
+        <v>0.048</v>
+      </c>
+      <c r="V48">
+        <v>0.23</v>
+      </c>
+      <c r="W48">
+        <v>0.03696</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>8.332625679347824</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1059487759728994</v>
+      </c>
+      <c r="C49">
+        <v>14.88160605037655</v>
+      </c>
+      <c r="D49">
+        <v>26.03660605037655</v>
+      </c>
+      <c r="E49">
+        <v>-3.367999999999999</v>
+      </c>
+      <c r="F49">
+        <v>12.032</v>
+      </c>
+      <c r="G49">
+        <v>0.877</v>
+      </c>
+      <c r="H49">
+        <v>10.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>6.62</v>
+      </c>
+      <c r="K49">
+        <v>1.91</v>
+      </c>
+      <c r="L49">
+        <v>4.71</v>
+      </c>
+      <c r="M49">
+        <v>0.577536</v>
+      </c>
+      <c r="N49">
+        <v>4.132464</v>
+      </c>
+      <c r="O49">
+        <v>0.95046672</v>
+      </c>
+      <c r="P49">
+        <v>3.18199728</v>
+      </c>
+      <c r="Q49">
+        <v>5.091997279999999</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1671275018356593</v>
+      </c>
+      <c r="T49">
+        <v>2.278803905056491</v>
+      </c>
+      <c r="U49">
+        <v>0.048</v>
+      </c>
+      <c r="V49">
+        <v>0.23</v>
+      </c>
+      <c r="W49">
+        <v>0.03696</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>8.155335771276594</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.105754984982051</v>
+      </c>
+      <c r="C50">
+        <v>14.70096503501651</v>
+      </c>
+      <c r="D50">
+        <v>26.11196503501651</v>
+      </c>
+      <c r="E50">
+        <v>-3.112</v>
+      </c>
+      <c r="F50">
+        <v>12.288</v>
+      </c>
+      <c r="G50">
+        <v>0.877</v>
+      </c>
+      <c r="H50">
+        <v>10.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>6.62</v>
+      </c>
+      <c r="K50">
+        <v>1.91</v>
+      </c>
+      <c r="L50">
+        <v>4.71</v>
+      </c>
+      <c r="M50">
+        <v>0.589824</v>
+      </c>
+      <c r="N50">
+        <v>4.120176</v>
+      </c>
+      <c r="O50">
+        <v>0.94764048</v>
+      </c>
+      <c r="P50">
+        <v>3.17253552</v>
+      </c>
+      <c r="Q50">
+        <v>5.08253552</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1692580480424059</v>
+      </c>
+      <c r="T50">
+        <v>2.316637549025148</v>
+      </c>
+      <c r="U50">
+        <v>0.048</v>
+      </c>
+      <c r="V50">
+        <v>0.23</v>
+      </c>
+      <c r="W50">
+        <v>0.03696</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>7.985432942708333</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1055611939912027</v>
+      </c>
+      <c r="C51">
+        <v>14.52076151609505</v>
+      </c>
+      <c r="D51">
+        <v>26.18776151609505</v>
+      </c>
+      <c r="E51">
+        <v>-2.856</v>
+      </c>
+      <c r="F51">
+        <v>12.544</v>
+      </c>
+      <c r="G51">
+        <v>0.877</v>
+      </c>
+      <c r="H51">
+        <v>10.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>6.62</v>
+      </c>
+      <c r="K51">
+        <v>1.91</v>
+      </c>
+      <c r="L51">
+        <v>4.71</v>
+      </c>
+      <c r="M51">
+        <v>0.602112</v>
+      </c>
+      <c r="N51">
+        <v>4.107888</v>
+      </c>
+      <c r="O51">
+        <v>0.94481424</v>
+      </c>
+      <c r="P51">
+        <v>3.16307376</v>
+      </c>
+      <c r="Q51">
+        <v>5.07307376</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1714721450807895</v>
+      </c>
+      <c r="T51">
+        <v>2.3559548653063</v>
+      </c>
+      <c r="U51">
+        <v>0.048</v>
+      </c>
+      <c r="V51">
+        <v>0.23</v>
+      </c>
+      <c r="W51">
+        <v>0.03696</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>7.822464923469388</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1059449030003543</v>
+      </c>
+      <c r="C52">
+        <v>14.1151078629624</v>
+      </c>
+      <c r="D52">
+        <v>26.0381078629624</v>
+      </c>
+      <c r="E52">
+        <v>-2.6</v>
+      </c>
+      <c r="F52">
+        <v>12.8</v>
+      </c>
+      <c r="G52">
+        <v>0.877</v>
+      </c>
+      <c r="H52">
+        <v>10.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>6.62</v>
+      </c>
+      <c r="K52">
+        <v>1.91</v>
+      </c>
+      <c r="L52">
+        <v>4.71</v>
+      </c>
+      <c r="M52">
+        <v>0.6336000000000001</v>
+      </c>
+      <c r="N52">
+        <v>4.0764</v>
+      </c>
+      <c r="O52">
+        <v>0.937572</v>
+      </c>
+      <c r="P52">
+        <v>3.138828</v>
+      </c>
+      <c r="Q52">
+        <v>5.048828</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1737748060007086</v>
+      </c>
+      <c r="T52">
+        <v>2.396844874238698</v>
+      </c>
+      <c r="U52">
+        <v>0.0495</v>
+      </c>
+      <c r="V52">
+        <v>0.23</v>
+      </c>
+      <c r="W52">
+        <v>0.038115</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>7.43371212121212</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1057626620095059</v>
+      </c>
+      <c r="C53">
+        <v>13.92997139249307</v>
+      </c>
+      <c r="D53">
+        <v>26.10897139249307</v>
+      </c>
+      <c r="E53">
+        <v>-2.343999999999999</v>
+      </c>
+      <c r="F53">
+        <v>13.056</v>
+      </c>
+      <c r="G53">
+        <v>0.877</v>
+      </c>
+      <c r="H53">
+        <v>10.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>6.62</v>
+      </c>
+      <c r="K53">
+        <v>1.91</v>
+      </c>
+      <c r="L53">
+        <v>4.71</v>
+      </c>
+      <c r="M53">
+        <v>0.6462720000000001</v>
+      </c>
+      <c r="N53">
+        <v>4.063728</v>
+      </c>
+      <c r="O53">
+        <v>0.9346574400000001</v>
+      </c>
+      <c r="P53">
+        <v>3.12907056</v>
+      </c>
+      <c r="Q53">
+        <v>5.039070560000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1761714530806243</v>
+      </c>
+      <c r="T53">
+        <v>2.439403863127521</v>
+      </c>
+      <c r="U53">
+        <v>0.0495</v>
+      </c>
+      <c r="V53">
+        <v>0.23</v>
+      </c>
+      <c r="W53">
+        <v>0.038115</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>7.287953060011883</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1055804210186575</v>
+      </c>
+      <c r="C54">
+        <v>13.74522168927198</v>
+      </c>
+      <c r="D54">
+        <v>26.18022168927198</v>
+      </c>
+      <c r="E54">
+        <v>-2.087999999999999</v>
+      </c>
+      <c r="F54">
+        <v>13.312</v>
+      </c>
+      <c r="G54">
+        <v>0.877</v>
+      </c>
+      <c r="H54">
+        <v>10.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>6.62</v>
+      </c>
+      <c r="K54">
+        <v>1.91</v>
+      </c>
+      <c r="L54">
+        <v>4.71</v>
+      </c>
+      <c r="M54">
+        <v>0.6589440000000001</v>
+      </c>
+      <c r="N54">
+        <v>4.051056</v>
+      </c>
+      <c r="O54">
+        <v>0.9317428800000001</v>
+      </c>
+      <c r="P54">
+        <v>3.11931312</v>
+      </c>
+      <c r="Q54">
+        <v>5.02931312</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1786679604555366</v>
+      </c>
+      <c r="T54">
+        <v>2.483736143220045</v>
+      </c>
+      <c r="U54">
+        <v>0.0495</v>
+      </c>
+      <c r="V54">
+        <v>0.23</v>
+      </c>
+      <c r="W54">
+        <v>0.038115</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>7.147800116550115</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1053981800278092</v>
+      </c>
+      <c r="C55">
+        <v>13.56086192837898</v>
+      </c>
+      <c r="D55">
+        <v>26.25186192837899</v>
+      </c>
+      <c r="E55">
+        <v>-1.831999999999999</v>
+      </c>
+      <c r="F55">
+        <v>13.568</v>
+      </c>
+      <c r="G55">
+        <v>0.877</v>
+      </c>
+      <c r="H55">
+        <v>10.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>6.62</v>
+      </c>
+      <c r="K55">
+        <v>1.91</v>
+      </c>
+      <c r="L55">
+        <v>4.71</v>
+      </c>
+      <c r="M55">
+        <v>0.6716160000000001</v>
+      </c>
+      <c r="N55">
+        <v>4.038384</v>
+      </c>
+      <c r="O55">
+        <v>0.9288283199999999</v>
+      </c>
+      <c r="P55">
+        <v>3.10955568</v>
+      </c>
+      <c r="Q55">
+        <v>5.01955568</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.181270702186828</v>
+      </c>
+      <c r="T55">
+        <v>2.529954903316506</v>
+      </c>
+      <c r="U55">
+        <v>0.0495</v>
+      </c>
+      <c r="V55">
+        <v>0.23</v>
+      </c>
+      <c r="W55">
+        <v>0.038115</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>7.01293596340766</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1052159390369608</v>
+      </c>
+      <c r="C56">
+        <v>13.37689531974276</v>
+      </c>
+      <c r="D56">
+        <v>26.32389531974277</v>
+      </c>
+      <c r="E56">
+        <v>-1.575999999999999</v>
+      </c>
+      <c r="F56">
+        <v>13.824</v>
+      </c>
+      <c r="G56">
+        <v>0.877</v>
+      </c>
+      <c r="H56">
+        <v>10.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>6.62</v>
+      </c>
+      <c r="K56">
+        <v>1.91</v>
+      </c>
+      <c r="L56">
+        <v>4.71</v>
+      </c>
+      <c r="M56">
+        <v>0.6842880000000001</v>
+      </c>
+      <c r="N56">
+        <v>4.025712</v>
+      </c>
+      <c r="O56">
+        <v>0.9259137599999999</v>
+      </c>
+      <c r="P56">
+        <v>3.09979824</v>
+      </c>
+      <c r="Q56">
+        <v>5.00979824</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1839866066020887</v>
+      </c>
+      <c r="T56">
+        <v>2.578183174721508</v>
+      </c>
+      <c r="U56">
+        <v>0.0495</v>
+      </c>
+      <c r="V56">
+        <v>0.23</v>
+      </c>
+      <c r="W56">
+        <v>0.038115</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>6.88306677890011</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1050336980461124</v>
+      </c>
+      <c r="C57">
+        <v>13.19332510862031</v>
+      </c>
+      <c r="D57">
+        <v>26.39632510862031</v>
+      </c>
+      <c r="E57">
+        <v>-1.319999999999999</v>
+      </c>
+      <c r="F57">
+        <v>14.08</v>
+      </c>
+      <c r="G57">
+        <v>0.877</v>
+      </c>
+      <c r="H57">
+        <v>10.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>6.62</v>
+      </c>
+      <c r="K57">
+        <v>1.91</v>
+      </c>
+      <c r="L57">
+        <v>4.71</v>
+      </c>
+      <c r="M57">
+        <v>0.6969600000000001</v>
+      </c>
+      <c r="N57">
+        <v>4.01304</v>
+      </c>
+      <c r="O57">
+        <v>0.9229992000000001</v>
+      </c>
+      <c r="P57">
+        <v>3.0900408</v>
+      </c>
+      <c r="Q57">
+        <v>5.000040800000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1868232178802498</v>
+      </c>
+      <c r="T57">
+        <v>2.628554924855622</v>
+      </c>
+      <c r="U57">
+        <v>0.0495</v>
+      </c>
+      <c r="V57">
+        <v>0.23</v>
+      </c>
+      <c r="W57">
+        <v>0.038115</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>6.757920110192837</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.104851457055264</v>
+      </c>
+      <c r="C58">
+        <v>13.01015457608423</v>
+      </c>
+      <c r="D58">
+        <v>26.46915457608424</v>
+      </c>
+      <c r="E58">
+        <v>-1.063999999999998</v>
+      </c>
+      <c r="F58">
+        <v>14.336</v>
+      </c>
+      <c r="G58">
+        <v>0.877</v>
+      </c>
+      <c r="H58">
+        <v>10.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>6.62</v>
+      </c>
+      <c r="K58">
+        <v>1.91</v>
+      </c>
+      <c r="L58">
+        <v>4.71</v>
+      </c>
+      <c r="M58">
+        <v>0.7096320000000002</v>
+      </c>
+      <c r="N58">
+        <v>4.000368</v>
+      </c>
+      <c r="O58">
+        <v>0.92008464</v>
+      </c>
+      <c r="P58">
+        <v>3.08028336</v>
+      </c>
+      <c r="Q58">
+        <v>4.99028336</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.189788766034691</v>
+      </c>
+      <c r="T58">
+        <v>2.681216299995832</v>
+      </c>
+      <c r="U58">
+        <v>0.0495</v>
+      </c>
+      <c r="V58">
+        <v>0.23</v>
+      </c>
+      <c r="W58">
+        <v>0.038115</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>6.637242965367964</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1046692160644156</v>
+      </c>
+      <c r="C59">
+        <v>12.82738703951824</v>
+      </c>
+      <c r="D59">
+        <v>26.54238703951824</v>
+      </c>
+      <c r="E59">
+        <v>-0.8079999999999981</v>
+      </c>
+      <c r="F59">
+        <v>14.592</v>
+      </c>
+      <c r="G59">
+        <v>0.877</v>
+      </c>
+      <c r="H59">
+        <v>10.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>6.62</v>
+      </c>
+      <c r="K59">
+        <v>1.91</v>
+      </c>
+      <c r="L59">
+        <v>4.71</v>
+      </c>
+      <c r="M59">
+        <v>0.7223040000000002</v>
+      </c>
+      <c r="N59">
+        <v>3.987696</v>
+      </c>
+      <c r="O59">
+        <v>0.91717008</v>
+      </c>
+      <c r="P59">
+        <v>3.07052592</v>
+      </c>
+      <c r="Q59">
+        <v>4.98052592</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1928922466614317</v>
+      </c>
+      <c r="T59">
+        <v>2.736327041421633</v>
+      </c>
+      <c r="U59">
+        <v>0.0495</v>
+      </c>
+      <c r="V59">
+        <v>0.23</v>
+      </c>
+      <c r="W59">
+        <v>0.038115</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>6.52080010632642</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1044869750735673</v>
+      </c>
+      <c r="C60">
+        <v>12.64502585312087</v>
+      </c>
+      <c r="D60">
+        <v>26.61602585312087</v>
+      </c>
+      <c r="E60">
+        <v>-0.5520000000000014</v>
+      </c>
+      <c r="F60">
+        <v>14.848</v>
+      </c>
+      <c r="G60">
+        <v>0.877</v>
+      </c>
+      <c r="H60">
+        <v>10.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>6.62</v>
+      </c>
+      <c r="K60">
+        <v>1.91</v>
+      </c>
+      <c r="L60">
+        <v>4.71</v>
+      </c>
+      <c r="M60">
+        <v>0.734976</v>
+      </c>
+      <c r="N60">
+        <v>3.975024</v>
+      </c>
+      <c r="O60">
+        <v>0.91425552</v>
+      </c>
+      <c r="P60">
+        <v>3.06076848</v>
+      </c>
+      <c r="Q60">
+        <v>4.97076848</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1961435120799221</v>
+      </c>
+      <c r="T60">
+        <v>2.79406210386771</v>
+      </c>
+      <c r="U60">
+        <v>0.0495</v>
+      </c>
+      <c r="V60">
+        <v>0.23</v>
+      </c>
+      <c r="W60">
+        <v>0.038115</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>6.408372518286312</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1043047340827189</v>
+      </c>
+      <c r="C61">
+        <v>12.46307440841756</v>
+      </c>
+      <c r="D61">
+        <v>26.69007440841756</v>
+      </c>
+      <c r="E61">
+        <v>-0.2960000000000012</v>
+      </c>
+      <c r="F61">
+        <v>15.104</v>
+      </c>
+      <c r="G61">
+        <v>0.877</v>
+      </c>
+      <c r="H61">
+        <v>10.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>6.62</v>
+      </c>
+      <c r="K61">
+        <v>1.91</v>
+      </c>
+      <c r="L61">
+        <v>4.71</v>
+      </c>
+      <c r="M61">
+        <v>0.747648</v>
+      </c>
+      <c r="N61">
+        <v>3.962352</v>
+      </c>
+      <c r="O61">
+        <v>0.9113409600000001</v>
+      </c>
+      <c r="P61">
+        <v>3.05101104</v>
+      </c>
+      <c r="Q61">
+        <v>4.961011040000001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1995533758115094</v>
+      </c>
+      <c r="T61">
+        <v>2.854613510823352</v>
+      </c>
+      <c r="U61">
+        <v>0.0495</v>
+      </c>
+      <c r="V61">
+        <v>0.23</v>
+      </c>
+      <c r="W61">
+        <v>0.038115</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>6.299756034925527</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1041224930918705</v>
+      </c>
+      <c r="C62">
+        <v>12.28153613478134</v>
+      </c>
+      <c r="D62">
+        <v>26.76453613478134</v>
+      </c>
+      <c r="E62">
+        <v>-0.04000000000000092</v>
+      </c>
+      <c r="F62">
+        <v>15.36</v>
+      </c>
+      <c r="G62">
+        <v>0.877</v>
+      </c>
+      <c r="H62">
+        <v>10.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>6.62</v>
+      </c>
+      <c r="K62">
+        <v>1.91</v>
+      </c>
+      <c r="L62">
+        <v>4.71</v>
+      </c>
+      <c r="M62">
+        <v>0.76032</v>
+      </c>
+      <c r="N62">
+        <v>3.94968</v>
+      </c>
+      <c r="O62">
+        <v>0.9084264</v>
+      </c>
+      <c r="P62">
+        <v>3.0412536</v>
+      </c>
+      <c r="Q62">
+        <v>4.9512536</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2031337327296762</v>
+      </c>
+      <c r="T62">
+        <v>2.918192488126776</v>
+      </c>
+      <c r="U62">
+        <v>0.0495</v>
+      </c>
+      <c r="V62">
+        <v>0.23</v>
+      </c>
+      <c r="W62">
+        <v>0.038115</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>6.194760101010101</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1045978321010221</v>
+      </c>
+      <c r="C63">
+        <v>11.83218283300117</v>
+      </c>
+      <c r="D63">
+        <v>26.57118283300117</v>
+      </c>
+      <c r="E63">
+        <v>0.2159999999999993</v>
+      </c>
+      <c r="F63">
+        <v>15.616</v>
+      </c>
+      <c r="G63">
+        <v>0.877</v>
+      </c>
+      <c r="H63">
+        <v>10.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>6.62</v>
+      </c>
+      <c r="K63">
+        <v>1.91</v>
+      </c>
+      <c r="L63">
+        <v>4.71</v>
+      </c>
+      <c r="M63">
+        <v>0.7948544</v>
+      </c>
+      <c r="N63">
+        <v>3.9151456</v>
+      </c>
+      <c r="O63">
+        <v>0.900483488</v>
+      </c>
+      <c r="P63">
+        <v>3.014662112</v>
+      </c>
+      <c r="Q63">
+        <v>4.924662112</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2068976976949285</v>
+      </c>
+      <c r="T63">
+        <v>2.985031925804735</v>
+      </c>
+      <c r="U63">
+        <v>0.0509</v>
+      </c>
+      <c r="V63">
+        <v>0.23</v>
+      </c>
+      <c r="W63">
+        <v>0.039193</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>5.925613546329995</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1044263711101738</v>
+      </c>
+      <c r="C64">
+        <v>11.64560494578128</v>
+      </c>
+      <c r="D64">
+        <v>26.64060494578128</v>
+      </c>
+      <c r="E64">
+        <v>0.4719999999999995</v>
+      </c>
+      <c r="F64">
+        <v>15.872</v>
+      </c>
+      <c r="G64">
+        <v>0.877</v>
+      </c>
+      <c r="H64">
+        <v>10.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>6.62</v>
+      </c>
+      <c r="K64">
+        <v>1.91</v>
+      </c>
+      <c r="L64">
+        <v>4.71</v>
+      </c>
+      <c r="M64">
+        <v>0.8078848</v>
+      </c>
+      <c r="N64">
+        <v>3.9021152</v>
+      </c>
+      <c r="O64">
+        <v>0.897486496</v>
+      </c>
+      <c r="P64">
+        <v>3.004628704</v>
+      </c>
+      <c r="Q64">
+        <v>4.914628704</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2108597660794046</v>
+      </c>
+      <c r="T64">
+        <v>3.055389228623639</v>
+      </c>
+      <c r="U64">
+        <v>0.0509</v>
+      </c>
+      <c r="V64">
+        <v>0.23</v>
+      </c>
+      <c r="W64">
+        <v>0.039193</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>5.830039134292414</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1042549101193254</v>
+      </c>
+      <c r="C65">
+        <v>11.45939076494254</v>
+      </c>
+      <c r="D65">
+        <v>26.71039076494254</v>
+      </c>
+      <c r="E65">
+        <v>0.7279999999999998</v>
+      </c>
+      <c r="F65">
+        <v>16.128</v>
+      </c>
+      <c r="G65">
+        <v>0.877</v>
+      </c>
+      <c r="H65">
+        <v>10.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>6.62</v>
+      </c>
+      <c r="K65">
+        <v>1.91</v>
+      </c>
+      <c r="L65">
+        <v>4.71</v>
+      </c>
+      <c r="M65">
+        <v>0.8209152000000001</v>
+      </c>
+      <c r="N65">
+        <v>3.8890848</v>
+      </c>
+      <c r="O65">
+        <v>0.894489504</v>
+      </c>
+      <c r="P65">
+        <v>2.994595296</v>
+      </c>
+      <c r="Q65">
+        <v>4.904595296</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.215036000322501</v>
+      </c>
+      <c r="T65">
+        <v>3.129549628892214</v>
+      </c>
+      <c r="U65">
+        <v>0.0509</v>
+      </c>
+      <c r="V65">
+        <v>0.23</v>
+      </c>
+      <c r="W65">
+        <v>0.039193</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>5.737498830573486</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.104083449128477</v>
+      </c>
+      <c r="C66">
+        <v>11.2735431562093</v>
+      </c>
+      <c r="D66">
+        <v>26.7805431562093</v>
+      </c>
+      <c r="E66">
+        <v>0.984</v>
+      </c>
+      <c r="F66">
+        <v>16.384</v>
+      </c>
+      <c r="G66">
+        <v>0.877</v>
+      </c>
+      <c r="H66">
+        <v>10.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>6.62</v>
+      </c>
+      <c r="K66">
+        <v>1.91</v>
+      </c>
+      <c r="L66">
+        <v>4.71</v>
+      </c>
+      <c r="M66">
+        <v>0.8339456000000001</v>
+      </c>
+      <c r="N66">
+        <v>3.8760544</v>
+      </c>
+      <c r="O66">
+        <v>0.891492512</v>
+      </c>
+      <c r="P66">
+        <v>2.984561888</v>
+      </c>
+      <c r="Q66">
+        <v>4.894561888</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2194442475791027</v>
+      </c>
+      <c r="T66">
+        <v>3.207830051397931</v>
+      </c>
+      <c r="U66">
+        <v>0.0509</v>
+      </c>
+      <c r="V66">
+        <v>0.23</v>
+      </c>
+      <c r="W66">
+        <v>0.039193</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>5.647850411345776</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1039119881376286</v>
+      </c>
+      <c r="C67">
+        <v>11.08806501549144</v>
+      </c>
+      <c r="D67">
+        <v>26.85106501549144</v>
+      </c>
+      <c r="E67">
+        <v>1.24</v>
+      </c>
+      <c r="F67">
+        <v>16.64</v>
+      </c>
+      <c r="G67">
+        <v>0.877</v>
+      </c>
+      <c r="H67">
+        <v>10.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>6.62</v>
+      </c>
+      <c r="K67">
+        <v>1.91</v>
+      </c>
+      <c r="L67">
+        <v>4.71</v>
+      </c>
+      <c r="M67">
+        <v>0.8469760000000001</v>
+      </c>
+      <c r="N67">
+        <v>3.863024</v>
+      </c>
+      <c r="O67">
+        <v>0.88849552</v>
+      </c>
+      <c r="P67">
+        <v>2.97452848</v>
+      </c>
+      <c r="Q67">
+        <v>4.88452848</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2241043946789389</v>
+      </c>
+      <c r="T67">
+        <v>3.290583640903975</v>
+      </c>
+      <c r="U67">
+        <v>0.0509</v>
+      </c>
+      <c r="V67">
+        <v>0.23</v>
+      </c>
+      <c r="W67">
+        <v>0.039193</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>5.560960405017379</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1037405271467802</v>
+      </c>
+      <c r="C68">
+        <v>10.90295926928282</v>
+      </c>
+      <c r="D68">
+        <v>26.92195926928282</v>
+      </c>
+      <c r="E68">
+        <v>1.496</v>
+      </c>
+      <c r="F68">
+        <v>16.896</v>
+      </c>
+      <c r="G68">
+        <v>0.877</v>
+      </c>
+      <c r="H68">
+        <v>10.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>6.62</v>
+      </c>
+      <c r="K68">
+        <v>1.91</v>
+      </c>
+      <c r="L68">
+        <v>4.71</v>
+      </c>
+      <c r="M68">
+        <v>0.8600064000000001</v>
+      </c>
+      <c r="N68">
+        <v>3.8499936</v>
+      </c>
+      <c r="O68">
+        <v>0.8854985280000001</v>
+      </c>
+      <c r="P68">
+        <v>2.964495072</v>
+      </c>
+      <c r="Q68">
+        <v>4.874495072</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2290386680787654</v>
+      </c>
+      <c r="T68">
+        <v>3.378205088616258</v>
+      </c>
+      <c r="U68">
+        <v>0.0509</v>
+      </c>
+      <c r="V68">
+        <v>0.23</v>
+      </c>
+      <c r="W68">
+        <v>0.039193</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>5.476703429183782</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1035690661559318</v>
+      </c>
+      <c r="C69">
+        <v>10.71822887506621</v>
+      </c>
+      <c r="D69">
+        <v>26.99322887506621</v>
+      </c>
+      <c r="E69">
+        <v>1.752000000000001</v>
+      </c>
+      <c r="F69">
+        <v>17.152</v>
+      </c>
+      <c r="G69">
+        <v>0.877</v>
+      </c>
+      <c r="H69">
+        <v>10.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>6.62</v>
+      </c>
+      <c r="K69">
+        <v>1.91</v>
+      </c>
+      <c r="L69">
+        <v>4.71</v>
+      </c>
+      <c r="M69">
+        <v>0.8730368000000001</v>
+      </c>
+      <c r="N69">
+        <v>3.8369632</v>
+      </c>
+      <c r="O69">
+        <v>0.882501536</v>
+      </c>
+      <c r="P69">
+        <v>2.954461664</v>
+      </c>
+      <c r="Q69">
+        <v>4.864461664</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2342719883513087</v>
+      </c>
+      <c r="T69">
+        <v>3.471136927098981</v>
+      </c>
+      <c r="U69">
+        <v>0.0509</v>
+      </c>
+      <c r="V69">
+        <v>0.23</v>
+      </c>
+      <c r="W69">
+        <v>0.039193</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>5.394961586957159</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1033976051650835</v>
+      </c>
+      <c r="C70">
+        <v>10.53387682172441</v>
+      </c>
+      <c r="D70">
+        <v>27.06487682172441</v>
+      </c>
+      <c r="E70">
+        <v>2.008000000000001</v>
+      </c>
+      <c r="F70">
+        <v>17.408</v>
+      </c>
+      <c r="G70">
+        <v>0.877</v>
+      </c>
+      <c r="H70">
+        <v>10.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>6.62</v>
+      </c>
+      <c r="K70">
+        <v>1.91</v>
+      </c>
+      <c r="L70">
+        <v>4.71</v>
+      </c>
+      <c r="M70">
+        <v>0.8860672000000001</v>
+      </c>
+      <c r="N70">
+        <v>3.8239328</v>
+      </c>
+      <c r="O70">
+        <v>0.879504544</v>
+      </c>
+      <c r="P70">
+        <v>2.944428256</v>
+      </c>
+      <c r="Q70">
+        <v>4.854428256</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2398323911408859</v>
+      </c>
+      <c r="T70">
+        <v>3.569877005486875</v>
+      </c>
+      <c r="U70">
+        <v>0.0509</v>
+      </c>
+      <c r="V70">
+        <v>0.23</v>
+      </c>
+      <c r="W70">
+        <v>0.039193</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>5.31562391656073</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1032261441742351</v>
+      </c>
+      <c r="C71">
+        <v>10.34990612995822</v>
+      </c>
+      <c r="D71">
+        <v>27.13690612995822</v>
+      </c>
+      <c r="E71">
+        <v>2.264000000000001</v>
+      </c>
+      <c r="F71">
+        <v>17.664</v>
+      </c>
+      <c r="G71">
+        <v>0.877</v>
+      </c>
+      <c r="H71">
+        <v>10.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>6.62</v>
+      </c>
+      <c r="K71">
+        <v>1.91</v>
+      </c>
+      <c r="L71">
+        <v>4.71</v>
+      </c>
+      <c r="M71">
+        <v>0.8990976000000001</v>
+      </c>
+      <c r="N71">
+        <v>3.8109024</v>
+      </c>
+      <c r="O71">
+        <v>0.876507552</v>
+      </c>
+      <c r="P71">
+        <v>2.934394848</v>
+      </c>
+      <c r="Q71">
+        <v>4.844394848</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2457515295943068</v>
+      </c>
+      <c r="T71">
+        <v>3.674987411512698</v>
+      </c>
+      <c r="U71">
+        <v>0.0509</v>
+      </c>
+      <c r="V71">
+        <v>0.23</v>
+      </c>
+      <c r="W71">
+        <v>0.039193</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>5.238585888784487</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1030546831833867</v>
+      </c>
+      <c r="C72">
+        <v>10.16631985271088</v>
+      </c>
+      <c r="D72">
+        <v>27.20931985271089</v>
+      </c>
+      <c r="E72">
+        <v>2.520000000000001</v>
+      </c>
+      <c r="F72">
+        <v>17.92</v>
+      </c>
+      <c r="G72">
+        <v>0.877</v>
+      </c>
+      <c r="H72">
+        <v>10.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>6.62</v>
+      </c>
+      <c r="K72">
+        <v>1.91</v>
+      </c>
+      <c r="L72">
+        <v>4.71</v>
+      </c>
+      <c r="M72">
+        <v>0.912128</v>
+      </c>
+      <c r="N72">
+        <v>3.797872</v>
+      </c>
+      <c r="O72">
+        <v>0.87351056</v>
+      </c>
+      <c r="P72">
+        <v>2.92436144</v>
+      </c>
+      <c r="Q72">
+        <v>4.83436144</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2520652772779557</v>
+      </c>
+      <c r="T72">
+        <v>3.787105177940241</v>
+      </c>
+      <c r="U72">
+        <v>0.0509</v>
+      </c>
+      <c r="V72">
+        <v>0.23</v>
+      </c>
+      <c r="W72">
+        <v>0.039193</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>5.163748947516138</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1028832221925384</v>
+      </c>
+      <c r="C73">
+        <v>9.983121075599442</v>
+      </c>
+      <c r="D73">
+        <v>27.28212107559944</v>
+      </c>
+      <c r="E73">
+        <v>2.775999999999998</v>
+      </c>
+      <c r="F73">
+        <v>18.176</v>
+      </c>
+      <c r="G73">
+        <v>0.877</v>
+      </c>
+      <c r="H73">
+        <v>10.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>6.62</v>
+      </c>
+      <c r="K73">
+        <v>1.91</v>
+      </c>
+      <c r="L73">
+        <v>4.71</v>
+      </c>
+      <c r="M73">
+        <v>0.9251583999999999</v>
+      </c>
+      <c r="N73">
+        <v>3.7848416</v>
+      </c>
+      <c r="O73">
+        <v>0.870513568</v>
+      </c>
+      <c r="P73">
+        <v>2.914328032</v>
+      </c>
+      <c r="Q73">
+        <v>4.824328032</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2588144558363391</v>
+      </c>
+      <c r="T73">
+        <v>3.906955204121408</v>
+      </c>
+      <c r="U73">
+        <v>0.0509</v>
+      </c>
+      <c r="V73">
+        <v>0.23</v>
+      </c>
+      <c r="W73">
+        <v>0.039193</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>5.091020089100418</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.10271176120169</v>
+      </c>
+      <c r="C74">
+        <v>9.80031291735305</v>
+      </c>
+      <c r="D74">
+        <v>27.35531291735305</v>
+      </c>
+      <c r="E74">
+        <v>3.031999999999998</v>
+      </c>
+      <c r="F74">
+        <v>18.432</v>
+      </c>
+      <c r="G74">
+        <v>0.877</v>
+      </c>
+      <c r="H74">
+        <v>10.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>6.62</v>
+      </c>
+      <c r="K74">
+        <v>1.91</v>
+      </c>
+      <c r="L74">
+        <v>4.71</v>
+      </c>
+      <c r="M74">
+        <v>0.9381887999999999</v>
+      </c>
+      <c r="N74">
+        <v>3.7718112</v>
+      </c>
+      <c r="O74">
+        <v>0.8675165760000001</v>
+      </c>
+      <c r="P74">
+        <v>2.904294624</v>
+      </c>
+      <c r="Q74">
+        <v>4.814294624</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2660457185774641</v>
+      </c>
+      <c r="T74">
+        <v>4.035365946458373</v>
+      </c>
+      <c r="U74">
+        <v>0.0509</v>
+      </c>
+      <c r="V74">
+        <v>0.23</v>
+      </c>
+      <c r="W74">
+        <v>0.039193</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>5.020311476751801</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1025403002108416</v>
+      </c>
+      <c r="C75">
+        <v>9.617898530258248</v>
+      </c>
+      <c r="D75">
+        <v>27.42889853025825</v>
+      </c>
+      <c r="E75">
+        <v>3.287999999999998</v>
+      </c>
+      <c r="F75">
+        <v>18.688</v>
+      </c>
+      <c r="G75">
+        <v>0.877</v>
+      </c>
+      <c r="H75">
+        <v>10.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>6.62</v>
+      </c>
+      <c r="K75">
+        <v>1.91</v>
+      </c>
+      <c r="L75">
+        <v>4.71</v>
+      </c>
+      <c r="M75">
+        <v>0.9512191999999999</v>
+      </c>
+      <c r="N75">
+        <v>3.7587808</v>
+      </c>
+      <c r="O75">
+        <v>0.8645195840000001</v>
+      </c>
+      <c r="P75">
+        <v>2.894261216</v>
+      </c>
+      <c r="Q75">
+        <v>4.804261216</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2738126304105244</v>
+      </c>
+      <c r="T75">
+        <v>4.173288595635113</v>
+      </c>
+      <c r="U75">
+        <v>0.0509</v>
+      </c>
+      <c r="V75">
+        <v>0.23</v>
+      </c>
+      <c r="W75">
+        <v>0.039193</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>4.95154008665931</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1023688392199932</v>
+      </c>
+      <c r="C76">
+        <v>9.435881100611667</v>
+      </c>
+      <c r="D76">
+        <v>27.50288110061167</v>
+      </c>
+      <c r="E76">
+        <v>3.543999999999999</v>
+      </c>
+      <c r="F76">
+        <v>18.944</v>
+      </c>
+      <c r="G76">
+        <v>0.877</v>
+      </c>
+      <c r="H76">
+        <v>10.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>6.62</v>
+      </c>
+      <c r="K76">
+        <v>1.91</v>
+      </c>
+      <c r="L76">
+        <v>4.71</v>
+      </c>
+      <c r="M76">
+        <v>0.9642495999999999</v>
+      </c>
+      <c r="N76">
+        <v>3.7457504</v>
+      </c>
+      <c r="O76">
+        <v>0.861522592</v>
+      </c>
+      <c r="P76">
+        <v>2.884227808</v>
+      </c>
+      <c r="Q76">
+        <v>4.794227808</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2821769969999739</v>
+      </c>
+      <c r="T76">
+        <v>4.321820679363911</v>
+      </c>
+      <c r="U76">
+        <v>0.0509</v>
+      </c>
+      <c r="V76">
+        <v>0.23</v>
+      </c>
+      <c r="W76">
+        <v>0.039193</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>4.884627382785537</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1021973782291448</v>
+      </c>
+      <c r="C77">
+        <v>9.254263849179775</v>
+      </c>
+      <c r="D77">
+        <v>27.57726384917978</v>
+      </c>
+      <c r="E77">
+        <v>3.800000000000002</v>
+      </c>
+      <c r="F77">
+        <v>19.2</v>
+      </c>
+      <c r="G77">
+        <v>0.877</v>
+      </c>
+      <c r="H77">
+        <v>10.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>6.62</v>
+      </c>
+      <c r="K77">
+        <v>1.91</v>
+      </c>
+      <c r="L77">
+        <v>4.71</v>
+      </c>
+      <c r="M77">
+        <v>0.9772800000000001</v>
+      </c>
+      <c r="N77">
+        <v>3.73272</v>
+      </c>
+      <c r="O77">
+        <v>0.8585255999999999</v>
+      </c>
+      <c r="P77">
+        <v>2.874194399999999</v>
+      </c>
+      <c r="Q77">
+        <v>4.7841944</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2912105129165793</v>
+      </c>
+      <c r="T77">
+        <v>4.482235329791012</v>
+      </c>
+      <c r="U77">
+        <v>0.0509</v>
+      </c>
+      <c r="V77">
+        <v>0.23</v>
+      </c>
+      <c r="W77">
+        <v>0.039193</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>4.819499017681729</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1020259172382964</v>
+      </c>
+      <c r="C78">
+        <v>9.073050031666398</v>
+      </c>
+      <c r="D78">
+        <v>27.6520500316664</v>
+      </c>
+      <c r="E78">
+        <v>4.056000000000003</v>
+      </c>
+      <c r="F78">
+        <v>19.456</v>
+      </c>
+      <c r="G78">
+        <v>0.877</v>
+      </c>
+      <c r="H78">
+        <v>10.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>6.62</v>
+      </c>
+      <c r="K78">
+        <v>1.91</v>
+      </c>
+      <c r="L78">
+        <v>4.71</v>
+      </c>
+      <c r="M78">
+        <v>0.9903104000000001</v>
+      </c>
+      <c r="N78">
+        <v>3.7196896</v>
+      </c>
+      <c r="O78">
+        <v>0.855528608</v>
+      </c>
+      <c r="P78">
+        <v>2.864160992</v>
+      </c>
+      <c r="Q78">
+        <v>4.774160992</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3009968218262352</v>
+      </c>
+      <c r="T78">
+        <v>4.656017867753705</v>
+      </c>
+      <c r="U78">
+        <v>0.0509</v>
+      </c>
+      <c r="V78">
+        <v>0.23</v>
+      </c>
+      <c r="W78">
+        <v>0.039193</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>4.756084556922758</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1018544562474481</v>
+      </c>
+      <c r="C79">
+        <v>8.892242939187675</v>
+      </c>
+      <c r="D79">
+        <v>27.72724293918768</v>
+      </c>
+      <c r="E79">
+        <v>4.312000000000003</v>
+      </c>
+      <c r="F79">
+        <v>19.712</v>
+      </c>
+      <c r="G79">
+        <v>0.877</v>
+      </c>
+      <c r="H79">
+        <v>10.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>6.62</v>
+      </c>
+      <c r="K79">
+        <v>1.91</v>
+      </c>
+      <c r="L79">
+        <v>4.71</v>
+      </c>
+      <c r="M79">
+        <v>1.0033408</v>
+      </c>
+      <c r="N79">
+        <v>3.7066592</v>
+      </c>
+      <c r="O79">
+        <v>0.852531616</v>
+      </c>
+      <c r="P79">
+        <v>2.854127584</v>
+      </c>
+      <c r="Q79">
+        <v>4.764127584</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3116341141193394</v>
+      </c>
+      <c r="T79">
+        <v>4.844911930756632</v>
+      </c>
+      <c r="U79">
+        <v>0.0509</v>
+      </c>
+      <c r="V79">
+        <v>0.23</v>
+      </c>
+      <c r="W79">
+        <v>0.039193</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>4.69431722501467</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1016829952565997</v>
+      </c>
+      <c r="C80">
+        <v>8.711845898754824</v>
+      </c>
+      <c r="D80">
+        <v>27.80284589875483</v>
+      </c>
+      <c r="E80">
+        <v>4.568000000000003</v>
+      </c>
+      <c r="F80">
+        <v>19.968</v>
+      </c>
+      <c r="G80">
+        <v>0.877</v>
+      </c>
+      <c r="H80">
+        <v>10.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>6.62</v>
+      </c>
+      <c r="K80">
+        <v>1.91</v>
+      </c>
+      <c r="L80">
+        <v>4.71</v>
+      </c>
+      <c r="M80">
+        <v>1.0163712</v>
+      </c>
+      <c r="N80">
+        <v>3.6936288</v>
+      </c>
+      <c r="O80">
+        <v>0.849534624</v>
+      </c>
+      <c r="P80">
+        <v>2.844094176</v>
+      </c>
+      <c r="Q80">
+        <v>4.754094176000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3232384329845441</v>
+      </c>
+      <c r="T80">
+        <v>5.05097818130528</v>
+      </c>
+      <c r="U80">
+        <v>0.0509</v>
+      </c>
+      <c r="V80">
+        <v>0.23</v>
+      </c>
+      <c r="W80">
+        <v>0.039193</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>4.634133670847815</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1015115342657513</v>
+      </c>
+      <c r="C81">
+        <v>8.531862273764947</v>
+      </c>
+      <c r="D81">
+        <v>27.87886227376495</v>
+      </c>
+      <c r="E81">
+        <v>4.824000000000003</v>
+      </c>
+      <c r="F81">
+        <v>20.224</v>
+      </c>
+      <c r="G81">
+        <v>0.877</v>
+      </c>
+      <c r="H81">
+        <v>10.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>6.62</v>
+      </c>
+      <c r="K81">
+        <v>1.91</v>
+      </c>
+      <c r="L81">
+        <v>4.71</v>
+      </c>
+      <c r="M81">
+        <v>1.0294016</v>
+      </c>
+      <c r="N81">
+        <v>3.6805984</v>
+      </c>
+      <c r="O81">
+        <v>0.8465376320000001</v>
+      </c>
+      <c r="P81">
+        <v>2.834060768</v>
+      </c>
+      <c r="Q81">
+        <v>4.744060768000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3359479250750063</v>
+      </c>
+      <c r="T81">
+        <v>5.276669789049037</v>
+      </c>
+      <c r="U81">
+        <v>0.0509</v>
+      </c>
+      <c r="V81">
+        <v>0.23</v>
+      </c>
+      <c r="W81">
+        <v>0.039193</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>4.575473750963666</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1013400732749029</v>
+      </c>
+      <c r="C82">
+        <v>8.35229546449969</v>
+      </c>
+      <c r="D82">
+        <v>27.9552954644997</v>
+      </c>
+      <c r="E82">
+        <v>5.080000000000004</v>
+      </c>
+      <c r="F82">
+        <v>20.48</v>
+      </c>
+      <c r="G82">
+        <v>0.877</v>
+      </c>
+      <c r="H82">
+        <v>10.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>6.62</v>
+      </c>
+      <c r="K82">
+        <v>1.91</v>
+      </c>
+      <c r="L82">
+        <v>4.71</v>
+      </c>
+      <c r="M82">
+        <v>1.042432</v>
+      </c>
+      <c r="N82">
+        <v>3.667568</v>
+      </c>
+      <c r="O82">
+        <v>0.84354064</v>
+      </c>
+      <c r="P82">
+        <v>2.82402736</v>
+      </c>
+      <c r="Q82">
+        <v>4.73402736</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3499283663745147</v>
+      </c>
+      <c r="T82">
+        <v>5.52493055756717</v>
+      </c>
+      <c r="U82">
+        <v>0.0509</v>
+      </c>
+      <c r="V82">
+        <v>0.23</v>
+      </c>
+      <c r="W82">
+        <v>0.039193</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>4.518280329076619</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1027902322840546</v>
+      </c>
+      <c r="C83">
+        <v>7.462767156751354</v>
+      </c>
+      <c r="D83">
+        <v>27.32176715675136</v>
+      </c>
+      <c r="E83">
+        <v>5.336000000000004</v>
+      </c>
+      <c r="F83">
+        <v>20.736</v>
+      </c>
+      <c r="G83">
+        <v>0.877</v>
+      </c>
+      <c r="H83">
+        <v>10.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>6.62</v>
+      </c>
+      <c r="K83">
+        <v>1.91</v>
+      </c>
+      <c r="L83">
+        <v>4.71</v>
+      </c>
+      <c r="M83">
+        <v>1.109376</v>
+      </c>
+      <c r="N83">
+        <v>3.600624</v>
+      </c>
+      <c r="O83">
+        <v>0.82814352</v>
+      </c>
+      <c r="P83">
+        <v>2.77248048</v>
+      </c>
+      <c r="Q83">
+        <v>4.68248048</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3653804330739714</v>
+      </c>
+      <c r="T83">
+        <v>5.799324038560895</v>
+      </c>
+      <c r="U83">
+        <v>0.0535</v>
+      </c>
+      <c r="V83">
+        <v>0.23</v>
+      </c>
+      <c r="W83">
+        <v>0.041195</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>4.245629975770163</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1026387912932062</v>
+      </c>
+      <c r="C84">
+        <v>7.271580969891136</v>
+      </c>
+      <c r="D84">
+        <v>27.38658096989114</v>
+      </c>
+      <c r="E84">
+        <v>5.592000000000004</v>
+      </c>
+      <c r="F84">
+        <v>20.992</v>
+      </c>
+      <c r="G84">
+        <v>0.877</v>
+      </c>
+      <c r="H84">
+        <v>10.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>6.62</v>
+      </c>
+      <c r="K84">
+        <v>1.91</v>
+      </c>
+      <c r="L84">
+        <v>4.71</v>
+      </c>
+      <c r="M84">
+        <v>1.123072</v>
+      </c>
+      <c r="N84">
+        <v>3.586927999999999</v>
+      </c>
+      <c r="O84">
+        <v>0.8249934399999999</v>
+      </c>
+      <c r="P84">
+        <v>2.761934559999999</v>
+      </c>
+      <c r="Q84">
+        <v>4.67193456</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3825493960733677</v>
+      </c>
+      <c r="T84">
+        <v>6.10420568410948</v>
+      </c>
+      <c r="U84">
+        <v>0.0535</v>
+      </c>
+      <c r="V84">
+        <v>0.23</v>
+      </c>
+      <c r="W84">
+        <v>0.041195</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>4.193854000455891</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1024873503023578</v>
+      </c>
+      <c r="C85">
+        <v>7.080703022203554</v>
+      </c>
+      <c r="D85">
+        <v>27.45170302220356</v>
+      </c>
+      <c r="E85">
+        <v>5.848000000000004</v>
+      </c>
+      <c r="F85">
+        <v>21.248</v>
+      </c>
+      <c r="G85">
+        <v>0.877</v>
+      </c>
+      <c r="H85">
+        <v>10.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>6.62</v>
+      </c>
+      <c r="K85">
+        <v>1.91</v>
+      </c>
+      <c r="L85">
+        <v>4.71</v>
+      </c>
+      <c r="M85">
+        <v>1.136768</v>
+      </c>
+      <c r="N85">
+        <v>3.573232</v>
+      </c>
+      <c r="O85">
+        <v>0.82184336</v>
+      </c>
+      <c r="P85">
+        <v>2.75138864</v>
+      </c>
+      <c r="Q85">
+        <v>4.66138864</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4017382370726931</v>
+      </c>
+      <c r="T85">
+        <v>6.444955758546134</v>
+      </c>
+      <c r="U85">
+        <v>0.0535</v>
+      </c>
+      <c r="V85">
+        <v>0.23</v>
+      </c>
+      <c r="W85">
+        <v>0.041195</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>4.143325639004615</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1023359093115094</v>
+      </c>
+      <c r="C86">
+        <v>6.89013551779869</v>
+      </c>
+      <c r="D86">
+        <v>27.51713551779869</v>
+      </c>
+      <c r="E86">
+        <v>6.104000000000001</v>
+      </c>
+      <c r="F86">
+        <v>21.504</v>
+      </c>
+      <c r="G86">
+        <v>0.877</v>
+      </c>
+      <c r="H86">
+        <v>10.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>6.62</v>
+      </c>
+      <c r="K86">
+        <v>1.91</v>
+      </c>
+      <c r="L86">
+        <v>4.71</v>
+      </c>
+      <c r="M86">
+        <v>1.150464</v>
+      </c>
+      <c r="N86">
+        <v>3.559536</v>
+      </c>
+      <c r="O86">
+        <v>0.81869328</v>
+      </c>
+      <c r="P86">
+        <v>2.74084272</v>
+      </c>
+      <c r="Q86">
+        <v>4.65084272</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4233256831969339</v>
+      </c>
+      <c r="T86">
+        <v>6.828299592287364</v>
+      </c>
+      <c r="U86">
+        <v>0.0535</v>
+      </c>
+      <c r="V86">
+        <v>0.23</v>
+      </c>
+      <c r="W86">
+        <v>0.041195</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>4.094000333778371</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1021844683206611</v>
+      </c>
+      <c r="C87">
+        <v>6.699880681851223</v>
+      </c>
+      <c r="D87">
+        <v>27.58288068185123</v>
+      </c>
+      <c r="E87">
+        <v>6.360000000000001</v>
+      </c>
+      <c r="F87">
+        <v>21.76</v>
+      </c>
+      <c r="G87">
+        <v>0.877</v>
+      </c>
+      <c r="H87">
+        <v>10.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>6.62</v>
+      </c>
+      <c r="K87">
+        <v>1.91</v>
+      </c>
+      <c r="L87">
+        <v>4.71</v>
+      </c>
+      <c r="M87">
+        <v>1.16416</v>
+      </c>
+      <c r="N87">
+        <v>3.54584</v>
+      </c>
+      <c r="O87">
+        <v>0.8155432</v>
+      </c>
+      <c r="P87">
+        <v>2.7302968</v>
+      </c>
+      <c r="Q87">
+        <v>4.6402968</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4477914554710736</v>
+      </c>
+      <c r="T87">
+        <v>7.262755937194097</v>
+      </c>
+      <c r="U87">
+        <v>0.0535</v>
+      </c>
+      <c r="V87">
+        <v>0.23</v>
+      </c>
+      <c r="W87">
+        <v>0.041195</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>4.045835623969214</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1038209673298127</v>
+      </c>
+      <c r="C88">
+        <v>5.74965297717203</v>
+      </c>
+      <c r="D88">
+        <v>26.88865297717203</v>
+      </c>
+      <c r="E88">
+        <v>6.616000000000001</v>
+      </c>
+      <c r="F88">
+        <v>22.016</v>
+      </c>
+      <c r="G88">
+        <v>0.877</v>
+      </c>
+      <c r="H88">
+        <v>10.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>6.62</v>
+      </c>
+      <c r="K88">
+        <v>1.91</v>
+      </c>
+      <c r="L88">
+        <v>4.71</v>
+      </c>
+      <c r="M88">
+        <v>1.2372992</v>
+      </c>
+      <c r="N88">
+        <v>3.4727008</v>
+      </c>
+      <c r="O88">
+        <v>0.798721184</v>
+      </c>
+      <c r="P88">
+        <v>2.673979616</v>
+      </c>
+      <c r="Q88">
+        <v>4.583979616000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4757523380700904</v>
+      </c>
+      <c r="T88">
+        <v>7.759277474230361</v>
+      </c>
+      <c r="U88">
+        <v>0.0562</v>
+      </c>
+      <c r="V88">
+        <v>0.23</v>
+      </c>
+      <c r="W88">
+        <v>0.043274</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>3.806678287676902</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1036903163389643</v>
+      </c>
+      <c r="C89">
+        <v>5.54779093414691</v>
+      </c>
+      <c r="D89">
+        <v>26.94279093414691</v>
+      </c>
+      <c r="E89">
+        <v>6.872000000000002</v>
+      </c>
+      <c r="F89">
+        <v>22.272</v>
+      </c>
+      <c r="G89">
+        <v>0.877</v>
+      </c>
+      <c r="H89">
+        <v>10.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>6.62</v>
+      </c>
+      <c r="K89">
+        <v>1.91</v>
+      </c>
+      <c r="L89">
+        <v>4.71</v>
+      </c>
+      <c r="M89">
+        <v>1.2516864</v>
+      </c>
+      <c r="N89">
+        <v>3.4583136</v>
+      </c>
+      <c r="O89">
+        <v>0.7954121280000001</v>
+      </c>
+      <c r="P89">
+        <v>2.662901472</v>
+      </c>
+      <c r="Q89">
+        <v>4.572901472</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.50801489491511</v>
+      </c>
+      <c r="T89">
+        <v>8.332186940041437</v>
+      </c>
+      <c r="U89">
+        <v>0.0562</v>
+      </c>
+      <c r="V89">
+        <v>0.23</v>
+      </c>
+      <c r="W89">
+        <v>0.043274</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>3.76292336483004</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1035596653481159</v>
+      </c>
+      <c r="C90">
+        <v>5.346147335046219</v>
+      </c>
+      <c r="D90">
+        <v>26.99714733504622</v>
+      </c>
+      <c r="E90">
+        <v>7.128000000000002</v>
+      </c>
+      <c r="F90">
+        <v>22.528</v>
+      </c>
+      <c r="G90">
+        <v>0.877</v>
+      </c>
+      <c r="H90">
+        <v>10.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>6.62</v>
+      </c>
+      <c r="K90">
+        <v>1.91</v>
+      </c>
+      <c r="L90">
+        <v>4.71</v>
+      </c>
+      <c r="M90">
+        <v>1.2660736</v>
+      </c>
+      <c r="N90">
+        <v>3.4439264</v>
+      </c>
+      <c r="O90">
+        <v>0.792103072</v>
+      </c>
+      <c r="P90">
+        <v>2.651823328</v>
+      </c>
+      <c r="Q90">
+        <v>4.561823328</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5456545445676326</v>
+      </c>
+      <c r="T90">
+        <v>9.000581316821025</v>
+      </c>
+      <c r="U90">
+        <v>0.0562</v>
+      </c>
+      <c r="V90">
+        <v>0.23</v>
+      </c>
+      <c r="W90">
+        <v>0.043274</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>3.72016287204788</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1034290143572675</v>
+      </c>
+      <c r="C91">
+        <v>5.144723504657982</v>
+      </c>
+      <c r="D91">
+        <v>27.05172350465799</v>
+      </c>
+      <c r="E91">
+        <v>7.384000000000002</v>
+      </c>
+      <c r="F91">
+        <v>22.784</v>
+      </c>
+      <c r="G91">
+        <v>0.877</v>
+      </c>
+      <c r="H91">
+        <v>10.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>6.62</v>
+      </c>
+      <c r="K91">
+        <v>1.91</v>
+      </c>
+      <c r="L91">
+        <v>4.71</v>
+      </c>
+      <c r="M91">
+        <v>1.2804608</v>
+      </c>
+      <c r="N91">
+        <v>3.4295392</v>
+      </c>
+      <c r="O91">
+        <v>0.788794016</v>
+      </c>
+      <c r="P91">
+        <v>2.640745184</v>
+      </c>
+      <c r="Q91">
+        <v>4.550745184</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5901377668842505</v>
+      </c>
+      <c r="T91">
+        <v>9.790501943924175</v>
+      </c>
+      <c r="U91">
+        <v>0.0562</v>
+      </c>
+      <c r="V91">
+        <v>0.23</v>
+      </c>
+      <c r="W91">
+        <v>0.043274</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>3.678363289215882</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1032983633664191</v>
+      </c>
+      <c r="C92">
+        <v>4.943520778504475</v>
+      </c>
+      <c r="D92">
+        <v>27.10652077850448</v>
+      </c>
+      <c r="E92">
+        <v>7.640000000000002</v>
+      </c>
+      <c r="F92">
+        <v>23.04</v>
+      </c>
+      <c r="G92">
+        <v>0.877</v>
+      </c>
+      <c r="H92">
+        <v>10.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>6.62</v>
+      </c>
+      <c r="K92">
+        <v>1.91</v>
+      </c>
+      <c r="L92">
+        <v>4.71</v>
+      </c>
+      <c r="M92">
+        <v>1.294848</v>
+      </c>
+      <c r="N92">
+        <v>3.415152</v>
+      </c>
+      <c r="O92">
+        <v>0.78548496</v>
+      </c>
+      <c r="P92">
+        <v>2.62966704</v>
+      </c>
+      <c r="Q92">
+        <v>4.53966704</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6435176336641917</v>
+      </c>
+      <c r="T92">
+        <v>10.73840669644795</v>
+      </c>
+      <c r="U92">
+        <v>0.0562</v>
+      </c>
+      <c r="V92">
+        <v>0.23</v>
+      </c>
+      <c r="W92">
+        <v>0.043274</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>3.637492586002372</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1031677123755708</v>
+      </c>
+      <c r="C93">
+        <v>4.742540502951101</v>
+      </c>
+      <c r="D93">
+        <v>27.16154050295111</v>
+      </c>
+      <c r="E93">
+        <v>7.896000000000003</v>
+      </c>
+      <c r="F93">
+        <v>23.296</v>
+      </c>
+      <c r="G93">
+        <v>0.877</v>
+      </c>
+      <c r="H93">
+        <v>10.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>6.62</v>
+      </c>
+      <c r="K93">
+        <v>1.91</v>
+      </c>
+      <c r="L93">
+        <v>4.71</v>
+      </c>
+      <c r="M93">
+        <v>1.3092352</v>
+      </c>
+      <c r="N93">
+        <v>3.4007648</v>
+      </c>
+      <c r="O93">
+        <v>0.7821759039999999</v>
+      </c>
+      <c r="P93">
+        <v>2.618588896</v>
+      </c>
+      <c r="Q93">
+        <v>4.528588896</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7087596930618978</v>
+      </c>
+      <c r="T93">
+        <v>11.89695694953257</v>
+      </c>
+      <c r="U93">
+        <v>0.0562</v>
+      </c>
+      <c r="V93">
+        <v>0.23</v>
+      </c>
+      <c r="W93">
+        <v>0.043274</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>3.597520140002346</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1030370613847224</v>
+      </c>
+      <c r="C94">
+        <v>4.541784035316716</v>
+      </c>
+      <c r="D94">
+        <v>27.21678403531672</v>
+      </c>
+      <c r="E94">
+        <v>8.152000000000003</v>
+      </c>
+      <c r="F94">
+        <v>23.552</v>
+      </c>
+      <c r="G94">
+        <v>0.877</v>
+      </c>
+      <c r="H94">
+        <v>10.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>6.62</v>
+      </c>
+      <c r="K94">
+        <v>1.91</v>
+      </c>
+      <c r="L94">
+        <v>4.71</v>
+      </c>
+      <c r="M94">
+        <v>1.3236224</v>
+      </c>
+      <c r="N94">
+        <v>3.3863776</v>
+      </c>
+      <c r="O94">
+        <v>0.7788668480000001</v>
+      </c>
+      <c r="P94">
+        <v>2.607510752</v>
+      </c>
+      <c r="Q94">
+        <v>4.517510752</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7903122673090304</v>
+      </c>
+      <c r="T94">
+        <v>13.34514476588835</v>
+      </c>
+      <c r="U94">
+        <v>0.0562</v>
+      </c>
+      <c r="V94">
+        <v>0.23</v>
+      </c>
+      <c r="W94">
+        <v>0.043274</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>3.558416660219712</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.102906410393874</v>
+      </c>
+      <c r="C95">
+        <v>4.341252743985205</v>
+      </c>
+      <c r="D95">
+        <v>27.27225274398521</v>
+      </c>
+      <c r="E95">
+        <v>8.408000000000003</v>
+      </c>
+      <c r="F95">
+        <v>23.808</v>
+      </c>
+      <c r="G95">
+        <v>0.877</v>
+      </c>
+      <c r="H95">
+        <v>10.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>6.62</v>
+      </c>
+      <c r="K95">
+        <v>1.91</v>
+      </c>
+      <c r="L95">
+        <v>4.71</v>
+      </c>
+      <c r="M95">
+        <v>1.3380096</v>
+      </c>
+      <c r="N95">
+        <v>3.3719904</v>
+      </c>
+      <c r="O95">
+        <v>0.775557792</v>
+      </c>
+      <c r="P95">
+        <v>2.596432608</v>
+      </c>
+      <c r="Q95">
+        <v>4.506432608</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8951655770553437</v>
+      </c>
+      <c r="T95">
+        <v>15.20710052977435</v>
+      </c>
+      <c r="U95">
+        <v>0.0562</v>
+      </c>
+      <c r="V95">
+        <v>0.23</v>
+      </c>
+      <c r="W95">
+        <v>0.043274</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>3.520154115486166</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1061776194030256</v>
+      </c>
+      <c r="C96">
+        <v>2.761174516430934</v>
+      </c>
+      <c r="D96">
+        <v>25.94817451643094</v>
+      </c>
+      <c r="E96">
+        <v>8.664000000000003</v>
+      </c>
+      <c r="F96">
+        <v>24.064</v>
+      </c>
+      <c r="G96">
+        <v>0.877</v>
+      </c>
+      <c r="H96">
+        <v>10.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>6.62</v>
+      </c>
+      <c r="K96">
+        <v>1.91</v>
+      </c>
+      <c r="L96">
+        <v>4.71</v>
+      </c>
+      <c r="M96">
+        <v>1.4654976</v>
+      </c>
+      <c r="N96">
+        <v>3.2445024</v>
+      </c>
+      <c r="O96">
+        <v>0.746235552</v>
+      </c>
+      <c r="P96">
+        <v>2.498266848</v>
+      </c>
+      <c r="Q96">
+        <v>4.408266848</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.034969990050428</v>
+      </c>
+      <c r="T96">
+        <v>17.68970821495568</v>
+      </c>
+      <c r="U96">
+        <v>0.0609</v>
+      </c>
+      <c r="V96">
+        <v>0.23</v>
+      </c>
+      <c r="W96">
+        <v>0.046893</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>3.213925427104077</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1060831584121773</v>
+      </c>
+      <c r="C97">
+        <v>2.541603993485399</v>
+      </c>
+      <c r="D97">
+        <v>25.9846039934854</v>
+      </c>
+      <c r="E97">
+        <v>8.920000000000003</v>
+      </c>
+      <c r="F97">
+        <v>24.32</v>
+      </c>
+      <c r="G97">
+        <v>0.877</v>
+      </c>
+      <c r="H97">
+        <v>10.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>6.62</v>
+      </c>
+      <c r="K97">
+        <v>1.91</v>
+      </c>
+      <c r="L97">
+        <v>4.71</v>
+      </c>
+      <c r="M97">
+        <v>1.481088</v>
+      </c>
+      <c r="N97">
+        <v>3.228911999999999</v>
+      </c>
+      <c r="O97">
+        <v>0.7426497599999998</v>
+      </c>
+      <c r="P97">
+        <v>2.486262239999999</v>
+      </c>
+      <c r="Q97">
+        <v>4.39626224</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.230696168243547</v>
+      </c>
+      <c r="T97">
+        <v>21.16535897420955</v>
+      </c>
+      <c r="U97">
+        <v>0.0609</v>
+      </c>
+      <c r="V97">
+        <v>0.23</v>
+      </c>
+      <c r="W97">
+        <v>0.046893</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>3.180094633134559</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1059886974213289</v>
+      </c>
+      <c r="C98">
+        <v>2.322135903378456</v>
+      </c>
+      <c r="D98">
+        <v>26.02113590337846</v>
+      </c>
+      <c r="E98">
+        <v>9.176</v>
+      </c>
+      <c r="F98">
+        <v>24.576</v>
+      </c>
+      <c r="G98">
+        <v>0.877</v>
+      </c>
+      <c r="H98">
+        <v>10.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>6.62</v>
+      </c>
+      <c r="K98">
+        <v>1.91</v>
+      </c>
+      <c r="L98">
+        <v>4.71</v>
+      </c>
+      <c r="M98">
+        <v>1.4966784</v>
+      </c>
+      <c r="N98">
+        <v>3.2133216</v>
+      </c>
+      <c r="O98">
+        <v>0.739063968</v>
+      </c>
+      <c r="P98">
+        <v>2.474257632</v>
+      </c>
+      <c r="Q98">
+        <v>4.384257632</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.524285435533221</v>
+      </c>
+      <c r="T98">
+        <v>26.37883511309028</v>
+      </c>
+      <c r="U98">
+        <v>0.0609</v>
+      </c>
+      <c r="V98">
+        <v>0.23</v>
+      </c>
+      <c r="W98">
+        <v>0.046893</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>3.146968647372742</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1058942364304805</v>
+      </c>
+      <c r="C99">
+        <v>2.102770678751146</v>
+      </c>
+      <c r="D99">
+        <v>26.05777067875115</v>
+      </c>
+      <c r="E99">
+        <v>9.432</v>
+      </c>
+      <c r="F99">
+        <v>24.832</v>
+      </c>
+      <c r="G99">
+        <v>0.877</v>
+      </c>
+      <c r="H99">
+        <v>10.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>6.62</v>
+      </c>
+      <c r="K99">
+        <v>1.91</v>
+      </c>
+      <c r="L99">
+        <v>4.71</v>
+      </c>
+      <c r="M99">
+        <v>1.5122688</v>
+      </c>
+      <c r="N99">
+        <v>3.1977312</v>
+      </c>
+      <c r="O99">
+        <v>0.735478176</v>
+      </c>
+      <c r="P99">
+        <v>2.462253024</v>
+      </c>
+      <c r="Q99">
+        <v>4.372253024</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.013600881016016</v>
+      </c>
+      <c r="T99">
+        <v>35.06796201122492</v>
+      </c>
+      <c r="U99">
+        <v>0.0609</v>
+      </c>
+      <c r="V99">
+        <v>0.23</v>
+      </c>
+      <c r="W99">
+        <v>0.046893</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>3.114525671626631</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1057997754396321</v>
+      </c>
+      <c r="C100">
+        <v>1.883508754684438</v>
+      </c>
+      <c r="D100">
+        <v>26.09450875468444</v>
+      </c>
+      <c r="E100">
+        <v>9.688000000000001</v>
+      </c>
+      <c r="F100">
+        <v>25.088</v>
+      </c>
+      <c r="G100">
+        <v>0.877</v>
+      </c>
+      <c r="H100">
+        <v>10.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>6.62</v>
+      </c>
+      <c r="K100">
+        <v>1.91</v>
+      </c>
+      <c r="L100">
+        <v>4.71</v>
+      </c>
+      <c r="M100">
+        <v>1.5278592</v>
+      </c>
+      <c r="N100">
+        <v>3.1821408</v>
+      </c>
+      <c r="O100">
+        <v>0.731892384</v>
+      </c>
+      <c r="P100">
+        <v>2.450248416</v>
+      </c>
+      <c r="Q100">
+        <v>4.360248416</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.992231771981604</v>
+      </c>
+      <c r="T100">
+        <v>52.44621580749418</v>
+      </c>
+      <c r="U100">
+        <v>0.0609</v>
+      </c>
+      <c r="V100">
+        <v>0.23</v>
+      </c>
+      <c r="W100">
+        <v>0.046893</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>3.08274479742636</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1057053144487838</v>
+      </c>
+      <c r="C101">
+        <v>1.664350568716362</v>
+      </c>
+      <c r="D101">
+        <v>26.13135056871636</v>
+      </c>
+      <c r="E101">
+        <v>9.944000000000001</v>
+      </c>
+      <c r="F101">
+        <v>25.344</v>
+      </c>
+      <c r="G101">
+        <v>0.877</v>
+      </c>
+      <c r="H101">
+        <v>10.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>6.62</v>
+      </c>
+      <c r="K101">
+        <v>1.91</v>
+      </c>
+      <c r="L101">
+        <v>4.71</v>
+      </c>
+      <c r="M101">
+        <v>1.5434496</v>
+      </c>
+      <c r="N101">
+        <v>3.1665504</v>
+      </c>
+      <c r="O101">
+        <v>0.728306592</v>
+      </c>
+      <c r="P101">
+        <v>2.438243808</v>
+      </c>
+      <c r="Q101">
+        <v>4.348243807999999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.92812444487837</v>
+      </c>
+      <c r="T101">
+        <v>104.580977196302</v>
+      </c>
+      <c r="U101">
+        <v>0.0609</v>
+      </c>
+      <c r="V101">
+        <v>0.23</v>
+      </c>
+      <c r="W101">
+        <v>0.046893</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>3.051605961088719</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/israel/israel_software_entertainment.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_software_entertainment.xlsx
@@ -1382,7 +1382,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1519,22 +1519,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1333357133907838</v>
+        <v>0.133063691249985</v>
       </c>
       <c r="C2">
-        <v>29.98157121689425</v>
+        <v>29.72748219842409</v>
       </c>
       <c r="D2">
-        <v>27.97157121689425</v>
+        <v>28.02148219842409</v>
       </c>
       <c r="E2">
-        <v>-15.6</v>
+        <v>-15.296</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.304</v>
       </c>
       <c r="G2">
         <v>2.01</v>
@@ -1555,28 +1555,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0152912</v>
       </c>
       <c r="N2">
-        <v>11.17666666666667</v>
+        <v>11.16137546666667</v>
       </c>
       <c r="O2">
-        <v>2.570633333333333</v>
+        <v>2.567116357333333</v>
       </c>
       <c r="P2">
-        <v>8.606033333333333</v>
+        <v>8.594259109333333</v>
       </c>
       <c r="Q2">
-        <v>9.646033333333332</v>
+        <v>9.634259109333332</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1333357133907838</v>
+        <v>0.1340165467171566</v>
       </c>
       <c r="T2">
-        <v>1.354149646462541</v>
+        <v>1.364681921490583</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>730.9214886121865</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1601,22 +1601,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.133063691249985</v>
+        <v>0.1327916691091862</v>
       </c>
       <c r="C3">
-        <v>29.72748219842409</v>
+        <v>29.47357161533752</v>
       </c>
       <c r="D3">
-        <v>28.02148219842409</v>
+        <v>28.07157161533751</v>
       </c>
       <c r="E3">
-        <v>-15.296</v>
+        <v>-14.992</v>
       </c>
       <c r="F3">
-        <v>0.304</v>
+        <v>0.608</v>
       </c>
       <c r="G3">
         <v>2.01</v>
@@ -1637,28 +1637,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M3">
-        <v>0.0152912</v>
+        <v>0.0305824</v>
       </c>
       <c r="N3">
-        <v>11.16137546666667</v>
+        <v>11.14608426666667</v>
       </c>
       <c r="O3">
-        <v>2.567116357333333</v>
+        <v>2.563599381333333</v>
       </c>
       <c r="P3">
-        <v>8.594259109333333</v>
+        <v>8.582484885333333</v>
       </c>
       <c r="Q3">
-        <v>9.634259109333332</v>
+        <v>9.622484885333332</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1340165467171566</v>
+        <v>0.1347112746012104</v>
       </c>
       <c r="T3">
-        <v>1.364681921490583</v>
+        <v>1.375429140906952</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>730.9214886121865</v>
+        <v>365.4607443060933</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1683,22 +1683,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1327916691091862</v>
+        <v>0.1325196469683874</v>
       </c>
       <c r="C4">
-        <v>29.47357161533752</v>
+        <v>29.21984042622723</v>
       </c>
       <c r="D4">
-        <v>28.07157161533751</v>
+        <v>28.12184042622723</v>
       </c>
       <c r="E4">
-        <v>-14.992</v>
+        <v>-14.688</v>
       </c>
       <c r="F4">
-        <v>0.608</v>
+        <v>0.9119999999999999</v>
       </c>
       <c r="G4">
         <v>2.01</v>
@@ -1719,28 +1719,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M4">
-        <v>0.0305824</v>
+        <v>0.04587359999999999</v>
       </c>
       <c r="N4">
-        <v>11.14608426666667</v>
+        <v>11.13079306666667</v>
       </c>
       <c r="O4">
-        <v>2.563599381333333</v>
+        <v>2.560082405333333</v>
       </c>
       <c r="P4">
-        <v>8.582484885333333</v>
+        <v>8.570710661333333</v>
       </c>
       <c r="Q4">
-        <v>9.622484885333332</v>
+        <v>9.610710661333332</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1347112746012104</v>
+        <v>0.1354203267715334</v>
       </c>
       <c r="T4">
-        <v>1.375429140906952</v>
+        <v>1.386397952476236</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>365.4607443060933</v>
+        <v>243.6404962040622</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1765,22 +1765,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1325196469683874</v>
+        <v>0.1322476248275886</v>
       </c>
       <c r="C5">
-        <v>29.21984042622723</v>
+        <v>28.9662895965646</v>
       </c>
       <c r="D5">
-        <v>28.12184042622723</v>
+        <v>28.1722895965646</v>
       </c>
       <c r="E5">
-        <v>-14.688</v>
+        <v>-14.384</v>
       </c>
       <c r="F5">
-        <v>0.9119999999999999</v>
+        <v>1.216</v>
       </c>
       <c r="G5">
         <v>2.01</v>
@@ -1801,28 +1801,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M5">
-        <v>0.04587359999999999</v>
+        <v>0.0611648</v>
       </c>
       <c r="N5">
-        <v>11.13079306666667</v>
+        <v>11.11550186666667</v>
       </c>
       <c r="O5">
-        <v>2.560082405333333</v>
+        <v>2.556565429333333</v>
       </c>
       <c r="P5">
-        <v>8.570710661333333</v>
+        <v>8.558936437333333</v>
       </c>
       <c r="Q5">
-        <v>9.610710661333332</v>
+        <v>9.598936437333332</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1354203267715334</v>
+        <v>0.1361441508620715</v>
       </c>
       <c r="T5">
-        <v>1.386397952476236</v>
+        <v>1.397595280953214</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>243.6404962040622</v>
+        <v>182.7303721530466</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1322476248275886</v>
+        <v>0.1319756026867898</v>
       </c>
       <c r="C6">
-        <v>28.9662895965646</v>
+        <v>28.71292009876148</v>
       </c>
       <c r="D6">
-        <v>28.1722895965646</v>
+        <v>28.22292009876148</v>
       </c>
       <c r="E6">
-        <v>-14.384</v>
+        <v>-14.08</v>
       </c>
       <c r="F6">
-        <v>1.216</v>
+        <v>1.52</v>
       </c>
       <c r="G6">
         <v>2.01</v>
@@ -1883,28 +1883,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M6">
-        <v>0.0611648</v>
+        <v>0.076456</v>
       </c>
       <c r="N6">
-        <v>11.11550186666667</v>
+        <v>11.10021066666667</v>
       </c>
       <c r="O6">
-        <v>2.556565429333333</v>
+        <v>2.553048453333333</v>
       </c>
       <c r="P6">
-        <v>8.558936437333333</v>
+        <v>8.547162213333333</v>
       </c>
       <c r="Q6">
-        <v>9.598936437333332</v>
+        <v>9.587162213333333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1361441508620715</v>
+        <v>0.1368832133545156</v>
       </c>
       <c r="T6">
-        <v>1.397595280953214</v>
+        <v>1.409028342661286</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>182.7303721530466</v>
+        <v>146.1842977224373</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1929,22 +1929,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1319756026867898</v>
+        <v>0.131703580545991</v>
       </c>
       <c r="C7">
-        <v>28.71292009876148</v>
+        <v>28.45973291223268</v>
       </c>
       <c r="D7">
-        <v>28.22292009876148</v>
+        <v>28.27373291223268</v>
       </c>
       <c r="E7">
-        <v>-14.08</v>
+        <v>-13.776</v>
       </c>
       <c r="F7">
-        <v>1.52</v>
+        <v>1.824</v>
       </c>
       <c r="G7">
         <v>2.01</v>
@@ -1965,28 +1965,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M7">
-        <v>0.076456</v>
+        <v>0.0917472</v>
       </c>
       <c r="N7">
-        <v>11.10021066666667</v>
+        <v>11.08491946666667</v>
       </c>
       <c r="O7">
-        <v>2.553048453333333</v>
+        <v>2.549531477333333</v>
       </c>
       <c r="P7">
-        <v>8.547162213333333</v>
+        <v>8.535387989333332</v>
       </c>
       <c r="Q7">
-        <v>9.587162213333333</v>
+        <v>9.575387989333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1368832133545156</v>
+        <v>0.1376380005808415</v>
       </c>
       <c r="T7">
-        <v>1.409028342661286</v>
+        <v>1.420704661001444</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>146.1842977224373</v>
+        <v>121.8202481020311</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2011,22 +2011,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.131703580545991</v>
+        <v>0.1314315584051922</v>
       </c>
       <c r="C8">
-        <v>28.45973291223269</v>
+        <v>28.20672902345912</v>
       </c>
       <c r="D8">
-        <v>28.27373291223269</v>
+        <v>28.32472902345912</v>
       </c>
       <c r="E8">
-        <v>-13.776</v>
+        <v>-13.472</v>
       </c>
       <c r="F8">
-        <v>1.824</v>
+        <v>2.128</v>
       </c>
       <c r="G8">
         <v>2.01</v>
@@ -2047,28 +2047,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M8">
-        <v>0.09174719999999999</v>
+        <v>0.1070384</v>
       </c>
       <c r="N8">
-        <v>11.08491946666667</v>
+        <v>11.06962826666667</v>
       </c>
       <c r="O8">
-        <v>2.549531477333333</v>
+        <v>2.546014501333333</v>
       </c>
       <c r="P8">
-        <v>8.535387989333332</v>
+        <v>8.523613765333332</v>
       </c>
       <c r="Q8">
-        <v>9.575387989333333</v>
+        <v>9.563613765333333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1376380005808415</v>
+        <v>0.1384090197905292</v>
       </c>
       <c r="T8">
-        <v>1.420704661001444</v>
+        <v>1.432632082961821</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>121.8202481020311</v>
+        <v>104.4173555160267</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2093,22 +2093,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1314315584051922</v>
+        <v>0.1311595362643934</v>
       </c>
       <c r="C9">
-        <v>28.20672902345912</v>
+        <v>27.95390942605168</v>
       </c>
       <c r="D9">
-        <v>28.32472902345912</v>
+        <v>28.37590942605167</v>
       </c>
       <c r="E9">
-        <v>-13.472</v>
+        <v>-13.168</v>
       </c>
       <c r="F9">
-        <v>2.128</v>
+        <v>2.432</v>
       </c>
       <c r="G9">
         <v>2.01</v>
@@ -2129,28 +2129,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M9">
-        <v>0.1070384</v>
+        <v>0.1223296</v>
       </c>
       <c r="N9">
-        <v>11.06962826666667</v>
+        <v>11.05433706666667</v>
       </c>
       <c r="O9">
-        <v>2.546014501333333</v>
+        <v>2.542497525333333</v>
       </c>
       <c r="P9">
-        <v>8.523613765333332</v>
+        <v>8.511839541333332</v>
       </c>
       <c r="Q9">
-        <v>9.563613765333333</v>
+        <v>9.551839541333333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1384090197905292</v>
+        <v>0.1391968002873841</v>
       </c>
       <c r="T9">
-        <v>1.432632082961821</v>
+        <v>1.444818796703945</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>104.4173555160266</v>
+        <v>91.36518607652332</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2175,22 +2175,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1311595362643934</v>
+        <v>0.1308875141235946</v>
       </c>
       <c r="C10">
-        <v>27.95390942605168</v>
+        <v>27.7012751208157</v>
       </c>
       <c r="D10">
-        <v>28.37590942605167</v>
+        <v>28.4272751208157</v>
       </c>
       <c r="E10">
-        <v>-13.168</v>
+        <v>-12.864</v>
       </c>
       <c r="F10">
-        <v>2.432</v>
+        <v>2.736</v>
       </c>
       <c r="G10">
         <v>2.01</v>
@@ -2211,28 +2211,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M10">
-        <v>0.1223296</v>
+        <v>0.1376208</v>
       </c>
       <c r="N10">
-        <v>11.05433706666667</v>
+        <v>11.03904586666667</v>
       </c>
       <c r="O10">
-        <v>2.542497525333333</v>
+        <v>2.538980549333333</v>
       </c>
       <c r="P10">
-        <v>8.511839541333332</v>
+        <v>8.500065317333332</v>
       </c>
       <c r="Q10">
-        <v>9.551839541333333</v>
+        <v>9.540065317333333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1391968002873841</v>
+        <v>0.1400018946413127</v>
       </c>
       <c r="T10">
-        <v>1.444818796703945</v>
+        <v>1.457273350308534</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>91.36518607652332</v>
+        <v>81.21349873468739</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2257,22 +2257,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1308875141235946</v>
+        <v>0.1306154919827958</v>
       </c>
       <c r="C11">
-        <v>27.7012751208157</v>
+        <v>27.44882711581626</v>
       </c>
       <c r="D11">
-        <v>28.4272751208157</v>
+        <v>28.47882711581626</v>
       </c>
       <c r="E11">
-        <v>-12.864</v>
+        <v>-12.56</v>
       </c>
       <c r="F11">
-        <v>2.736</v>
+        <v>3.04</v>
       </c>
       <c r="G11">
         <v>2.01</v>
@@ -2293,28 +2293,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M11">
-        <v>0.1376208</v>
+        <v>0.152912</v>
       </c>
       <c r="N11">
-        <v>11.03904586666667</v>
+        <v>11.02375466666667</v>
       </c>
       <c r="O11">
-        <v>2.538980549333333</v>
+        <v>2.535463573333333</v>
       </c>
       <c r="P11">
-        <v>8.500065317333332</v>
+        <v>8.488291093333332</v>
       </c>
       <c r="Q11">
-        <v>9.540065317333333</v>
+        <v>9.528291093333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1400018946413127</v>
+        <v>0.1408248799808842</v>
       </c>
       <c r="T11">
-        <v>1.457273350308534</v>
+        <v>1.470004671771002</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>81.21349873468739</v>
+        <v>73.09214886121866</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2339,22 +2339,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1306154919827958</v>
+        <v>0.130343469841997</v>
       </c>
       <c r="C12">
-        <v>27.44882711581626</v>
+        <v>27.1965664264441</v>
       </c>
       <c r="D12">
-        <v>28.47882711581626</v>
+        <v>28.5305664264441</v>
       </c>
       <c r="E12">
-        <v>-12.56</v>
+        <v>-12.256</v>
       </c>
       <c r="F12">
-        <v>3.04</v>
+        <v>3.344</v>
       </c>
       <c r="G12">
         <v>2.01</v>
@@ -2375,28 +2375,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M12">
-        <v>0.152912</v>
+        <v>0.1682032</v>
       </c>
       <c r="N12">
-        <v>11.02375466666667</v>
+        <v>11.00846346666667</v>
       </c>
       <c r="O12">
-        <v>2.535463573333333</v>
+        <v>2.531946597333333</v>
       </c>
       <c r="P12">
-        <v>8.488291093333332</v>
+        <v>8.476516869333333</v>
       </c>
       <c r="Q12">
-        <v>9.528291093333333</v>
+        <v>9.516516869333334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1408248799808842</v>
+        <v>0.1416663593730303</v>
       </c>
       <c r="T12">
-        <v>1.470004671771002</v>
+        <v>1.483022090344987</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>73.09214886121865</v>
+        <v>66.44740805565331</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2421,22 +2421,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.130343469841997</v>
+        <v>0.1300714477011982</v>
       </c>
       <c r="C13">
-        <v>27.1965664264441</v>
+        <v>26.94449407548232</v>
       </c>
       <c r="D13">
-        <v>28.5305664264441</v>
+        <v>28.58249407548232</v>
       </c>
       <c r="E13">
-        <v>-12.256</v>
+        <v>-11.952</v>
       </c>
       <c r="F13">
-        <v>3.344</v>
+        <v>3.648</v>
       </c>
       <c r="G13">
         <v>2.01</v>
@@ -2457,28 +2457,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M13">
-        <v>0.1682032</v>
+        <v>0.1834944</v>
       </c>
       <c r="N13">
-        <v>11.00846346666667</v>
+        <v>10.99317226666667</v>
       </c>
       <c r="O13">
-        <v>2.531946597333333</v>
+        <v>2.528429621333333</v>
       </c>
       <c r="P13">
-        <v>8.476516869333333</v>
+        <v>8.464742645333331</v>
       </c>
       <c r="Q13">
-        <v>9.516516869333334</v>
+        <v>9.50474264533333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1416663593730303</v>
+        <v>0.1425269632968161</v>
       </c>
       <c r="T13">
-        <v>1.483022090344987</v>
+        <v>1.496335359341108</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>66.44740805565331</v>
+        <v>60.91012405101554</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2503,22 +2503,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1300714477011982</v>
+        <v>0.1297994255603994</v>
       </c>
       <c r="C14">
-        <v>26.94449407548232</v>
+        <v>26.6926110931737</v>
       </c>
       <c r="D14">
-        <v>28.58249407548232</v>
+        <v>28.6346110931737</v>
       </c>
       <c r="E14">
-        <v>-11.952</v>
+        <v>-11.648</v>
       </c>
       <c r="F14">
-        <v>3.648</v>
+        <v>3.952</v>
       </c>
       <c r="G14">
         <v>2.01</v>
@@ -2539,28 +2539,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M14">
-        <v>0.1834944</v>
+        <v>0.1987856</v>
       </c>
       <c r="N14">
-        <v>10.99317226666667</v>
+        <v>10.97788106666667</v>
       </c>
       <c r="O14">
-        <v>2.528429621333333</v>
+        <v>2.524912645333333</v>
       </c>
       <c r="P14">
-        <v>8.464742645333331</v>
+        <v>8.452968421333331</v>
       </c>
       <c r="Q14">
-        <v>9.50474264533333</v>
+        <v>9.49296842133333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1425269632968161</v>
+        <v>0.1434073512188499</v>
       </c>
       <c r="T14">
-        <v>1.496335359341108</v>
+        <v>1.509954680498058</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>60.91012405101554</v>
+        <v>56.22472989324512</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2585,22 +2585,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1297994255603994</v>
+        <v>0.1295274034196006</v>
       </c>
       <c r="C15">
-        <v>26.6926110931737</v>
+        <v>26.44091851728891</v>
       </c>
       <c r="D15">
-        <v>28.6346110931737</v>
+        <v>28.68691851728892</v>
       </c>
       <c r="E15">
-        <v>-11.648</v>
+        <v>-11.344</v>
       </c>
       <c r="F15">
-        <v>3.952</v>
+        <v>4.256</v>
       </c>
       <c r="G15">
         <v>2.01</v>
@@ -2621,28 +2621,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M15">
-        <v>0.1987856</v>
+        <v>0.2140768</v>
       </c>
       <c r="N15">
-        <v>10.97788106666667</v>
+        <v>10.96258986666667</v>
       </c>
       <c r="O15">
-        <v>2.524912645333333</v>
+        <v>2.521395669333333</v>
       </c>
       <c r="P15">
-        <v>8.452968421333331</v>
+        <v>8.441194197333331</v>
       </c>
       <c r="Q15">
-        <v>9.49296842133333</v>
+        <v>9.48119419733333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1434073512188499</v>
+        <v>0.1443082132786053</v>
       </c>
       <c r="T15">
-        <v>1.509954680498058</v>
+        <v>1.523890730054008</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>56.22472989324512</v>
+        <v>52.20867775801332</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2667,22 +2667,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1295274034196006</v>
+        <v>0.1292553812788018</v>
       </c>
       <c r="C16">
-        <v>26.44091851728891</v>
+        <v>26.18941739319536</v>
       </c>
       <c r="D16">
-        <v>28.68691851728892</v>
+        <v>28.73941739319536</v>
       </c>
       <c r="E16">
-        <v>-11.344</v>
+        <v>-11.04</v>
       </c>
       <c r="F16">
-        <v>4.256</v>
+        <v>4.56</v>
       </c>
       <c r="G16">
         <v>2.01</v>
@@ -2703,28 +2703,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M16">
-        <v>0.2140768</v>
+        <v>0.229368</v>
       </c>
       <c r="N16">
-        <v>10.96258986666667</v>
+        <v>10.94729866666666</v>
       </c>
       <c r="O16">
-        <v>2.521395669333333</v>
+        <v>2.517878693333333</v>
       </c>
       <c r="P16">
-        <v>8.441194197333331</v>
+        <v>8.429419973333331</v>
       </c>
       <c r="Q16">
-        <v>9.48119419733333</v>
+        <v>9.469419973333331</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1443082132786053</v>
+        <v>0.145230272092708</v>
       </c>
       <c r="T16">
-        <v>1.523890730054008</v>
+        <v>1.538154686658333</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>52.20867775801332</v>
+        <v>48.72809924081243</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2749,22 +2749,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1292553812788018</v>
+        <v>0.128983359138003</v>
       </c>
       <c r="C17">
-        <v>26.18941739319536</v>
+        <v>25.93810877392685</v>
       </c>
       <c r="D17">
-        <v>28.73941739319536</v>
+        <v>28.79210877392685</v>
       </c>
       <c r="E17">
-        <v>-11.04</v>
+        <v>-10.736</v>
       </c>
       <c r="F17">
-        <v>4.56</v>
+        <v>4.864</v>
       </c>
       <c r="G17">
         <v>2.01</v>
@@ -2785,28 +2785,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M17">
-        <v>0.229368</v>
+        <v>0.2446592</v>
       </c>
       <c r="N17">
-        <v>10.94729866666667</v>
+        <v>10.93200746666667</v>
       </c>
       <c r="O17">
-        <v>2.517878693333333</v>
+        <v>2.514361717333333</v>
       </c>
       <c r="P17">
-        <v>8.429419973333333</v>
+        <v>8.417645749333333</v>
       </c>
       <c r="Q17">
-        <v>9.469419973333334</v>
+        <v>9.457645749333334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.145230272092708</v>
+        <v>0.1461742846880988</v>
       </c>
       <c r="T17">
-        <v>1.538154686658333</v>
+        <v>1.552758261277047</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>48.72809924081244</v>
+        <v>45.68259303826166</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2831,22 +2831,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.128983359138003</v>
+        <v>0.1287113369972042</v>
       </c>
       <c r="C18">
-        <v>25.93810877392685</v>
+        <v>25.68699372025394</v>
       </c>
       <c r="D18">
-        <v>28.79210877392685</v>
+        <v>28.84499372025394</v>
       </c>
       <c r="E18">
-        <v>-10.736</v>
+        <v>-10.432</v>
       </c>
       <c r="F18">
-        <v>4.864</v>
+        <v>5.168</v>
       </c>
       <c r="G18">
         <v>2.01</v>
@@ -2867,28 +2867,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M18">
-        <v>0.2446592</v>
+        <v>0.2599504</v>
       </c>
       <c r="N18">
-        <v>10.93200746666667</v>
+        <v>10.91671626666667</v>
       </c>
       <c r="O18">
-        <v>2.514361717333333</v>
+        <v>2.510844741333333</v>
       </c>
       <c r="P18">
-        <v>8.417645749333333</v>
+        <v>8.405871525333334</v>
       </c>
       <c r="Q18">
-        <v>9.457645749333334</v>
+        <v>9.445871525333335</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1461742846880988</v>
+        <v>0.1471410445749448</v>
       </c>
       <c r="T18">
-        <v>1.552758261277047</v>
+        <v>1.567713729260067</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>45.68259303826166</v>
+        <v>42.9953816830698</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1287113369972042</v>
+        <v>0.1284393148564054</v>
       </c>
       <c r="C19">
-        <v>25.68699372025394</v>
+        <v>25.43607330075519</v>
       </c>
       <c r="D19">
-        <v>28.84499372025394</v>
+        <v>28.89807330075519</v>
       </c>
       <c r="E19">
-        <v>-10.432</v>
+        <v>-10.128</v>
       </c>
       <c r="F19">
-        <v>5.168</v>
+        <v>5.472</v>
       </c>
       <c r="G19">
         <v>2.01</v>
@@ -2949,28 +2949,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M19">
-        <v>0.2599504</v>
+        <v>0.2752416</v>
       </c>
       <c r="N19">
-        <v>10.91671626666667</v>
+        <v>10.90142506666667</v>
       </c>
       <c r="O19">
-        <v>2.510844741333333</v>
+        <v>2.507327765333333</v>
       </c>
       <c r="P19">
-        <v>8.405871525333334</v>
+        <v>8.394097301333334</v>
       </c>
       <c r="Q19">
-        <v>9.445871525333335</v>
+        <v>9.434097301333335</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1471410445749448</v>
+        <v>0.148131383971226</v>
       </c>
       <c r="T19">
-        <v>1.567713729260067</v>
+        <v>1.583033964754867</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>42.9953816830698</v>
+        <v>40.60674936734369</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2995,22 +2995,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1284393148564054</v>
+        <v>0.1281672927156066</v>
       </c>
       <c r="C20">
-        <v>25.43607330075519</v>
+        <v>25.18534859188913</v>
       </c>
       <c r="D20">
-        <v>28.89807330075519</v>
+        <v>28.95134859188913</v>
       </c>
       <c r="E20">
-        <v>-10.128</v>
+        <v>-9.824</v>
       </c>
       <c r="F20">
-        <v>5.472</v>
+        <v>5.776</v>
       </c>
       <c r="G20">
         <v>2.01</v>
@@ -3031,28 +3031,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M20">
-        <v>0.2752416</v>
+        <v>0.2905328</v>
       </c>
       <c r="N20">
-        <v>10.90142506666667</v>
+        <v>10.88613386666667</v>
       </c>
       <c r="O20">
-        <v>2.507327765333333</v>
+        <v>2.503810789333333</v>
       </c>
       <c r="P20">
-        <v>8.394097301333334</v>
+        <v>8.382323077333332</v>
       </c>
       <c r="Q20">
-        <v>9.434097301333335</v>
+        <v>9.422323077333331</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.148131383971226</v>
+        <v>0.1491461761921069</v>
       </c>
       <c r="T20">
-        <v>1.583033964754867</v>
+        <v>1.598732477669293</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>40.6067493673437</v>
+        <v>38.46955203222034</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3077,22 +3077,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1281672927156066</v>
+        <v>0.1278952705748078</v>
       </c>
       <c r="C21">
-        <v>25.18534859188913</v>
+        <v>24.93482067806699</v>
       </c>
       <c r="D21">
-        <v>28.95134859188913</v>
+        <v>29.00482067806699</v>
       </c>
       <c r="E21">
-        <v>-9.824</v>
+        <v>-9.52</v>
       </c>
       <c r="F21">
-        <v>5.776</v>
+        <v>6.08</v>
       </c>
       <c r="G21">
         <v>2.01</v>
@@ -3113,28 +3113,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M21">
-        <v>0.2905328</v>
+        <v>0.305824</v>
       </c>
       <c r="N21">
-        <v>10.88613386666667</v>
+        <v>10.87084266666667</v>
       </c>
       <c r="O21">
-        <v>2.503810789333333</v>
+        <v>2.500293813333333</v>
       </c>
       <c r="P21">
-        <v>8.382323077333332</v>
+        <v>8.370548853333332</v>
       </c>
       <c r="Q21">
-        <v>9.422323077333331</v>
+        <v>9.410548853333331</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1491461761921069</v>
+        <v>0.1501863382185097</v>
       </c>
       <c r="T21">
-        <v>1.598732477669293</v>
+        <v>1.61482345340658</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>38.46955203222034</v>
+        <v>36.54607443060933</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3159,22 +3159,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1278952705748078</v>
+        <v>0.127623248434009</v>
       </c>
       <c r="C22">
-        <v>24.93482067806699</v>
+        <v>24.68449065172627</v>
       </c>
       <c r="D22">
-        <v>29.00482067806699</v>
+        <v>29.05849065172627</v>
       </c>
       <c r="E22">
-        <v>-9.52</v>
+        <v>-9.215999999999999</v>
       </c>
       <c r="F22">
-        <v>6.08</v>
+        <v>6.384</v>
       </c>
       <c r="G22">
         <v>2.01</v>
@@ -3195,28 +3195,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M22">
-        <v>0.305824</v>
+        <v>0.3211152</v>
       </c>
       <c r="N22">
-        <v>10.87084266666667</v>
+        <v>10.85555146666667</v>
       </c>
       <c r="O22">
-        <v>2.500293813333333</v>
+        <v>2.496776837333333</v>
       </c>
       <c r="P22">
-        <v>8.370548853333332</v>
+        <v>8.358774629333332</v>
       </c>
       <c r="Q22">
-        <v>9.410548853333331</v>
+        <v>9.398774629333332</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1501863382185097</v>
+        <v>0.1512528334607708</v>
       </c>
       <c r="T22">
-        <v>1.61482345340658</v>
+        <v>1.631321795618228</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>36.54607443060933</v>
+        <v>34.80578517200888</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3241,22 +3241,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.127623248434009</v>
+        <v>0.1273512262932102</v>
       </c>
       <c r="C23">
-        <v>24.68449065172627</v>
+        <v>24.4343596134052</v>
       </c>
       <c r="D23">
-        <v>29.05849065172627</v>
+        <v>29.1123596134052</v>
       </c>
       <c r="E23">
-        <v>-9.216000000000001</v>
+        <v>-8.911999999999999</v>
       </c>
       <c r="F23">
-        <v>6.383999999999999</v>
+        <v>6.688</v>
       </c>
       <c r="G23">
         <v>2.01</v>
@@ -3277,28 +3277,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M23">
-        <v>0.3211151999999999</v>
+        <v>0.3364064</v>
       </c>
       <c r="N23">
-        <v>10.85555146666667</v>
+        <v>10.84026026666667</v>
       </c>
       <c r="O23">
-        <v>2.496776837333333</v>
+        <v>2.493259861333333</v>
       </c>
       <c r="P23">
-        <v>8.358774629333332</v>
+        <v>8.347000405333333</v>
       </c>
       <c r="Q23">
-        <v>9.398774629333332</v>
+        <v>9.387000405333332</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1512528334607708</v>
+        <v>0.1523466747348848</v>
       </c>
       <c r="T23">
-        <v>1.631321795618228</v>
+        <v>1.648243172245559</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>34.80578517200889</v>
+        <v>33.22370402782666</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3323,22 +3323,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1273512262932102</v>
+        <v>0.1270792041524114</v>
       </c>
       <c r="C24">
-        <v>24.4343596134052</v>
+        <v>24.18442867181791</v>
       </c>
       <c r="D24">
-        <v>29.1123596134052</v>
+        <v>29.16642867181791</v>
       </c>
       <c r="E24">
-        <v>-8.911999999999999</v>
+        <v>-8.608000000000001</v>
       </c>
       <c r="F24">
-        <v>6.688</v>
+        <v>6.992</v>
       </c>
       <c r="G24">
         <v>2.01</v>
@@ -3359,28 +3359,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M24">
-        <v>0.3364064</v>
+        <v>0.3516976</v>
       </c>
       <c r="N24">
-        <v>10.84026026666667</v>
+        <v>10.82496906666667</v>
       </c>
       <c r="O24">
-        <v>2.493259861333333</v>
+        <v>2.489742885333333</v>
       </c>
       <c r="P24">
-        <v>8.347000405333333</v>
+        <v>8.335226181333333</v>
       </c>
       <c r="Q24">
-        <v>9.387000405333332</v>
+        <v>9.375226181333332</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1523466747348848</v>
+        <v>0.1534689274706641</v>
       </c>
       <c r="T24">
-        <v>1.648243172245559</v>
+        <v>1.665604065148925</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>33.22370402782666</v>
+        <v>31.77919515705159</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3405,22 +3405,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1270792041524114</v>
+        <v>0.1268071820116126</v>
       </c>
       <c r="C25">
-        <v>24.18442867181791</v>
+        <v>23.93469894393052</v>
       </c>
       <c r="D25">
-        <v>29.16642867181791</v>
+        <v>29.22069894393052</v>
       </c>
       <c r="E25">
-        <v>-8.608000000000001</v>
+        <v>-8.303999999999998</v>
       </c>
       <c r="F25">
-        <v>6.992</v>
+        <v>7.296</v>
       </c>
       <c r="G25">
         <v>2.01</v>
@@ -3441,28 +3441,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M25">
-        <v>0.3516976</v>
+        <v>0.3669888</v>
       </c>
       <c r="N25">
-        <v>10.82496906666667</v>
+        <v>10.80967786666667</v>
       </c>
       <c r="O25">
-        <v>2.489742885333333</v>
+        <v>2.486225909333333</v>
       </c>
       <c r="P25">
-        <v>8.335226181333333</v>
+        <v>8.323451957333333</v>
       </c>
       <c r="Q25">
-        <v>9.375226181333332</v>
+        <v>9.363451957333332</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1534689274706641</v>
+        <v>0.1546207131731744</v>
       </c>
       <c r="T25">
-        <v>1.665604065148925</v>
+        <v>1.683421823655011</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>31.77919515705159</v>
+        <v>30.45506202550777</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3487,22 +3487,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1268071820116126</v>
+        <v>0.1265351598708137</v>
       </c>
       <c r="C26">
-        <v>23.93469894393052</v>
+        <v>23.68517155503804</v>
       </c>
       <c r="D26">
-        <v>29.22069894393052</v>
+        <v>29.27517155503804</v>
       </c>
       <c r="E26">
-        <v>-8.304</v>
+        <v>-8</v>
       </c>
       <c r="F26">
-        <v>7.295999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="G26">
         <v>2.01</v>
@@ -3523,28 +3523,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M26">
-        <v>0.3669887999999999</v>
+        <v>0.38228</v>
       </c>
       <c r="N26">
-        <v>10.80967786666667</v>
+        <v>10.79438666666667</v>
       </c>
       <c r="O26">
-        <v>2.486225909333333</v>
+        <v>2.482708933333333</v>
       </c>
       <c r="P26">
-        <v>8.323451957333333</v>
+        <v>8.311677733333333</v>
       </c>
       <c r="Q26">
-        <v>9.363451957333332</v>
+        <v>9.351677733333332</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1546207131731744</v>
+        <v>0.155803213161085</v>
       </c>
       <c r="T26">
-        <v>1.683421823655011</v>
+        <v>1.701714722387926</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>30.45506202550778</v>
+        <v>29.23685954448746</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3569,22 +3569,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1265351598708137</v>
+        <v>0.126263137730015</v>
       </c>
       <c r="C27">
-        <v>23.68517155503804</v>
+        <v>23.43584763884217</v>
       </c>
       <c r="D27">
-        <v>29.27517155503804</v>
+        <v>29.32984763884216</v>
       </c>
       <c r="E27">
-        <v>-8</v>
+        <v>-7.696</v>
       </c>
       <c r="F27">
-        <v>7.6</v>
+        <v>7.904</v>
       </c>
       <c r="G27">
         <v>2.01</v>
@@ -3605,28 +3605,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M27">
-        <v>0.38228</v>
+        <v>0.3975712</v>
       </c>
       <c r="N27">
-        <v>10.79438666666667</v>
+        <v>10.77909546666667</v>
       </c>
       <c r="O27">
-        <v>2.482708933333333</v>
+        <v>2.479191957333333</v>
       </c>
       <c r="P27">
-        <v>8.311677733333333</v>
+        <v>8.299903509333333</v>
       </c>
       <c r="Q27">
-        <v>9.351677733333332</v>
+        <v>9.339903509333332</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.155803213161085</v>
+        <v>0.1570176726081283</v>
       </c>
       <c r="T27">
-        <v>1.701714722387926</v>
+        <v>1.720502023789298</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>29.23685954448746</v>
+        <v>28.11236494662256</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3651,22 +3651,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.126263137730015</v>
+        <v>0.1259911155892162</v>
       </c>
       <c r="C28">
-        <v>23.43584763884217</v>
+        <v>23.18672833752992</v>
       </c>
       <c r="D28">
-        <v>29.32984763884216</v>
+        <v>29.38472833752992</v>
       </c>
       <c r="E28">
-        <v>-7.696</v>
+        <v>-7.391999999999999</v>
       </c>
       <c r="F28">
-        <v>7.904</v>
+        <v>8.208</v>
       </c>
       <c r="G28">
         <v>2.01</v>
@@ -3687,28 +3687,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M28">
-        <v>0.3975712</v>
+        <v>0.4128624</v>
       </c>
       <c r="N28">
-        <v>10.77909546666667</v>
+        <v>10.76380426666667</v>
       </c>
       <c r="O28">
-        <v>2.479191957333333</v>
+        <v>2.475674981333333</v>
       </c>
       <c r="P28">
-        <v>8.299903509333333</v>
+        <v>8.288129285333333</v>
       </c>
       <c r="Q28">
-        <v>9.339903509333332</v>
+        <v>9.328129285333333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1570176726081283</v>
+        <v>0.1582654049167345</v>
       </c>
       <c r="T28">
-        <v>1.720502023789298</v>
+        <v>1.739804045777009</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>28.11236494662256</v>
+        <v>27.0711662448958</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3733,22 +3733,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1259911155892162</v>
+        <v>0.1257190934484174</v>
       </c>
       <c r="C29">
-        <v>23.18672833752992</v>
+        <v>22.93781480185318</v>
       </c>
       <c r="D29">
-        <v>29.38472833752992</v>
+        <v>29.43981480185318</v>
       </c>
       <c r="E29">
-        <v>-7.391999999999999</v>
+        <v>-7.087999999999999</v>
       </c>
       <c r="F29">
-        <v>8.208</v>
+        <v>8.512</v>
       </c>
       <c r="G29">
         <v>2.01</v>
@@ -3769,28 +3769,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M29">
-        <v>0.4128624</v>
+        <v>0.4281536</v>
       </c>
       <c r="N29">
-        <v>10.76380426666667</v>
+        <v>10.74851306666667</v>
       </c>
       <c r="O29">
-        <v>2.475674981333333</v>
+        <v>2.472158005333333</v>
       </c>
       <c r="P29">
-        <v>8.288129285333333</v>
+        <v>8.276355061333334</v>
       </c>
       <c r="Q29">
-        <v>9.328129285333333</v>
+        <v>9.316355061333333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1582654049167345</v>
+        <v>0.1595477964561352</v>
       </c>
       <c r="T29">
-        <v>1.739804045777009</v>
+        <v>1.759642235042157</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>27.0711662448958</v>
+        <v>26.10433887900666</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3815,22 +3815,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1257190934484174</v>
+        <v>0.1254470713076186</v>
       </c>
       <c r="C30">
-        <v>22.93781480185318</v>
+        <v>22.68910819120912</v>
       </c>
       <c r="D30">
-        <v>29.43981480185318</v>
+        <v>29.49510819120912</v>
       </c>
       <c r="E30">
-        <v>-7.087999999999999</v>
+        <v>-6.783999999999999</v>
       </c>
       <c r="F30">
-        <v>8.512</v>
+        <v>8.816000000000001</v>
       </c>
       <c r="G30">
         <v>2.01</v>
@@ -3851,28 +3851,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M30">
-        <v>0.4281536</v>
+        <v>0.4434448</v>
       </c>
       <c r="N30">
-        <v>10.74851306666667</v>
+        <v>10.73322186666667</v>
       </c>
       <c r="O30">
-        <v>2.472158005333333</v>
+        <v>2.468641029333333</v>
       </c>
       <c r="P30">
-        <v>8.276355061333334</v>
+        <v>8.264580837333332</v>
       </c>
       <c r="Q30">
-        <v>9.316355061333333</v>
+        <v>9.304580837333333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1595477964561352</v>
+        <v>0.1608663117008712</v>
       </c>
       <c r="T30">
-        <v>1.759642235042157</v>
+        <v>1.780039246540126</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>26.10433887900666</v>
+        <v>25.20418926248919</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3897,22 +3897,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1254470713076186</v>
+        <v>0.1251750491668197</v>
       </c>
       <c r="C31">
-        <v>22.68910819120913</v>
+        <v>22.44060967372157</v>
       </c>
       <c r="D31">
-        <v>29.49510819120912</v>
+        <v>29.55060967372157</v>
       </c>
       <c r="E31">
-        <v>-6.784000000000001</v>
+        <v>-6.48</v>
       </c>
       <c r="F31">
-        <v>8.815999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G31">
         <v>2.01</v>
@@ -3933,28 +3933,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M31">
-        <v>0.4434447999999999</v>
+        <v>0.4587359999999999</v>
       </c>
       <c r="N31">
-        <v>10.73322186666667</v>
+        <v>10.71793066666667</v>
       </c>
       <c r="O31">
-        <v>2.468641029333333</v>
+        <v>2.465124053333333</v>
       </c>
       <c r="P31">
-        <v>8.264580837333332</v>
+        <v>8.252806613333332</v>
       </c>
       <c r="Q31">
-        <v>9.304580837333333</v>
+        <v>9.292806613333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1608663117008712</v>
+        <v>0.1622224988097425</v>
       </c>
       <c r="T31">
-        <v>1.780039246540126</v>
+        <v>1.801019029795179</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>25.20418926248919</v>
+        <v>24.36404962040622</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1251750491668197</v>
+        <v>0.1249030270260209</v>
       </c>
       <c r="C32">
-        <v>22.44060967372157</v>
+        <v>22.19232042632322</v>
       </c>
       <c r="D32">
-        <v>29.55060967372157</v>
+        <v>29.60632042632322</v>
       </c>
       <c r="E32">
-        <v>-6.48</v>
+        <v>-6.176</v>
       </c>
       <c r="F32">
-        <v>9.119999999999999</v>
+        <v>9.423999999999999</v>
       </c>
       <c r="G32">
         <v>2.01</v>
@@ -4015,28 +4015,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M32">
-        <v>0.4587359999999999</v>
+        <v>0.4740271999999999</v>
       </c>
       <c r="N32">
-        <v>10.71793066666667</v>
+        <v>10.70263946666667</v>
       </c>
       <c r="O32">
-        <v>2.465124053333333</v>
+        <v>2.461607077333333</v>
       </c>
       <c r="P32">
-        <v>8.252806613333332</v>
+        <v>8.241032389333332</v>
       </c>
       <c r="Q32">
-        <v>9.292806613333333</v>
+        <v>9.281032389333333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1622224988097425</v>
+        <v>0.1636179956898854</v>
       </c>
       <c r="T32">
-        <v>1.801019029795179</v>
+        <v>1.822606922709799</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>24.36404962040622</v>
+        <v>23.57811253587699</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4061,22 +4061,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1249030270260209</v>
+        <v>0.1246310048852221</v>
       </c>
       <c r="C33">
-        <v>22.19232042632322</v>
+        <v>21.94424163483887</v>
       </c>
       <c r="D33">
-        <v>29.60632042632322</v>
+        <v>29.66224163483888</v>
       </c>
       <c r="E33">
-        <v>-6.176</v>
+        <v>-5.872</v>
       </c>
       <c r="F33">
-        <v>9.423999999999999</v>
+        <v>9.728</v>
       </c>
       <c r="G33">
         <v>2.01</v>
@@ -4097,28 +4097,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M33">
-        <v>0.4740271999999999</v>
+        <v>0.4893184</v>
       </c>
       <c r="N33">
-        <v>10.70263946666667</v>
+        <v>10.68734826666667</v>
       </c>
       <c r="O33">
-        <v>2.461607077333333</v>
+        <v>2.458090101333333</v>
       </c>
       <c r="P33">
-        <v>8.241032389333332</v>
+        <v>8.229258165333333</v>
       </c>
       <c r="Q33">
-        <v>9.281032389333333</v>
+        <v>9.269258165333333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1636179956898854</v>
+        <v>0.1650545365959149</v>
       </c>
       <c r="T33">
-        <v>1.822606922709799</v>
+        <v>1.84482975365132</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>23.57811253587699</v>
+        <v>22.84129651913083</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4143,22 +4143,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1246310048852221</v>
+        <v>0.1243589827444233</v>
       </c>
       <c r="C34">
-        <v>21.94424163483887</v>
+        <v>21.69637449406956</v>
       </c>
       <c r="D34">
-        <v>29.66224163483888</v>
+        <v>29.71837449406956</v>
       </c>
       <c r="E34">
-        <v>-5.872</v>
+        <v>-5.568</v>
       </c>
       <c r="F34">
-        <v>9.728</v>
+        <v>10.032</v>
       </c>
       <c r="G34">
         <v>2.01</v>
@@ -4179,28 +4179,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M34">
-        <v>0.4893184</v>
+        <v>0.5046096</v>
       </c>
       <c r="N34">
-        <v>10.68734826666667</v>
+        <v>10.67205706666667</v>
       </c>
       <c r="O34">
-        <v>2.458090101333333</v>
+        <v>2.454573125333333</v>
       </c>
       <c r="P34">
-        <v>8.229258165333333</v>
+        <v>8.217483941333333</v>
       </c>
       <c r="Q34">
-        <v>9.269258165333333</v>
+        <v>9.257483941333334</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1650545365959149</v>
+        <v>0.1665339593200348</v>
       </c>
       <c r="T34">
-        <v>1.84482975365132</v>
+        <v>1.867715952680647</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>22.84129651913083</v>
+        <v>22.1491360185511</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4225,22 +4225,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1243589827444233</v>
+        <v>0.1240869606036245</v>
       </c>
       <c r="C35">
-        <v>21.69637449406956</v>
+        <v>21.4487202078776</v>
       </c>
       <c r="D35">
-        <v>29.71837449406956</v>
+        <v>29.7747202078776</v>
       </c>
       <c r="E35">
-        <v>-5.568</v>
+        <v>-5.263999999999999</v>
       </c>
       <c r="F35">
-        <v>10.032</v>
+        <v>10.336</v>
       </c>
       <c r="G35">
         <v>2.01</v>
@@ -4261,28 +4261,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M35">
-        <v>0.5046096</v>
+        <v>0.5199007999999999</v>
       </c>
       <c r="N35">
-        <v>10.67205706666667</v>
+        <v>10.65676586666667</v>
       </c>
       <c r="O35">
-        <v>2.454573125333333</v>
+        <v>2.451056149333333</v>
       </c>
       <c r="P35">
-        <v>8.217483941333333</v>
+        <v>8.205709717333333</v>
       </c>
       <c r="Q35">
-        <v>9.257483941333334</v>
+        <v>9.245709717333334</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1665339593200348</v>
+        <v>0.1680582130357948</v>
       </c>
       <c r="T35">
-        <v>1.867715952680647</v>
+        <v>1.891295672892682</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>22.1491360185511</v>
+        <v>21.4976908415349</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4307,22 +4307,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1240869606036245</v>
+        <v>0.1238149384628257</v>
       </c>
       <c r="C36">
-        <v>21.4487202078776</v>
+        <v>21.20127998927273</v>
       </c>
       <c r="D36">
-        <v>29.7747202078776</v>
+        <v>29.83127998927273</v>
       </c>
       <c r="E36">
-        <v>-5.263999999999999</v>
+        <v>-4.959999999999999</v>
       </c>
       <c r="F36">
-        <v>10.336</v>
+        <v>10.64</v>
       </c>
       <c r="G36">
         <v>2.01</v>
@@ -4343,28 +4343,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M36">
-        <v>0.5199007999999999</v>
+        <v>0.535192</v>
       </c>
       <c r="N36">
-        <v>10.65676586666667</v>
+        <v>10.64147466666667</v>
       </c>
       <c r="O36">
-        <v>2.451056149333333</v>
+        <v>2.447539173333333</v>
       </c>
       <c r="P36">
-        <v>8.205709717333333</v>
+        <v>8.193935493333331</v>
       </c>
       <c r="Q36">
-        <v>9.245709717333334</v>
+        <v>9.23393549333333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1680582130357948</v>
+        <v>0.1696293668658857</v>
       </c>
       <c r="T36">
-        <v>1.891295672892682</v>
+        <v>1.915600922957394</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>21.4976908415349</v>
+        <v>20.88347110320533</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4389,22 +4389,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1238149384628257</v>
+        <v>0.1235429163220269</v>
       </c>
       <c r="C37">
-        <v>21.20127998927273</v>
+        <v>20.95405506049909</v>
       </c>
       <c r="D37">
-        <v>29.83127998927273</v>
+        <v>29.88805506049909</v>
       </c>
       <c r="E37">
-        <v>-4.959999999999999</v>
+        <v>-4.655999999999999</v>
       </c>
       <c r="F37">
-        <v>10.64</v>
+        <v>10.944</v>
       </c>
       <c r="G37">
         <v>2.01</v>
@@ -4425,28 +4425,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M37">
-        <v>0.535192</v>
+        <v>0.5504832000000001</v>
       </c>
       <c r="N37">
-        <v>10.64147466666667</v>
+        <v>10.62618346666667</v>
       </c>
       <c r="O37">
-        <v>2.447539173333333</v>
+        <v>2.444022197333333</v>
       </c>
       <c r="P37">
-        <v>8.193935493333331</v>
+        <v>8.182161269333331</v>
       </c>
       <c r="Q37">
-        <v>9.23393549333333</v>
+        <v>9.222161269333331</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1696293668658857</v>
+        <v>0.1712496192531671</v>
       </c>
       <c r="T37">
-        <v>1.915600922957394</v>
+        <v>1.940665712086629</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>20.88347110320533</v>
+        <v>20.30337468367184</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4471,22 +4471,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1235429163220269</v>
+        <v>0.1232708941812281</v>
       </c>
       <c r="C38">
-        <v>20.95405506049909</v>
+        <v>20.70704665312334</v>
       </c>
       <c r="D38">
-        <v>29.88805506049909</v>
+        <v>29.94504665312333</v>
       </c>
       <c r="E38">
-        <v>-4.656000000000001</v>
+        <v>-4.352</v>
       </c>
       <c r="F38">
-        <v>10.944</v>
+        <v>11.248</v>
       </c>
       <c r="G38">
         <v>2.01</v>
@@ -4507,28 +4507,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M38">
-        <v>0.5504832</v>
+        <v>0.5657743999999999</v>
       </c>
       <c r="N38">
-        <v>10.62618346666667</v>
+        <v>10.61089226666667</v>
       </c>
       <c r="O38">
-        <v>2.444022197333333</v>
+        <v>2.440505221333333</v>
       </c>
       <c r="P38">
-        <v>8.182161269333331</v>
+        <v>8.170387045333332</v>
       </c>
       <c r="Q38">
-        <v>9.222161269333331</v>
+        <v>9.210387045333331</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1712496192531671</v>
+        <v>0.1729213082241716</v>
       </c>
       <c r="T38">
-        <v>1.940665712086629</v>
+        <v>1.966526208807267</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>20.30337468367185</v>
+        <v>19.75463482735639</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4553,22 +4553,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1232708941812281</v>
+        <v>0.1229988720404293</v>
       </c>
       <c r="C39">
-        <v>20.70704665312334</v>
+        <v>20.46025600812357</v>
       </c>
       <c r="D39">
-        <v>29.94504665312333</v>
+        <v>30.00225600812357</v>
       </c>
       <c r="E39">
-        <v>-4.352</v>
+        <v>-4.048</v>
       </c>
       <c r="F39">
-        <v>11.248</v>
+        <v>11.552</v>
       </c>
       <c r="G39">
         <v>2.01</v>
@@ -4589,28 +4589,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M39">
-        <v>0.5657743999999999</v>
+        <v>0.5810656</v>
       </c>
       <c r="N39">
-        <v>10.61089226666667</v>
+        <v>10.59560106666667</v>
       </c>
       <c r="O39">
-        <v>2.440505221333333</v>
+        <v>2.436988245333333</v>
       </c>
       <c r="P39">
-        <v>8.170387045333332</v>
+        <v>8.158612821333332</v>
       </c>
       <c r="Q39">
-        <v>9.210387045333331</v>
+        <v>9.198612821333331</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1729213082241716</v>
+        <v>0.1746469226458537</v>
       </c>
       <c r="T39">
-        <v>1.966526208807267</v>
+        <v>1.99322091509954</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>19.75463482735639</v>
+        <v>19.23477601611017</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4635,22 +4635,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1229988720404293</v>
+        <v>0.1227268498996305</v>
       </c>
       <c r="C40">
-        <v>20.46025600812357</v>
+        <v>20.21368437597957</v>
       </c>
       <c r="D40">
-        <v>30.00225600812357</v>
+        <v>30.05968437597957</v>
       </c>
       <c r="E40">
-        <v>-4.048</v>
+        <v>-3.744</v>
       </c>
       <c r="F40">
-        <v>11.552</v>
+        <v>11.856</v>
       </c>
       <c r="G40">
         <v>2.01</v>
@@ -4671,28 +4671,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M40">
-        <v>0.5810656</v>
+        <v>0.5963567999999999</v>
       </c>
       <c r="N40">
-        <v>10.59560106666667</v>
+        <v>10.58030986666667</v>
       </c>
       <c r="O40">
-        <v>2.436988245333333</v>
+        <v>2.433471269333333</v>
       </c>
       <c r="P40">
-        <v>8.158612821333332</v>
+        <v>8.146838597333332</v>
       </c>
       <c r="Q40">
-        <v>9.198612821333331</v>
+        <v>9.186838597333331</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1746469226458537</v>
+        <v>0.1764291145895582</v>
       </c>
       <c r="T40">
-        <v>1.99322091509954</v>
+        <v>2.02079085766369</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>19.23477601611017</v>
+        <v>18.74157663108171</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4717,22 +4717,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1227268498996305</v>
+        <v>0.1224548277588317</v>
       </c>
       <c r="C41">
-        <v>20.21368437597957</v>
+        <v>19.96733301676378</v>
       </c>
       <c r="D41">
-        <v>30.05968437597957</v>
+        <v>30.11733301676378</v>
       </c>
       <c r="E41">
-        <v>-3.744</v>
+        <v>-3.44</v>
       </c>
       <c r="F41">
-        <v>11.856</v>
+        <v>12.16</v>
       </c>
       <c r="G41">
         <v>2.01</v>
@@ -4753,28 +4753,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M41">
-        <v>0.5963567999999999</v>
+        <v>0.611648</v>
       </c>
       <c r="N41">
-        <v>10.58030986666667</v>
+        <v>10.56501866666667</v>
       </c>
       <c r="O41">
-        <v>2.433471269333333</v>
+        <v>2.429954293333333</v>
       </c>
       <c r="P41">
-        <v>8.146838597333332</v>
+        <v>8.135064373333332</v>
       </c>
       <c r="Q41">
-        <v>9.186838597333331</v>
+        <v>9.175064373333331</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1764291145895582</v>
+        <v>0.1782707129313862</v>
       </c>
       <c r="T41">
-        <v>2.02079085766369</v>
+        <v>2.049279798313312</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>18.74157663108171</v>
+        <v>18.27303721530466</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4799,22 +4799,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1224548277588317</v>
+        <v>0.1221828056180329</v>
       </c>
       <c r="C42">
-        <v>19.96733301676378</v>
+        <v>19.72120320023354</v>
       </c>
       <c r="D42">
-        <v>30.11733301676378</v>
+        <v>30.17520320023354</v>
       </c>
       <c r="E42">
-        <v>-3.44</v>
+        <v>-3.135999999999999</v>
       </c>
       <c r="F42">
-        <v>12.16</v>
+        <v>12.464</v>
       </c>
       <c r="G42">
         <v>2.01</v>
@@ -4835,28 +4835,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M42">
-        <v>0.611648</v>
+        <v>0.6269392</v>
       </c>
       <c r="N42">
-        <v>10.56501866666667</v>
+        <v>10.54972746666667</v>
       </c>
       <c r="O42">
-        <v>2.429954293333333</v>
+        <v>2.426437317333333</v>
       </c>
       <c r="P42">
-        <v>8.135064373333332</v>
+        <v>8.123290149333332</v>
       </c>
       <c r="Q42">
-        <v>9.175064373333331</v>
+        <v>9.163290149333331</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1782707129313862</v>
+        <v>0.180174738335649</v>
       </c>
       <c r="T42">
-        <v>2.049279798313312</v>
+        <v>2.078734465764616</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>18.27303721530466</v>
+        <v>17.82735338078503</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4881,22 +4881,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1221828056180329</v>
+        <v>0.1219107834772341</v>
       </c>
       <c r="C43">
-        <v>19.72120320023354</v>
+        <v>19.47529620592427</v>
       </c>
       <c r="D43">
-        <v>30.17520320023354</v>
+        <v>30.23329620592427</v>
       </c>
       <c r="E43">
-        <v>-3.135999999999999</v>
+        <v>-2.831999999999999</v>
       </c>
       <c r="F43">
-        <v>12.464</v>
+        <v>12.768</v>
       </c>
       <c r="G43">
         <v>2.01</v>
@@ -4917,28 +4917,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M43">
-        <v>0.6269392</v>
+        <v>0.6422304</v>
       </c>
       <c r="N43">
-        <v>10.54972746666667</v>
+        <v>10.53443626666667</v>
       </c>
       <c r="O43">
-        <v>2.426437317333333</v>
+        <v>2.422920341333333</v>
       </c>
       <c r="P43">
-        <v>8.123290149333332</v>
+        <v>8.111515925333332</v>
       </c>
       <c r="Q43">
-        <v>9.163290149333331</v>
+        <v>9.151515925333332</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.180174738335649</v>
+        <v>0.1821444197883347</v>
       </c>
       <c r="T43">
-        <v>2.078734465764616</v>
+        <v>2.109204811403895</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>17.82735338078503</v>
+        <v>17.40289258600444</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4963,22 +4963,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1219107834772341</v>
+        <v>0.1216387613364353</v>
       </c>
       <c r="C44">
-        <v>19.47529620592427</v>
+        <v>19.22961332324378</v>
       </c>
       <c r="D44">
-        <v>30.23329620592427</v>
+        <v>30.29161332324378</v>
       </c>
       <c r="E44">
-        <v>-2.832000000000001</v>
+        <v>-2.528</v>
       </c>
       <c r="F44">
-        <v>12.768</v>
+        <v>13.072</v>
       </c>
       <c r="G44">
         <v>2.01</v>
@@ -4999,28 +4999,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M44">
-        <v>0.6422303999999999</v>
+        <v>0.6575215999999999</v>
       </c>
       <c r="N44">
-        <v>10.53443626666667</v>
+        <v>10.51914506666667</v>
       </c>
       <c r="O44">
-        <v>2.422920341333334</v>
+        <v>2.419403365333333</v>
       </c>
       <c r="P44">
-        <v>8.111515925333332</v>
+        <v>8.099741701333333</v>
       </c>
       <c r="Q44">
-        <v>9.151515925333332</v>
+        <v>9.139741701333332</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1821444197883346</v>
+        <v>0.1841832128709391</v>
       </c>
       <c r="T44">
-        <v>2.109204811403895</v>
+        <v>2.140744291977887</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>17.40289258600444</v>
+        <v>16.99817415377178</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1216387613364353</v>
+        <v>0.1213667391956365</v>
       </c>
       <c r="C45">
-        <v>19.22961332324378</v>
+        <v>18.98415585156774</v>
       </c>
       <c r="D45">
-        <v>30.29161332324378</v>
+        <v>30.35015585156774</v>
       </c>
       <c r="E45">
-        <v>-2.528</v>
+        <v>-2.224</v>
       </c>
       <c r="F45">
-        <v>13.072</v>
+        <v>13.376</v>
       </c>
       <c r="G45">
         <v>2.01</v>
@@ -5081,28 +5081,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M45">
-        <v>0.6575215999999999</v>
+        <v>0.6728128</v>
       </c>
       <c r="N45">
-        <v>10.51914506666667</v>
+        <v>10.50385386666667</v>
       </c>
       <c r="O45">
-        <v>2.419403365333333</v>
+        <v>2.415886389333334</v>
       </c>
       <c r="P45">
-        <v>8.099741701333333</v>
+        <v>8.087967477333333</v>
       </c>
       <c r="Q45">
-        <v>9.139741701333332</v>
+        <v>9.127967477333332</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1841832128709391</v>
+        <v>0.186294819992208</v>
       </c>
       <c r="T45">
-        <v>2.140744291977887</v>
+        <v>2.173410182572378</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>16.99817415377178</v>
+        <v>16.61185201391333</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5127,22 +5127,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1213667391956365</v>
+        <v>0.1210947170548377</v>
       </c>
       <c r="C46">
-        <v>18.98415585156774</v>
+        <v>18.73892510033605</v>
       </c>
       <c r="D46">
-        <v>30.35015585156774</v>
+        <v>30.40892510033605</v>
       </c>
       <c r="E46">
-        <v>-2.224</v>
+        <v>-1.92</v>
       </c>
       <c r="F46">
-        <v>13.376</v>
+        <v>13.68</v>
       </c>
       <c r="G46">
         <v>2.01</v>
@@ -5163,28 +5163,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M46">
-        <v>0.6728128</v>
+        <v>0.6881039999999999</v>
       </c>
       <c r="N46">
-        <v>10.50385386666667</v>
+        <v>10.48856266666667</v>
       </c>
       <c r="O46">
-        <v>2.415886389333334</v>
+        <v>2.412369413333333</v>
       </c>
       <c r="P46">
-        <v>8.087967477333333</v>
+        <v>8.076193253333333</v>
       </c>
       <c r="Q46">
-        <v>9.127967477333332</v>
+        <v>9.116193253333332</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.186294819992208</v>
+        <v>0.1884832128269776</v>
       </c>
       <c r="T46">
-        <v>2.173410182572378</v>
+        <v>2.207263923733941</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>16.61185201391333</v>
+        <v>16.24269974693748</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5209,22 +5209,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1210947170548377</v>
+        <v>0.1208226949140389</v>
       </c>
       <c r="C47">
-        <v>18.73892510033605</v>
+        <v>18.4939223891506</v>
       </c>
       <c r="D47">
-        <v>30.40892510033605</v>
+        <v>30.4679223891506</v>
       </c>
       <c r="E47">
-        <v>-1.92</v>
+        <v>-1.616</v>
       </c>
       <c r="F47">
-        <v>13.68</v>
+        <v>13.984</v>
       </c>
       <c r="G47">
         <v>2.01</v>
@@ -5245,28 +5245,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M47">
-        <v>0.6881039999999999</v>
+        <v>0.7033952</v>
       </c>
       <c r="N47">
-        <v>10.48856266666667</v>
+        <v>10.47327146666667</v>
       </c>
       <c r="O47">
-        <v>2.412369413333333</v>
+        <v>2.408852437333334</v>
       </c>
       <c r="P47">
-        <v>8.076193253333333</v>
+        <v>8.064419029333333</v>
       </c>
       <c r="Q47">
-        <v>9.116193253333332</v>
+        <v>9.104419029333332</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1884832128269776</v>
+        <v>0.1907526572482202</v>
       </c>
       <c r="T47">
-        <v>2.207263923733941</v>
+        <v>2.242371507160748</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>16.24269974693748</v>
+        <v>15.88959757852579</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5291,22 +5291,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1208226949140389</v>
+        <v>0.1205506727732401</v>
       </c>
       <c r="C48">
-        <v>18.4939223891506</v>
+        <v>18.24914904787398</v>
       </c>
       <c r="D48">
-        <v>30.4679223891506</v>
+        <v>30.52714904787398</v>
       </c>
       <c r="E48">
-        <v>-1.616</v>
+        <v>-1.311999999999999</v>
       </c>
       <c r="F48">
-        <v>13.984</v>
+        <v>14.288</v>
       </c>
       <c r="G48">
         <v>2.01</v>
@@ -5327,28 +5327,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M48">
-        <v>0.7033952</v>
+        <v>0.7186863999999999</v>
       </c>
       <c r="N48">
-        <v>10.47327146666667</v>
+        <v>10.45798026666667</v>
       </c>
       <c r="O48">
-        <v>2.408852437333334</v>
+        <v>2.405335461333333</v>
       </c>
       <c r="P48">
-        <v>8.064419029333333</v>
+        <v>8.052644805333333</v>
       </c>
       <c r="Q48">
-        <v>9.104419029333332</v>
+        <v>9.092644805333332</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1907526572482202</v>
+        <v>0.1931077410815851</v>
       </c>
       <c r="T48">
-        <v>2.242371507160748</v>
+        <v>2.278803905056491</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>15.88959757852579</v>
+        <v>15.55152103430184</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5373,22 +5373,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1205506727732401</v>
+        <v>0.1202786506324413</v>
       </c>
       <c r="C49">
-        <v>18.24914904787398</v>
+        <v>18.00460641672939</v>
       </c>
       <c r="D49">
-        <v>30.52714904787398</v>
+        <v>30.5866064167294</v>
       </c>
       <c r="E49">
-        <v>-1.311999999999999</v>
+        <v>-1.007999999999999</v>
       </c>
       <c r="F49">
-        <v>14.288</v>
+        <v>14.592</v>
       </c>
       <c r="G49">
         <v>2.01</v>
@@ -5409,28 +5409,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M49">
-        <v>0.7186863999999999</v>
+        <v>0.7339776</v>
       </c>
       <c r="N49">
-        <v>10.45798026666667</v>
+        <v>10.44268906666667</v>
       </c>
       <c r="O49">
-        <v>2.405335461333333</v>
+        <v>2.401818485333334</v>
       </c>
       <c r="P49">
-        <v>8.052644805333333</v>
+        <v>8.040870581333333</v>
       </c>
       <c r="Q49">
-        <v>9.092644805333332</v>
+        <v>9.080870581333333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1931077410815851</v>
+        <v>0.1955534050623871</v>
       </c>
       <c r="T49">
-        <v>2.278803905056491</v>
+        <v>2.316637549025147</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>15.55152103430184</v>
+        <v>15.22753101275389</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5455,22 +5455,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1202786506324413</v>
+        <v>0.1200066284916425</v>
       </c>
       <c r="C50">
-        <v>18.00460641672939</v>
+        <v>17.7602958464018</v>
       </c>
       <c r="D50">
-        <v>30.5866064167294</v>
+        <v>30.6462958464018</v>
       </c>
       <c r="E50">
-        <v>-1.008000000000001</v>
+        <v>-0.7040000000000006</v>
       </c>
       <c r="F50">
-        <v>14.592</v>
+        <v>14.896</v>
       </c>
       <c r="G50">
         <v>2.01</v>
@@ -5491,28 +5491,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M50">
-        <v>0.7339775999999999</v>
+        <v>0.7492688</v>
       </c>
       <c r="N50">
-        <v>10.44268906666667</v>
+        <v>10.42739786666667</v>
       </c>
       <c r="O50">
-        <v>2.401818485333334</v>
+        <v>2.398301509333333</v>
       </c>
       <c r="P50">
-        <v>8.040870581333333</v>
+        <v>8.029096357333334</v>
       </c>
       <c r="Q50">
-        <v>9.080870581333333</v>
+        <v>9.069096357333333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1955534050623871</v>
+        <v>0.1980949774345931</v>
       </c>
       <c r="T50">
-        <v>2.316637549025147</v>
+        <v>2.355954865306299</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5529,7 +5529,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>15.22753101275389</v>
+        <v>14.91676507371809</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5537,22 +5537,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1200066284916425</v>
+        <v>0.1197346063508437</v>
       </c>
       <c r="C51">
-        <v>17.7602958464018</v>
+        <v>17.5162186981401</v>
       </c>
       <c r="D51">
-        <v>30.6462958464018</v>
+        <v>30.7062186981401</v>
       </c>
       <c r="E51">
-        <v>-0.7040000000000006</v>
+        <v>-0.4000000000000004</v>
       </c>
       <c r="F51">
-        <v>14.896</v>
+        <v>15.2</v>
       </c>
       <c r="G51">
         <v>2.01</v>
@@ -5573,28 +5573,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M51">
-        <v>0.7492688</v>
+        <v>0.7645599999999999</v>
       </c>
       <c r="N51">
-        <v>10.42739786666667</v>
+        <v>10.41210666666667</v>
       </c>
       <c r="O51">
-        <v>2.398301509333333</v>
+        <v>2.394784533333334</v>
       </c>
       <c r="P51">
-        <v>8.029096357333334</v>
+        <v>8.017322133333334</v>
       </c>
       <c r="Q51">
-        <v>9.069096357333333</v>
+        <v>9.057322133333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1980949774345931</v>
+        <v>0.2007382127016874</v>
       </c>
       <c r="T51">
-        <v>2.355954865306299</v>
+        <v>2.396844874238697</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>14.91676507371809</v>
+        <v>14.61842977224373</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5619,22 +5619,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1197346063508437</v>
+        <v>0.1194625842100449</v>
       </c>
       <c r="C52">
-        <v>17.5162186981401</v>
+        <v>17.27237634386076</v>
       </c>
       <c r="D52">
-        <v>30.7062186981401</v>
+        <v>30.76637634386076</v>
       </c>
       <c r="E52">
-        <v>-0.4000000000000004</v>
+        <v>-0.09600000000000009</v>
       </c>
       <c r="F52">
-        <v>15.2</v>
+        <v>15.504</v>
       </c>
       <c r="G52">
         <v>2.01</v>
@@ -5655,28 +5655,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M52">
-        <v>0.7645599999999999</v>
+        <v>0.7798512</v>
       </c>
       <c r="N52">
-        <v>10.41210666666667</v>
+        <v>10.39681546666667</v>
       </c>
       <c r="O52">
-        <v>2.394784533333334</v>
+        <v>2.391267557333333</v>
       </c>
       <c r="P52">
-        <v>8.017322133333334</v>
+        <v>8.005547909333334</v>
       </c>
       <c r="Q52">
-        <v>9.057322133333333</v>
+        <v>9.045547909333333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2007382127016874</v>
+        <v>0.2034893351225406</v>
       </c>
       <c r="T52">
-        <v>2.396844874238697</v>
+        <v>2.43940386312752</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>14.61842977224373</v>
+        <v>14.3317938943566</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5701,22 +5701,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1194625842100449</v>
+        <v>0.1191905620692461</v>
       </c>
       <c r="C53">
-        <v>17.27237634386076</v>
+        <v>17.02877016625237</v>
       </c>
       <c r="D53">
-        <v>30.76637634386076</v>
+        <v>30.82677016625237</v>
       </c>
       <c r="E53">
-        <v>-0.09600000000000009</v>
+        <v>0.2080000000000002</v>
       </c>
       <c r="F53">
-        <v>15.504</v>
+        <v>15.808</v>
       </c>
       <c r="G53">
         <v>2.01</v>
@@ -5737,28 +5737,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M53">
-        <v>0.7798512</v>
+        <v>0.7951423999999999</v>
       </c>
       <c r="N53">
-        <v>10.39681546666667</v>
+        <v>10.38152426666667</v>
       </c>
       <c r="O53">
-        <v>2.391267557333333</v>
+        <v>2.387750581333334</v>
       </c>
       <c r="P53">
-        <v>8.005547909333334</v>
+        <v>7.993773685333332</v>
       </c>
       <c r="Q53">
-        <v>9.045547909333333</v>
+        <v>9.033773685333333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2034893351225406</v>
+        <v>0.2063550876442627</v>
       </c>
       <c r="T53">
-        <v>2.43940386312752</v>
+        <v>2.483736143220044</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>14.3317938943566</v>
+        <v>14.05618247331128</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5783,22 +5783,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1191905620692461</v>
+        <v>0.1189185399284473</v>
       </c>
       <c r="C54">
-        <v>17.02877016625237</v>
+        <v>16.78540155888168</v>
       </c>
       <c r="D54">
-        <v>30.82677016625237</v>
+        <v>30.88740155888168</v>
       </c>
       <c r="E54">
-        <v>0.2080000000000002</v>
+        <v>0.5119999999999987</v>
       </c>
       <c r="F54">
-        <v>15.808</v>
+        <v>16.112</v>
       </c>
       <c r="G54">
         <v>2.01</v>
@@ -5819,28 +5819,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M54">
-        <v>0.7951423999999999</v>
+        <v>0.8104335999999999</v>
       </c>
       <c r="N54">
-        <v>10.38152426666667</v>
+        <v>10.36623306666667</v>
       </c>
       <c r="O54">
-        <v>2.387750581333334</v>
+        <v>2.384233605333333</v>
       </c>
       <c r="P54">
-        <v>7.993773685333332</v>
+        <v>7.981999461333332</v>
       </c>
       <c r="Q54">
-        <v>9.033773685333333</v>
+        <v>9.021999461333333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2063550876442627</v>
+        <v>0.2093427870818027</v>
       </c>
       <c r="T54">
-        <v>2.483736143220044</v>
+        <v>2.529954903316504</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5857,7 +5857,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>14.05618247331128</v>
+        <v>13.7909714832488</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5865,22 +5865,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1189185399284473</v>
+        <v>0.1186465177876485</v>
       </c>
       <c r="C55">
-        <v>16.78540155888168</v>
+        <v>16.54227192630071</v>
       </c>
       <c r="D55">
-        <v>30.88740155888168</v>
+        <v>30.94827192630071</v>
       </c>
       <c r="E55">
-        <v>0.5119999999999987</v>
+        <v>0.8160000000000007</v>
       </c>
       <c r="F55">
-        <v>16.112</v>
+        <v>16.416</v>
       </c>
       <c r="G55">
         <v>2.01</v>
@@ -5901,28 +5901,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M55">
-        <v>0.8104335999999999</v>
+        <v>0.8257247999999999</v>
       </c>
       <c r="N55">
-        <v>10.36623306666667</v>
+        <v>10.35094186666667</v>
       </c>
       <c r="O55">
-        <v>2.384233605333333</v>
+        <v>2.380716629333334</v>
       </c>
       <c r="P55">
-        <v>7.981999461333332</v>
+        <v>7.970225237333333</v>
       </c>
       <c r="Q55">
-        <v>9.021999461333333</v>
+        <v>9.010225237333334</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2093427870818027</v>
+        <v>0.212460386494888</v>
       </c>
       <c r="T55">
-        <v>2.529954903316504</v>
+        <v>2.578183174721507</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>13.7909714832488</v>
+        <v>13.5355831224479</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5947,22 +5947,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1186465177876485</v>
+        <v>0.1183744956468497</v>
       </c>
       <c r="C56">
-        <v>16.54227192630071</v>
+        <v>16.29938268415529</v>
       </c>
       <c r="D56">
-        <v>30.94827192630071</v>
+        <v>31.00938268415529</v>
       </c>
       <c r="E56">
-        <v>0.8160000000000007</v>
+        <v>1.119999999999999</v>
       </c>
       <c r="F56">
-        <v>16.416</v>
+        <v>16.72</v>
       </c>
       <c r="G56">
         <v>2.01</v>
@@ -5983,28 +5983,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M56">
-        <v>0.8257247999999999</v>
+        <v>0.8410159999999999</v>
       </c>
       <c r="N56">
-        <v>10.35094186666667</v>
+        <v>10.33565066666667</v>
       </c>
       <c r="O56">
-        <v>2.380716629333334</v>
+        <v>2.377199653333333</v>
       </c>
       <c r="P56">
-        <v>7.970225237333333</v>
+        <v>7.958451013333333</v>
       </c>
       <c r="Q56">
-        <v>9.010225237333334</v>
+        <v>8.998451013333334</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.212460386494888</v>
+        <v>0.2157165458818882</v>
       </c>
       <c r="T56">
-        <v>2.578183174721507</v>
+        <v>2.628554924855621</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>13.5355831224479</v>
+        <v>13.28948161113066</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6029,22 +6029,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1183744956468497</v>
+        <v>0.1181024735060509</v>
       </c>
       <c r="C57">
-        <v>16.29938268415529</v>
+        <v>16.05673525929474</v>
       </c>
       <c r="D57">
-        <v>31.00938268415529</v>
+        <v>31.07073525929474</v>
       </c>
       <c r="E57">
-        <v>1.119999999999999</v>
+        <v>1.424000000000001</v>
       </c>
       <c r="F57">
-        <v>16.72</v>
+        <v>17.024</v>
       </c>
       <c r="G57">
         <v>2.01</v>
@@ -6065,28 +6065,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M57">
-        <v>0.8410159999999999</v>
+        <v>0.8563072</v>
       </c>
       <c r="N57">
-        <v>10.33565066666667</v>
+        <v>10.32035946666667</v>
       </c>
       <c r="O57">
-        <v>2.377199653333333</v>
+        <v>2.373682677333333</v>
       </c>
       <c r="P57">
-        <v>7.958451013333333</v>
+        <v>7.946676789333333</v>
       </c>
       <c r="Q57">
-        <v>8.998451013333334</v>
+        <v>8.986676789333334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2157165458818882</v>
+        <v>0.219120712513752</v>
       </c>
       <c r="T57">
-        <v>2.628554924855621</v>
+        <v>2.681216299995831</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>13.28948161113066</v>
+        <v>13.05216943950333</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1181024735060509</v>
+        <v>0.1184888013652521</v>
       </c>
       <c r="C58">
-        <v>16.05673525929474</v>
+        <v>15.66567411625192</v>
       </c>
       <c r="D58">
-        <v>31.07073525929474</v>
+        <v>30.98367411625193</v>
       </c>
       <c r="E58">
-        <v>1.424000000000001</v>
+        <v>1.728</v>
       </c>
       <c r="F58">
-        <v>17.024</v>
+        <v>17.328</v>
       </c>
       <c r="G58">
         <v>2.01</v>
@@ -6147,45 +6147,45 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M58">
-        <v>0.8563072</v>
+        <v>0.8975903999999999</v>
       </c>
       <c r="N58">
-        <v>10.32035946666667</v>
+        <v>10.27907626666667</v>
       </c>
       <c r="O58">
-        <v>2.373682677333333</v>
+        <v>2.364187541333333</v>
       </c>
       <c r="P58">
-        <v>7.946676789333333</v>
+        <v>7.914888725333332</v>
       </c>
       <c r="Q58">
-        <v>8.986676789333334</v>
+        <v>8.954888725333333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.219120712513752</v>
+        <v>0.2226832124773304</v>
       </c>
       <c r="T58">
-        <v>2.681216299995831</v>
+        <v>2.736327041421632</v>
       </c>
       <c r="U58">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V58">
         <v>0.23</v>
       </c>
       <c r="W58">
-        <v>0.038731</v>
+        <v>0.039886</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y58">
-        <v>13.05216943950333</v>
+        <v>12.45185628842139</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6193,22 +6193,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1184888013652521</v>
+        <v>0.1182283292244533</v>
       </c>
       <c r="C59">
-        <v>15.66567411625192</v>
+        <v>15.4203192860141</v>
       </c>
       <c r="D59">
-        <v>30.98367411625193</v>
+        <v>31.0423192860141</v>
       </c>
       <c r="E59">
-        <v>1.728</v>
+        <v>2.032000000000002</v>
       </c>
       <c r="F59">
-        <v>17.328</v>
+        <v>17.632</v>
       </c>
       <c r="G59">
         <v>2.01</v>
@@ -6229,28 +6229,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M59">
-        <v>0.8975903999999999</v>
+        <v>0.9133376000000001</v>
       </c>
       <c r="N59">
-        <v>10.27907626666667</v>
+        <v>10.26332906666667</v>
       </c>
       <c r="O59">
-        <v>2.364187541333333</v>
+        <v>2.360565685333333</v>
       </c>
       <c r="P59">
-        <v>7.914888725333332</v>
+        <v>7.902763381333333</v>
       </c>
       <c r="Q59">
-        <v>8.954888725333333</v>
+        <v>8.942763381333332</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2226832124773304</v>
+        <v>0.2264153552963173</v>
       </c>
       <c r="T59">
-        <v>2.736327041421632</v>
+        <v>2.794062103867709</v>
       </c>
       <c r="U59">
         <v>0.0518</v>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>12.45185628842139</v>
+        <v>12.23716911103481</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6275,22 +6275,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1182283292244533</v>
+        <v>0.1179678570836545</v>
       </c>
       <c r="C60">
-        <v>15.42031928601411</v>
+        <v>15.17518688117433</v>
       </c>
       <c r="D60">
-        <v>31.0423192860141</v>
+        <v>31.10118688117432</v>
       </c>
       <c r="E60">
-        <v>2.031999999999998</v>
+        <v>2.336</v>
       </c>
       <c r="F60">
-        <v>17.632</v>
+        <v>17.936</v>
       </c>
       <c r="G60">
         <v>2.01</v>
@@ -6311,28 +6311,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M60">
-        <v>0.9133375999999999</v>
+        <v>0.9290847999999999</v>
       </c>
       <c r="N60">
-        <v>10.26332906666667</v>
+        <v>10.24758186666667</v>
       </c>
       <c r="O60">
-        <v>2.360565685333333</v>
+        <v>2.356943829333333</v>
       </c>
       <c r="P60">
-        <v>7.902763381333333</v>
+        <v>7.890638037333332</v>
       </c>
       <c r="Q60">
-        <v>8.942763381333332</v>
+        <v>8.930638037333331</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2264153552963173</v>
+        <v>0.2303295538625718</v>
       </c>
       <c r="T60">
-        <v>2.794062103867709</v>
+        <v>2.854613510823351</v>
       </c>
       <c r="U60">
         <v>0.0518</v>
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>12.23716911103481</v>
+        <v>12.02975946508507</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6357,22 +6357,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1179678570836545</v>
+        <v>0.1177073849428557</v>
       </c>
       <c r="C61">
-        <v>15.17518688117433</v>
+        <v>14.93027816953661</v>
       </c>
       <c r="D61">
-        <v>31.10118688117432</v>
+        <v>31.16027816953661</v>
       </c>
       <c r="E61">
-        <v>2.336</v>
+        <v>2.639999999999999</v>
       </c>
       <c r="F61">
-        <v>17.936</v>
+        <v>18.24</v>
       </c>
       <c r="G61">
         <v>2.01</v>
@@ -6393,28 +6393,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M61">
-        <v>0.9290847999999999</v>
+        <v>0.9448319999999999</v>
       </c>
       <c r="N61">
-        <v>10.24758186666667</v>
+        <v>10.23183466666667</v>
       </c>
       <c r="O61">
-        <v>2.356943829333333</v>
+        <v>2.353321973333333</v>
       </c>
       <c r="P61">
-        <v>7.890638037333332</v>
+        <v>7.878512693333333</v>
       </c>
       <c r="Q61">
-        <v>8.930638037333331</v>
+        <v>8.918512693333334</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2303295538625718</v>
+        <v>0.2344394623571391</v>
       </c>
       <c r="T61">
-        <v>2.854613510823351</v>
+        <v>2.918192488126775</v>
       </c>
       <c r="U61">
         <v>0.0518</v>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>12.02975946508507</v>
+        <v>11.82926347400032</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6439,22 +6439,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1177073849428557</v>
+        <v>0.1174469128020569</v>
       </c>
       <c r="C62">
-        <v>14.93027816953661</v>
+        <v>14.68559442855849</v>
       </c>
       <c r="D62">
-        <v>31.16027816953661</v>
+        <v>31.21959442855849</v>
       </c>
       <c r="E62">
-        <v>2.639999999999999</v>
+        <v>2.944000000000001</v>
       </c>
       <c r="F62">
-        <v>18.24</v>
+        <v>18.544</v>
       </c>
       <c r="G62">
         <v>2.01</v>
@@ -6475,28 +6475,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M62">
-        <v>0.9448319999999999</v>
+        <v>0.9605792</v>
       </c>
       <c r="N62">
-        <v>10.23183466666667</v>
+        <v>10.21608746666667</v>
       </c>
       <c r="O62">
-        <v>2.353321973333333</v>
+        <v>2.349700117333333</v>
       </c>
       <c r="P62">
-        <v>7.878512693333333</v>
+        <v>7.866387349333333</v>
       </c>
       <c r="Q62">
-        <v>8.918512693333334</v>
+        <v>8.906387349333333</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2344394623571391</v>
+        <v>0.2387601353898894</v>
       </c>
       <c r="T62">
-        <v>2.918192488126775</v>
+        <v>2.985031925804734</v>
       </c>
       <c r="U62">
         <v>0.0518</v>
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>11.82926347400032</v>
+        <v>11.63534112196752</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6521,22 +6521,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1174469128020569</v>
+        <v>0.1171864406612581</v>
       </c>
       <c r="C63">
-        <v>14.68559442855849</v>
+        <v>14.44113694544303</v>
       </c>
       <c r="D63">
-        <v>31.21959442855849</v>
+        <v>31.27913694544304</v>
       </c>
       <c r="E63">
-        <v>2.944000000000001</v>
+        <v>3.247999999999999</v>
       </c>
       <c r="F63">
-        <v>18.544</v>
+        <v>18.848</v>
       </c>
       <c r="G63">
         <v>2.01</v>
@@ -6557,28 +6557,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M63">
-        <v>0.9605792</v>
+        <v>0.9763263999999999</v>
       </c>
       <c r="N63">
-        <v>10.21608746666667</v>
+        <v>10.20034026666667</v>
       </c>
       <c r="O63">
-        <v>2.349700117333333</v>
+        <v>2.346078261333334</v>
       </c>
       <c r="P63">
-        <v>7.866387349333333</v>
+        <v>7.854262005333332</v>
       </c>
       <c r="Q63">
-        <v>8.906387349333333</v>
+        <v>8.894262005333331</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2387601353898894</v>
+        <v>0.2433082122664686</v>
       </c>
       <c r="T63">
-        <v>2.985031925804734</v>
+        <v>3.055389228623638</v>
       </c>
       <c r="U63">
         <v>0.0518</v>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>11.63534112196752</v>
+        <v>11.44767432967773</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6603,22 +6603,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1171864406612581</v>
+        <v>0.1169259685204593</v>
       </c>
       <c r="C64">
-        <v>14.44113694544303</v>
+        <v>14.19690701723199</v>
       </c>
       <c r="D64">
-        <v>31.27913694544304</v>
+        <v>31.33890701723199</v>
       </c>
       <c r="E64">
-        <v>3.247999999999999</v>
+        <v>3.551999999999998</v>
       </c>
       <c r="F64">
-        <v>18.848</v>
+        <v>19.152</v>
       </c>
       <c r="G64">
         <v>2.01</v>
@@ -6639,28 +6639,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M64">
-        <v>0.9763263999999999</v>
+        <v>0.9920735999999999</v>
       </c>
       <c r="N64">
-        <v>10.20034026666667</v>
+        <v>10.18459306666667</v>
       </c>
       <c r="O64">
-        <v>2.346078261333334</v>
+        <v>2.342456405333333</v>
       </c>
       <c r="P64">
-        <v>7.854262005333332</v>
+        <v>7.842136661333333</v>
       </c>
       <c r="Q64">
-        <v>8.894262005333331</v>
+        <v>8.882136661333334</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2433082122664686</v>
+        <v>0.2481021311363764</v>
       </c>
       <c r="T64">
-        <v>3.055389228623638</v>
+        <v>3.129549628892212</v>
       </c>
       <c r="U64">
         <v>0.0518</v>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>11.44767432967773</v>
+        <v>11.26596521333363</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6685,22 +6685,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1169259685204593</v>
+        <v>0.1166654963796604</v>
       </c>
       <c r="C65">
-        <v>14.19690701723199</v>
+        <v>13.95290595089992</v>
       </c>
       <c r="D65">
-        <v>31.33890701723199</v>
+        <v>31.39890595089992</v>
       </c>
       <c r="E65">
-        <v>3.551999999999998</v>
+        <v>3.856</v>
       </c>
       <c r="F65">
-        <v>19.152</v>
+        <v>19.456</v>
       </c>
       <c r="G65">
         <v>2.01</v>
@@ -6721,28 +6721,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M65">
-        <v>0.9920735999999999</v>
+        <v>1.0078208</v>
       </c>
       <c r="N65">
-        <v>10.18459306666667</v>
+        <v>10.16884586666667</v>
       </c>
       <c r="O65">
-        <v>2.342456405333333</v>
+        <v>2.338834549333333</v>
       </c>
       <c r="P65">
-        <v>7.842136661333333</v>
+        <v>7.830011317333334</v>
       </c>
       <c r="Q65">
-        <v>8.882136661333334</v>
+        <v>8.870011317333333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2481021311363764</v>
+        <v>0.2531623788323901</v>
       </c>
       <c r="T65">
-        <v>3.129549628892212</v>
+        <v>3.207830051397929</v>
       </c>
       <c r="U65">
         <v>0.0518</v>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>11.26596521333363</v>
+        <v>11.0899345068753</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6767,22 +6767,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1166654963796604</v>
+        <v>0.1164050242388616</v>
       </c>
       <c r="C66">
-        <v>13.95290595089992</v>
+        <v>13.70913506344952</v>
       </c>
       <c r="D66">
-        <v>31.39890595089992</v>
+        <v>31.45913506344952</v>
       </c>
       <c r="E66">
-        <v>3.856</v>
+        <v>4.159999999999998</v>
       </c>
       <c r="F66">
-        <v>19.456</v>
+        <v>19.76</v>
       </c>
       <c r="G66">
         <v>2.01</v>
@@ -6803,28 +6803,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M66">
-        <v>1.0078208</v>
+        <v>1.023568</v>
       </c>
       <c r="N66">
-        <v>10.16884586666667</v>
+        <v>10.15309866666667</v>
       </c>
       <c r="O66">
-        <v>2.338834549333333</v>
+        <v>2.335212693333333</v>
       </c>
       <c r="P66">
-        <v>7.830011317333334</v>
+        <v>7.817885973333333</v>
       </c>
       <c r="Q66">
-        <v>8.870011317333333</v>
+        <v>8.857885973333333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2531623788323901</v>
+        <v>0.2585117835396047</v>
       </c>
       <c r="T66">
-        <v>3.207830051397929</v>
+        <v>3.290583640903974</v>
       </c>
       <c r="U66">
         <v>0.0518</v>
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>11.0899345068753</v>
+        <v>10.91932012984645</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6849,22 +6849,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1164050242388616</v>
+        <v>0.1161445520980628</v>
       </c>
       <c r="C67">
-        <v>13.70913506344952</v>
+        <v>13.46559568200795</v>
       </c>
       <c r="D67">
-        <v>31.45913506344952</v>
+        <v>31.51959568200795</v>
       </c>
       <c r="E67">
-        <v>4.159999999999998</v>
+        <v>4.464</v>
       </c>
       <c r="F67">
-        <v>19.76</v>
+        <v>20.064</v>
       </c>
       <c r="G67">
         <v>2.01</v>
@@ -6885,28 +6885,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M67">
-        <v>1.023568</v>
+        <v>1.0393152</v>
       </c>
       <c r="N67">
-        <v>10.15309866666667</v>
+        <v>10.13735146666667</v>
       </c>
       <c r="O67">
-        <v>2.335212693333333</v>
+        <v>2.331590837333333</v>
       </c>
       <c r="P67">
-        <v>7.817885973333333</v>
+        <v>7.805760629333331</v>
       </c>
       <c r="Q67">
-        <v>8.857885973333333</v>
+        <v>8.845760629333331</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2585117835396047</v>
+        <v>0.2641758591119496</v>
       </c>
       <c r="T67">
-        <v>3.290583640903974</v>
+        <v>3.378205088616256</v>
       </c>
       <c r="U67">
         <v>0.0518</v>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>10.91932012984645</v>
+        <v>10.75387588545483</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6931,22 +6931,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1161445520980628</v>
+        <v>0.115884079957264</v>
       </c>
       <c r="C68">
-        <v>13.46559568200795</v>
+        <v>13.22228914392435</v>
       </c>
       <c r="D68">
-        <v>31.51959568200795</v>
+        <v>31.58028914392434</v>
       </c>
       <c r="E68">
-        <v>4.464</v>
+        <v>4.767999999999999</v>
       </c>
       <c r="F68">
-        <v>20.064</v>
+        <v>20.368</v>
       </c>
       <c r="G68">
         <v>2.01</v>
@@ -6967,28 +6967,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M68">
-        <v>1.0393152</v>
+        <v>1.0550624</v>
       </c>
       <c r="N68">
-        <v>10.13735146666667</v>
+        <v>10.12160426666667</v>
       </c>
       <c r="O68">
-        <v>2.331590837333333</v>
+        <v>2.327968981333333</v>
       </c>
       <c r="P68">
-        <v>7.805760629333331</v>
+        <v>7.793635285333332</v>
       </c>
       <c r="Q68">
-        <v>8.845760629333331</v>
+        <v>8.833635285333333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2641758591119496</v>
+        <v>0.2701832119917092</v>
       </c>
       <c r="T68">
-        <v>3.378205088616256</v>
+        <v>3.471136927098979</v>
       </c>
       <c r="U68">
         <v>0.0518</v>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>10.75387588545483</v>
+        <v>10.59337027522416</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7013,22 +7013,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.115884079957264</v>
+        <v>0.1156236078164652</v>
       </c>
       <c r="C69">
-        <v>13.22228914392435</v>
+        <v>12.97921679686835</v>
       </c>
       <c r="D69">
-        <v>31.58028914392434</v>
+        <v>31.64121679686835</v>
       </c>
       <c r="E69">
-        <v>4.767999999999999</v>
+        <v>5.072000000000001</v>
       </c>
       <c r="F69">
-        <v>20.368</v>
+        <v>20.672</v>
       </c>
       <c r="G69">
         <v>2.01</v>
@@ -7049,28 +7049,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M69">
-        <v>1.0550624</v>
+        <v>1.0708096</v>
       </c>
       <c r="N69">
-        <v>10.12160426666667</v>
+        <v>10.10585706666667</v>
       </c>
       <c r="O69">
-        <v>2.327968981333333</v>
+        <v>2.324347125333333</v>
       </c>
       <c r="P69">
-        <v>7.793635285333332</v>
+        <v>7.781509941333333</v>
       </c>
       <c r="Q69">
-        <v>8.833635285333333</v>
+        <v>8.821509941333332</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2701832119917092</v>
+        <v>0.2765660244264539</v>
       </c>
       <c r="T69">
-        <v>3.471136927098979</v>
+        <v>3.569877005486874</v>
       </c>
       <c r="U69">
         <v>0.0518</v>
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>10.59337027522416</v>
+        <v>10.43758541823557</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7095,22 +7095,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1156236078164652</v>
+        <v>0.1153631356756664</v>
       </c>
       <c r="C70">
-        <v>12.97921679686835</v>
+        <v>12.73637999892996</v>
       </c>
       <c r="D70">
-        <v>31.64121679686835</v>
+        <v>31.70237999892996</v>
       </c>
       <c r="E70">
-        <v>5.072000000000001</v>
+        <v>5.375999999999999</v>
       </c>
       <c r="F70">
-        <v>20.672</v>
+        <v>20.976</v>
       </c>
       <c r="G70">
         <v>2.01</v>
@@ -7131,28 +7131,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M70">
-        <v>1.0708096</v>
+        <v>1.0865568</v>
       </c>
       <c r="N70">
-        <v>10.10585706666667</v>
+        <v>10.09010986666667</v>
       </c>
       <c r="O70">
-        <v>2.324347125333333</v>
+        <v>2.320725269333333</v>
       </c>
       <c r="P70">
-        <v>7.781509941333333</v>
+        <v>7.769384597333332</v>
       </c>
       <c r="Q70">
-        <v>8.821509941333332</v>
+        <v>8.809384597333331</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2765660244264539</v>
+        <v>0.2833606312118273</v>
       </c>
       <c r="T70">
-        <v>3.569877005486874</v>
+        <v>3.674987411512696</v>
       </c>
       <c r="U70">
         <v>0.0518</v>
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>10.43758541823557</v>
+        <v>10.2863160643481</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7177,22 +7177,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1153631356756664</v>
+        <v>0.1151026635348676</v>
       </c>
       <c r="C71">
-        <v>12.73637999892996</v>
+        <v>12.49378011872036</v>
       </c>
       <c r="D71">
-        <v>31.70237999892996</v>
+        <v>31.76378011872036</v>
       </c>
       <c r="E71">
-        <v>5.375999999999999</v>
+        <v>5.680000000000001</v>
       </c>
       <c r="F71">
-        <v>20.976</v>
+        <v>21.28</v>
       </c>
       <c r="G71">
         <v>2.01</v>
@@ -7213,28 +7213,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M71">
-        <v>1.0865568</v>
+        <v>1.102304</v>
       </c>
       <c r="N71">
-        <v>10.09010986666667</v>
+        <v>10.07436266666667</v>
       </c>
       <c r="O71">
-        <v>2.320725269333333</v>
+        <v>2.317103413333333</v>
       </c>
       <c r="P71">
-        <v>7.769384597333332</v>
+        <v>7.757259253333332</v>
       </c>
       <c r="Q71">
-        <v>8.809384597333331</v>
+        <v>8.797259253333333</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2833606312118273</v>
+        <v>0.2906082117828921</v>
       </c>
       <c r="T71">
-        <v>3.674987411512696</v>
+        <v>3.787105177940239</v>
       </c>
       <c r="U71">
         <v>0.0518</v>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>10.2863160643481</v>
+        <v>10.13936869200027</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7259,22 +7259,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1151026635348676</v>
+        <v>0.1148421913940688</v>
       </c>
       <c r="C72">
-        <v>12.49378011872036</v>
+        <v>12.25141853547405</v>
       </c>
       <c r="D72">
-        <v>31.76378011872036</v>
+        <v>31.82541853547405</v>
       </c>
       <c r="E72">
-        <v>5.680000000000001</v>
+        <v>5.984</v>
       </c>
       <c r="F72">
-        <v>21.28</v>
+        <v>21.584</v>
       </c>
       <c r="G72">
         <v>2.01</v>
@@ -7295,28 +7295,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M72">
-        <v>1.102304</v>
+        <v>1.1180512</v>
       </c>
       <c r="N72">
-        <v>10.07436266666667</v>
+        <v>10.05861546666667</v>
       </c>
       <c r="O72">
-        <v>2.317103413333333</v>
+        <v>2.313481557333333</v>
       </c>
       <c r="P72">
-        <v>7.757259253333332</v>
+        <v>7.745133909333333</v>
       </c>
       <c r="Q72">
-        <v>8.797259253333333</v>
+        <v>8.785133909333332</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2906082117828921</v>
+        <v>0.2983556254967892</v>
       </c>
       <c r="T72">
-        <v>3.787105177940239</v>
+        <v>3.906955204121408</v>
       </c>
       <c r="U72">
         <v>0.0518</v>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>10.13936869200027</v>
+        <v>9.996560682253786</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7341,22 +7341,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1148421913940688</v>
+        <v>0.11458171925327</v>
       </c>
       <c r="C73">
-        <v>12.25141853547405</v>
+        <v>12.00929663915208</v>
       </c>
       <c r="D73">
-        <v>31.82541853547405</v>
+        <v>31.88729663915208</v>
       </c>
       <c r="E73">
-        <v>5.984</v>
+        <v>6.287999999999998</v>
       </c>
       <c r="F73">
-        <v>21.584</v>
+        <v>21.888</v>
       </c>
       <c r="G73">
         <v>2.01</v>
@@ -7377,28 +7377,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M73">
-        <v>1.1180512</v>
+        <v>1.1337984</v>
       </c>
       <c r="N73">
-        <v>10.05861546666667</v>
+        <v>10.04286826666667</v>
       </c>
       <c r="O73">
-        <v>2.313481557333333</v>
+        <v>2.309859701333333</v>
       </c>
       <c r="P73">
-        <v>7.745133909333333</v>
+        <v>7.733008565333333</v>
       </c>
       <c r="Q73">
-        <v>8.785133909333332</v>
+        <v>8.773008565333333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2983556254967891</v>
+        <v>0.3066564259045358</v>
       </c>
       <c r="T73">
-        <v>3.906955204121406</v>
+        <v>4.035365946458371</v>
       </c>
       <c r="U73">
         <v>0.0518</v>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>9.996560682253786</v>
+        <v>9.857719561666931</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7423,22 +7423,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.11458171925327</v>
+        <v>0.1152768171124712</v>
       </c>
       <c r="C74">
-        <v>12.00929663915208</v>
+        <v>11.54070123503279</v>
       </c>
       <c r="D74">
-        <v>31.88729663915208</v>
+        <v>31.72270123503279</v>
       </c>
       <c r="E74">
-        <v>6.287999999999998</v>
+        <v>6.592000000000001</v>
       </c>
       <c r="F74">
-        <v>21.888</v>
+        <v>22.192</v>
       </c>
       <c r="G74">
         <v>2.01</v>
@@ -7459,45 +7459,45 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M74">
-        <v>1.1337984</v>
+        <v>1.187272</v>
       </c>
       <c r="N74">
-        <v>10.04286826666667</v>
+        <v>9.989394666666666</v>
       </c>
       <c r="O74">
-        <v>2.309859701333333</v>
+        <v>2.297560773333333</v>
       </c>
       <c r="P74">
-        <v>7.733008565333333</v>
+        <v>7.691833893333333</v>
       </c>
       <c r="Q74">
-        <v>8.773008565333333</v>
+        <v>8.731833893333333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3066564259045358</v>
+        <v>0.3155721004165601</v>
       </c>
       <c r="T74">
-        <v>4.035365946458371</v>
+        <v>4.173288595635111</v>
       </c>
       <c r="U74">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V74">
         <v>0.23</v>
       </c>
       <c r="W74">
-        <v>0.039886</v>
+        <v>0.041195</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>9.857719561666931</v>
+        <v>9.413737262115729</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7505,22 +7505,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1152768171124712</v>
+        <v>0.1150294349716724</v>
       </c>
       <c r="C75">
-        <v>11.54070123503279</v>
+        <v>11.29508486765362</v>
       </c>
       <c r="D75">
-        <v>31.72270123503279</v>
+        <v>31.78108486765361</v>
       </c>
       <c r="E75">
-        <v>6.592000000000001</v>
+        <v>6.895999999999999</v>
       </c>
       <c r="F75">
-        <v>22.192</v>
+        <v>22.496</v>
       </c>
       <c r="G75">
         <v>2.01</v>
@@ -7541,28 +7541,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M75">
-        <v>1.187272</v>
+        <v>1.203536</v>
       </c>
       <c r="N75">
-        <v>9.989394666666666</v>
+        <v>9.973130666666666</v>
       </c>
       <c r="O75">
-        <v>2.297560773333333</v>
+        <v>2.293820053333333</v>
       </c>
       <c r="P75">
-        <v>7.691833893333333</v>
+        <v>7.679310613333333</v>
       </c>
       <c r="Q75">
-        <v>8.731833893333333</v>
+        <v>8.719310613333333</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3155721004165601</v>
+        <v>0.3251735960448939</v>
       </c>
       <c r="T75">
-        <v>4.173288595635111</v>
+        <v>4.321820679363908</v>
       </c>
       <c r="U75">
         <v>0.0535</v>
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>9.413737262115729</v>
+        <v>9.286524596411462</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7587,22 +7587,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1150294349716724</v>
+        <v>0.1147820528308736</v>
       </c>
       <c r="C76">
-        <v>11.29508486765362</v>
+        <v>11.04968379931236</v>
       </c>
       <c r="D76">
-        <v>31.78108486765361</v>
+        <v>31.83968379931236</v>
       </c>
       <c r="E76">
-        <v>6.895999999999999</v>
+        <v>7.199999999999998</v>
       </c>
       <c r="F76">
-        <v>22.496</v>
+        <v>22.8</v>
       </c>
       <c r="G76">
         <v>2.01</v>
@@ -7623,28 +7623,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M76">
-        <v>1.203536</v>
+        <v>1.2198</v>
       </c>
       <c r="N76">
-        <v>9.973130666666666</v>
+        <v>9.956866666666667</v>
       </c>
       <c r="O76">
-        <v>2.293820053333333</v>
+        <v>2.290079333333333</v>
       </c>
       <c r="P76">
-        <v>7.679310613333333</v>
+        <v>7.666787333333334</v>
       </c>
       <c r="Q76">
-        <v>8.719310613333333</v>
+        <v>8.706787333333335</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3251735960448939</v>
+        <v>0.3355432113234945</v>
       </c>
       <c r="T76">
-        <v>4.321820679363908</v>
+        <v>4.48223532979101</v>
       </c>
       <c r="U76">
         <v>0.0535</v>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>9.286524596411462</v>
+        <v>9.162704268459311</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7669,22 +7669,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1147820528308736</v>
+        <v>0.1145346706900748</v>
       </c>
       <c r="C77">
-        <v>11.04968379931236</v>
+        <v>10.80449922313368</v>
       </c>
       <c r="D77">
-        <v>31.83968379931236</v>
+        <v>31.89849922313368</v>
       </c>
       <c r="E77">
-        <v>7.199999999999998</v>
+        <v>7.504</v>
       </c>
       <c r="F77">
-        <v>22.8</v>
+        <v>23.104</v>
       </c>
       <c r="G77">
         <v>2.01</v>
@@ -7705,28 +7705,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M77">
-        <v>1.2198</v>
+        <v>1.236064</v>
       </c>
       <c r="N77">
-        <v>9.956866666666667</v>
+        <v>9.940602666666667</v>
       </c>
       <c r="O77">
-        <v>2.290079333333333</v>
+        <v>2.286338613333334</v>
       </c>
       <c r="P77">
-        <v>7.666787333333334</v>
+        <v>7.654264053333334</v>
       </c>
       <c r="Q77">
-        <v>8.706787333333335</v>
+        <v>8.694264053333335</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3355432113234945</v>
+        <v>0.346776961208645</v>
       </c>
       <c r="T77">
-        <v>4.48223532979101</v>
+        <v>4.656017867753702</v>
       </c>
       <c r="U77">
         <v>0.0535</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>9.162704268459311</v>
+        <v>9.04214237019011</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7751,22 +7751,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1145346706900748</v>
+        <v>0.114287288549276</v>
       </c>
       <c r="C78">
-        <v>10.80449922313368</v>
+        <v>10.55953234107453</v>
       </c>
       <c r="D78">
-        <v>31.89849922313368</v>
+        <v>31.95753234107453</v>
       </c>
       <c r="E78">
-        <v>7.504</v>
+        <v>7.807999999999998</v>
       </c>
       <c r="F78">
-        <v>23.104</v>
+        <v>23.408</v>
       </c>
       <c r="G78">
         <v>2.01</v>
@@ -7787,28 +7787,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M78">
-        <v>1.236064</v>
+        <v>1.252328</v>
       </c>
       <c r="N78">
-        <v>9.940602666666667</v>
+        <v>9.924338666666666</v>
       </c>
       <c r="O78">
-        <v>2.286338613333334</v>
+        <v>2.282597893333333</v>
       </c>
       <c r="P78">
-        <v>7.654264053333334</v>
+        <v>7.641740773333332</v>
       </c>
       <c r="Q78">
-        <v>8.694264053333335</v>
+        <v>8.681740773333331</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.346776961208645</v>
+        <v>0.3589875589098958</v>
       </c>
       <c r="T78">
-        <v>4.656017867753702</v>
+        <v>4.84491193075663</v>
       </c>
       <c r="U78">
         <v>0.0535</v>
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>9.04214237019011</v>
+        <v>8.924711949798029</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7833,22 +7833,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.114287288549276</v>
+        <v>0.1140399064084772</v>
       </c>
       <c r="C79">
-        <v>10.55953234107453</v>
+        <v>10.31478436400595</v>
       </c>
       <c r="D79">
-        <v>31.95753234107453</v>
+        <v>32.01678436400595</v>
       </c>
       <c r="E79">
-        <v>7.807999999999998</v>
+        <v>8.112</v>
       </c>
       <c r="F79">
-        <v>23.408</v>
+        <v>23.712</v>
       </c>
       <c r="G79">
         <v>2.01</v>
@@ -7869,28 +7869,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M79">
-        <v>1.252328</v>
+        <v>1.268592</v>
       </c>
       <c r="N79">
-        <v>9.924338666666666</v>
+        <v>9.908074666666666</v>
       </c>
       <c r="O79">
-        <v>2.282597893333333</v>
+        <v>2.278857173333333</v>
       </c>
       <c r="P79">
-        <v>7.641740773333332</v>
+        <v>7.629217493333332</v>
       </c>
       <c r="Q79">
-        <v>8.681740773333331</v>
+        <v>8.669217493333331</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3589875589098958</v>
+        <v>0.3723082109476237</v>
       </c>
       <c r="T79">
-        <v>4.84491193075663</v>
+        <v>5.050978181305277</v>
       </c>
       <c r="U79">
         <v>0.0535</v>
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>8.924711949798029</v>
+        <v>8.810292565826259</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7915,22 +7915,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1140399064084772</v>
+        <v>0.1137925242676784</v>
       </c>
       <c r="C80">
-        <v>10.31478436400595</v>
+        <v>10.07025651179592</v>
       </c>
       <c r="D80">
-        <v>32.01678436400595</v>
+        <v>32.07625651179592</v>
       </c>
       <c r="E80">
-        <v>8.112</v>
+        <v>8.415999999999999</v>
       </c>
       <c r="F80">
-        <v>23.712</v>
+        <v>24.016</v>
       </c>
       <c r="G80">
         <v>2.01</v>
@@ -7951,28 +7951,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M80">
-        <v>1.268592</v>
+        <v>1.284856</v>
       </c>
       <c r="N80">
-        <v>9.908074666666666</v>
+        <v>9.891810666666666</v>
       </c>
       <c r="O80">
-        <v>2.278857173333333</v>
+        <v>2.275116453333333</v>
       </c>
       <c r="P80">
-        <v>7.629217493333332</v>
+        <v>7.616694213333333</v>
       </c>
       <c r="Q80">
-        <v>8.669217493333331</v>
+        <v>8.656694213333333</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3723082109476237</v>
+        <v>0.3868974965127543</v>
       </c>
       <c r="T80">
-        <v>5.050978181305277</v>
+        <v>5.276669789049034</v>
       </c>
       <c r="U80">
         <v>0.0535</v>
@@ -7989,7 +7989,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>8.810292565826259</v>
+        <v>8.698769875119599</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7997,22 +7997,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1137925242676784</v>
+        <v>0.1135451421268796</v>
       </c>
       <c r="C81">
-        <v>10.07025651179592</v>
+        <v>9.82595001339304</v>
       </c>
       <c r="D81">
-        <v>32.07625651179592</v>
+        <v>32.13595001339304</v>
       </c>
       <c r="E81">
-        <v>8.415999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="F81">
-        <v>24.016</v>
+        <v>24.32</v>
       </c>
       <c r="G81">
         <v>2.01</v>
@@ -8033,28 +8033,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M81">
-        <v>1.284856</v>
+        <v>1.30112</v>
       </c>
       <c r="N81">
-        <v>9.891810666666666</v>
+        <v>9.875546666666665</v>
       </c>
       <c r="O81">
-        <v>2.275116453333333</v>
+        <v>2.271375733333333</v>
       </c>
       <c r="P81">
-        <v>7.616694213333333</v>
+        <v>7.604170933333332</v>
       </c>
       <c r="Q81">
-        <v>8.656694213333333</v>
+        <v>8.644170933333331</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3868974965127543</v>
+        <v>0.4029457106343981</v>
       </c>
       <c r="T81">
-        <v>5.276669789049034</v>
+        <v>5.524930557567167</v>
       </c>
       <c r="U81">
         <v>0.0535</v>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>8.698769875119599</v>
+        <v>8.590035251680602</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8079,22 +8079,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1135451421268796</v>
+        <v>0.1132977599860808</v>
       </c>
       <c r="C82">
-        <v>9.82595001339304</v>
+        <v>9.581866106911217</v>
       </c>
       <c r="D82">
-        <v>32.13595001339304</v>
+        <v>32.19586610691122</v>
       </c>
       <c r="E82">
-        <v>8.720000000000001</v>
+        <v>9.023999999999999</v>
       </c>
       <c r="F82">
-        <v>24.32</v>
+        <v>24.624</v>
       </c>
       <c r="G82">
         <v>2.01</v>
@@ -8115,28 +8115,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M82">
-        <v>1.30112</v>
+        <v>1.317384</v>
       </c>
       <c r="N82">
-        <v>9.875546666666665</v>
+        <v>9.859282666666665</v>
       </c>
       <c r="O82">
-        <v>2.271375733333333</v>
+        <v>2.267635013333333</v>
       </c>
       <c r="P82">
-        <v>7.604170933333332</v>
+        <v>7.591647653333332</v>
       </c>
       <c r="Q82">
-        <v>8.644170933333331</v>
+        <v>8.631647653333332</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4029457106343981</v>
+        <v>0.420683210453057</v>
       </c>
       <c r="T82">
-        <v>5.524930557567167</v>
+        <v>5.799324038560893</v>
       </c>
       <c r="U82">
         <v>0.0535</v>
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>8.590035251680602</v>
+        <v>8.483985433758619</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8161,22 +8161,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1132977599860808</v>
+        <v>0.113050377845282</v>
       </c>
       <c r="C83">
-        <v>9.581866106911217</v>
+        <v>9.338006039715221</v>
       </c>
       <c r="D83">
-        <v>32.19586610691122</v>
+        <v>32.25600603971522</v>
       </c>
       <c r="E83">
-        <v>9.023999999999999</v>
+        <v>9.328000000000001</v>
       </c>
       <c r="F83">
-        <v>24.624</v>
+        <v>24.928</v>
       </c>
       <c r="G83">
         <v>2.01</v>
@@ -8197,28 +8197,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M83">
-        <v>1.317384</v>
+        <v>1.333648</v>
       </c>
       <c r="N83">
-        <v>9.859282666666665</v>
+        <v>9.843018666666666</v>
       </c>
       <c r="O83">
-        <v>2.267635013333333</v>
+        <v>2.263894293333333</v>
       </c>
       <c r="P83">
-        <v>7.591647653333332</v>
+        <v>7.579124373333332</v>
       </c>
       <c r="Q83">
-        <v>8.631647653333332</v>
+        <v>8.619124373333332</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.420683210453057</v>
+        <v>0.4403915435849001</v>
       </c>
       <c r="T83">
-        <v>5.799324038560893</v>
+        <v>6.104205684109477</v>
       </c>
       <c r="U83">
         <v>0.0535</v>
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>8.483985433758619</v>
+        <v>8.380522196761564</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8243,22 +8243,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.113050377845282</v>
+        <v>0.1128029957044832</v>
       </c>
       <c r="C84">
-        <v>9.338006039715221</v>
+        <v>9.094371068507293</v>
       </c>
       <c r="D84">
-        <v>32.25600603971522</v>
+        <v>32.31637106850729</v>
       </c>
       <c r="E84">
-        <v>9.328000000000001</v>
+        <v>9.632</v>
       </c>
       <c r="F84">
-        <v>24.928</v>
+        <v>25.232</v>
       </c>
       <c r="G84">
         <v>2.01</v>
@@ -8279,28 +8279,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M84">
-        <v>1.333648</v>
+        <v>1.349912</v>
       </c>
       <c r="N84">
-        <v>9.843018666666666</v>
+        <v>9.826754666666666</v>
       </c>
       <c r="O84">
-        <v>2.263894293333333</v>
+        <v>2.260153573333333</v>
       </c>
       <c r="P84">
-        <v>7.579124373333332</v>
+        <v>7.566601093333333</v>
       </c>
       <c r="Q84">
-        <v>8.619124373333332</v>
+        <v>8.606601093333332</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4403915435849001</v>
+        <v>0.462418504144019</v>
       </c>
       <c r="T84">
-        <v>6.104205684109477</v>
+        <v>6.44495575854613</v>
       </c>
       <c r="U84">
         <v>0.0535</v>
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>8.380522196761564</v>
+        <v>8.279552049812629</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8325,22 +8325,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1128029957044832</v>
+        <v>0.1125556135636844</v>
       </c>
       <c r="C85">
-        <v>9.094371068507293</v>
+        <v>8.850962459414639</v>
       </c>
       <c r="D85">
-        <v>32.31637106850729</v>
+        <v>32.37696245941464</v>
       </c>
       <c r="E85">
-        <v>9.632</v>
+        <v>9.936000000000002</v>
       </c>
       <c r="F85">
-        <v>25.232</v>
+        <v>25.536</v>
       </c>
       <c r="G85">
         <v>2.01</v>
@@ -8361,28 +8361,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M85">
-        <v>1.349912</v>
+        <v>1.366176</v>
       </c>
       <c r="N85">
-        <v>9.826754666666666</v>
+        <v>9.810490666666666</v>
       </c>
       <c r="O85">
-        <v>2.260153573333333</v>
+        <v>2.256412853333333</v>
       </c>
       <c r="P85">
-        <v>7.566601093333333</v>
+        <v>7.554077813333333</v>
       </c>
       <c r="Q85">
-        <v>8.606601093333332</v>
+        <v>8.594077813333332</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.462418504144019</v>
+        <v>0.4871988347730277</v>
       </c>
       <c r="T85">
-        <v>6.44495575854613</v>
+        <v>6.828299592287365</v>
       </c>
       <c r="U85">
         <v>0.0535</v>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>8.279552049812629</v>
+        <v>8.180985953981526</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8407,22 +8407,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1125556135636844</v>
+        <v>0.1123082314228856</v>
       </c>
       <c r="C86">
-        <v>8.850962459414642</v>
+        <v>8.607781488078007</v>
       </c>
       <c r="D86">
-        <v>32.37696245941464</v>
+        <v>32.43778148807801</v>
       </c>
       <c r="E86">
-        <v>9.935999999999998</v>
+        <v>10.24</v>
       </c>
       <c r="F86">
-        <v>25.536</v>
+        <v>25.84</v>
       </c>
       <c r="G86">
         <v>2.01</v>
@@ -8443,28 +8443,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M86">
-        <v>1.366176</v>
+        <v>1.38244</v>
       </c>
       <c r="N86">
-        <v>9.810490666666666</v>
+        <v>9.794226666666667</v>
       </c>
       <c r="O86">
-        <v>2.256412853333333</v>
+        <v>2.252672133333333</v>
       </c>
       <c r="P86">
-        <v>7.554077813333333</v>
+        <v>7.541554533333334</v>
       </c>
       <c r="Q86">
-        <v>8.594077813333332</v>
+        <v>8.581554533333334</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4871988347730274</v>
+        <v>0.5152832094859039</v>
       </c>
       <c r="T86">
-        <v>6.828299592287361</v>
+        <v>7.262755937194093</v>
       </c>
       <c r="U86">
         <v>0.0535</v>
@@ -8481,7 +8481,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>8.180985953981528</v>
+        <v>8.084739060405274</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8489,22 +8489,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1123082314228856</v>
+        <v>0.1120608492820868</v>
       </c>
       <c r="C87">
-        <v>8.607781488078007</v>
+        <v>8.36482943974115</v>
       </c>
       <c r="D87">
-        <v>32.43778148807801</v>
+        <v>32.49882943974115</v>
       </c>
       <c r="E87">
-        <v>10.24</v>
+        <v>10.544</v>
       </c>
       <c r="F87">
-        <v>25.84</v>
+        <v>26.144</v>
       </c>
       <c r="G87">
         <v>2.01</v>
@@ -8525,28 +8525,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M87">
-        <v>1.38244</v>
+        <v>1.398704</v>
       </c>
       <c r="N87">
-        <v>9.794226666666667</v>
+        <v>9.777962666666665</v>
       </c>
       <c r="O87">
-        <v>2.252672133333333</v>
+        <v>2.248931413333333</v>
       </c>
       <c r="P87">
-        <v>7.541554533333334</v>
+        <v>7.529031253333333</v>
       </c>
       <c r="Q87">
-        <v>8.581554533333334</v>
+        <v>8.569031253333332</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5152832094859039</v>
+        <v>0.5473796377291912</v>
       </c>
       <c r="T87">
-        <v>7.262755937194093</v>
+        <v>7.759277474230357</v>
       </c>
       <c r="U87">
         <v>0.0535</v>
@@ -8563,7 +8563,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>8.084739060405274</v>
+        <v>7.99073046667963</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8571,22 +8571,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1120608492820868</v>
+        <v>0.111813467141288</v>
       </c>
       <c r="C88">
-        <v>8.36482943974115</v>
+        <v>8.12210760934137</v>
       </c>
       <c r="D88">
-        <v>32.49882943974115</v>
+        <v>32.56010760934137</v>
       </c>
       <c r="E88">
-        <v>10.544</v>
+        <v>10.848</v>
       </c>
       <c r="F88">
-        <v>26.144</v>
+        <v>26.448</v>
       </c>
       <c r="G88">
         <v>2.01</v>
@@ -8607,28 +8607,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M88">
-        <v>1.398704</v>
+        <v>1.414968</v>
       </c>
       <c r="N88">
-        <v>9.777962666666665</v>
+        <v>9.761698666666666</v>
       </c>
       <c r="O88">
-        <v>2.248931413333333</v>
+        <v>2.245190693333333</v>
       </c>
       <c r="P88">
-        <v>7.529031253333333</v>
+        <v>7.516507973333333</v>
       </c>
       <c r="Q88">
-        <v>8.569031253333332</v>
+        <v>8.556507973333332</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5473796377291912</v>
+        <v>0.5844139780099076</v>
       </c>
       <c r="T88">
-        <v>7.759277474230357</v>
+        <v>8.332186940041433</v>
       </c>
       <c r="U88">
         <v>0.0535</v>
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>7.99073046667963</v>
+        <v>7.898882990051129</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8653,22 +8653,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.111813467141288</v>
+        <v>0.1115660850004892</v>
       </c>
       <c r="C89">
-        <v>8.12210760934137</v>
+        <v>7.879617301601126</v>
       </c>
       <c r="D89">
-        <v>32.56010760934137</v>
+        <v>32.62161730160113</v>
       </c>
       <c r="E89">
-        <v>10.848</v>
+        <v>11.152</v>
       </c>
       <c r="F89">
-        <v>26.448</v>
+        <v>26.752</v>
       </c>
       <c r="G89">
         <v>2.01</v>
@@ -8689,28 +8689,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M89">
-        <v>1.414968</v>
+        <v>1.431232</v>
       </c>
       <c r="N89">
-        <v>9.761698666666666</v>
+        <v>9.745434666666666</v>
       </c>
       <c r="O89">
-        <v>2.245190693333333</v>
+        <v>2.241449973333333</v>
       </c>
       <c r="P89">
-        <v>7.516507973333333</v>
+        <v>7.503984693333333</v>
       </c>
       <c r="Q89">
-        <v>8.556507973333332</v>
+        <v>8.543984693333332</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5844139780099076</v>
+        <v>0.6276207083374099</v>
       </c>
       <c r="T89">
-        <v>8.332186940041433</v>
+        <v>9.000581316821021</v>
       </c>
       <c r="U89">
         <v>0.0535</v>
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>7.898882990051129</v>
+        <v>7.809122956073276</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8735,22 +8735,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1115660850004892</v>
+        <v>0.1113187028596904</v>
       </c>
       <c r="C90">
-        <v>7.879617301601126</v>
+        <v>7.637359831120627</v>
       </c>
       <c r="D90">
-        <v>32.62161730160113</v>
+        <v>32.68335983112063</v>
       </c>
       <c r="E90">
-        <v>11.152</v>
+        <v>11.456</v>
       </c>
       <c r="F90">
-        <v>26.752</v>
+        <v>27.056</v>
       </c>
       <c r="G90">
         <v>2.01</v>
@@ -8771,28 +8771,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M90">
-        <v>1.431232</v>
+        <v>1.447496</v>
       </c>
       <c r="N90">
-        <v>9.745434666666666</v>
+        <v>9.729170666666667</v>
       </c>
       <c r="O90">
-        <v>2.241449973333333</v>
+        <v>2.237709253333334</v>
       </c>
       <c r="P90">
-        <v>7.503984693333333</v>
+        <v>7.491461413333333</v>
       </c>
       <c r="Q90">
-        <v>8.543984693333332</v>
+        <v>8.531461413333332</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6276207083374099</v>
+        <v>0.6786832078153671</v>
       </c>
       <c r="T90">
-        <v>9.000581316821021</v>
+        <v>9.79050194392417</v>
       </c>
       <c r="U90">
         <v>0.0535</v>
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>7.809122956073276</v>
+        <v>7.721380001510656</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8817,22 +8817,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1113187028596904</v>
+        <v>0.1110713207188916</v>
       </c>
       <c r="C91">
-        <v>7.637359831120627</v>
+        <v>7.395336522471396</v>
       </c>
       <c r="D91">
-        <v>32.68335983112063</v>
+        <v>32.7453365224714</v>
       </c>
       <c r="E91">
-        <v>11.456</v>
+        <v>11.76</v>
       </c>
       <c r="F91">
-        <v>27.056</v>
+        <v>27.36</v>
       </c>
       <c r="G91">
         <v>2.01</v>
@@ -8853,28 +8853,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M91">
-        <v>1.447496</v>
+        <v>1.46376</v>
       </c>
       <c r="N91">
-        <v>9.729170666666667</v>
+        <v>9.712906666666665</v>
       </c>
       <c r="O91">
-        <v>2.237709253333334</v>
+        <v>2.233968533333333</v>
       </c>
       <c r="P91">
-        <v>7.491461413333333</v>
+        <v>7.478938133333332</v>
       </c>
       <c r="Q91">
-        <v>8.531461413333332</v>
+        <v>8.518938133333332</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6786832078153671</v>
+        <v>0.7399582071889158</v>
       </c>
       <c r="T91">
-        <v>9.79050194392417</v>
+        <v>10.73840669644795</v>
       </c>
       <c r="U91">
         <v>0.0535</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>7.721380001510656</v>
+        <v>7.635586890382758</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8899,22 +8899,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1110713207188916</v>
+        <v>0.1113844985780927</v>
       </c>
       <c r="C92">
-        <v>7.395336522471396</v>
+        <v>7.012915494880229</v>
       </c>
       <c r="D92">
-        <v>32.7453365224714</v>
+        <v>32.66691549488023</v>
       </c>
       <c r="E92">
-        <v>11.76</v>
+        <v>12.064</v>
       </c>
       <c r="F92">
-        <v>27.36</v>
+        <v>27.664</v>
       </c>
       <c r="G92">
         <v>2.01</v>
@@ -8935,45 +8935,45 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M92">
-        <v>1.46376</v>
+        <v>1.5021552</v>
       </c>
       <c r="N92">
-        <v>9.712906666666665</v>
+        <v>9.674511466666665</v>
       </c>
       <c r="O92">
-        <v>2.233968533333333</v>
+        <v>2.225137637333333</v>
       </c>
       <c r="P92">
-        <v>7.478938133333332</v>
+        <v>7.449373829333332</v>
       </c>
       <c r="Q92">
-        <v>8.518938133333332</v>
+        <v>8.489373829333331</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7399582071889158</v>
+        <v>0.8148498730899197</v>
       </c>
       <c r="T92">
-        <v>10.73840669644795</v>
+        <v>11.89695694953257</v>
       </c>
       <c r="U92">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V92">
         <v>0.23</v>
       </c>
       <c r="W92">
-        <v>0.041195</v>
+        <v>0.041811</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y92">
-        <v>7.635586890382758</v>
+        <v>7.440420714628332</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8981,22 +8981,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1113844985780927</v>
+        <v>0.111143276437294</v>
       </c>
       <c r="C93">
-        <v>7.012915494880229</v>
+        <v>6.769285215839087</v>
       </c>
       <c r="D93">
-        <v>32.66691549488023</v>
+        <v>32.72728521583909</v>
       </c>
       <c r="E93">
-        <v>12.064</v>
+        <v>12.368</v>
       </c>
       <c r="F93">
-        <v>27.664</v>
+        <v>27.968</v>
       </c>
       <c r="G93">
         <v>2.01</v>
@@ -9017,28 +9017,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M93">
-        <v>1.5021552</v>
+        <v>1.5186624</v>
       </c>
       <c r="N93">
-        <v>9.674511466666665</v>
+        <v>9.658004266666666</v>
       </c>
       <c r="O93">
-        <v>2.225137637333333</v>
+        <v>2.221340981333333</v>
       </c>
       <c r="P93">
-        <v>7.449373829333332</v>
+        <v>7.436663285333332</v>
       </c>
       <c r="Q93">
-        <v>8.489373829333331</v>
+        <v>8.476663285333332</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8148498730899197</v>
+        <v>0.908464455466175</v>
       </c>
       <c r="T93">
-        <v>11.89695694953257</v>
+        <v>13.34514476588835</v>
       </c>
       <c r="U93">
         <v>0.0543</v>
@@ -9055,7 +9055,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>7.440420714628332</v>
+        <v>7.359546576425851</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9063,22 +9063,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.111143276437294</v>
+        <v>0.1109020542964952</v>
       </c>
       <c r="C94">
-        <v>6.769285215839087</v>
+        <v>6.525878481066279</v>
       </c>
       <c r="D94">
-        <v>32.72728521583909</v>
+        <v>32.78787848106628</v>
       </c>
       <c r="E94">
-        <v>12.368</v>
+        <v>12.672</v>
       </c>
       <c r="F94">
-        <v>27.968</v>
+        <v>28.272</v>
       </c>
       <c r="G94">
         <v>2.01</v>
@@ -9099,28 +9099,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M94">
-        <v>1.5186624</v>
+        <v>1.5351696</v>
       </c>
       <c r="N94">
-        <v>9.658004266666666</v>
+        <v>9.641497066666666</v>
       </c>
       <c r="O94">
-        <v>2.221340981333333</v>
+        <v>2.217544325333333</v>
       </c>
       <c r="P94">
-        <v>7.436663285333332</v>
+        <v>7.423952741333332</v>
       </c>
       <c r="Q94">
-        <v>8.476663285333332</v>
+        <v>8.463952741333333</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.908464455466175</v>
+        <v>1.028826061378503</v>
       </c>
       <c r="T94">
-        <v>13.34514476588835</v>
+        <v>15.20710052977434</v>
       </c>
       <c r="U94">
         <v>0.0543</v>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>7.359546576425851</v>
+        <v>7.280411667001918</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9145,22 +9145,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1109020542964952</v>
+        <v>0.1106608321556964</v>
       </c>
       <c r="C95">
-        <v>6.525878481066279</v>
+        <v>6.282696534514841</v>
       </c>
       <c r="D95">
-        <v>32.78787848106628</v>
+        <v>32.84869653451484</v>
       </c>
       <c r="E95">
-        <v>12.672</v>
+        <v>12.976</v>
       </c>
       <c r="F95">
-        <v>28.272</v>
+        <v>28.576</v>
       </c>
       <c r="G95">
         <v>2.01</v>
@@ -9181,28 +9181,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M95">
-        <v>1.5351696</v>
+        <v>1.5516768</v>
       </c>
       <c r="N95">
-        <v>9.641497066666666</v>
+        <v>9.624989866666667</v>
       </c>
       <c r="O95">
-        <v>2.217544325333333</v>
+        <v>2.213747669333333</v>
       </c>
       <c r="P95">
-        <v>7.423952741333332</v>
+        <v>7.411242197333333</v>
       </c>
       <c r="Q95">
-        <v>8.463952741333333</v>
+        <v>8.451242197333332</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.028826061378503</v>
+        <v>1.18930820259494</v>
       </c>
       <c r="T95">
-        <v>15.20710052977434</v>
+        <v>17.68970821495567</v>
       </c>
       <c r="U95">
         <v>0.0543</v>
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>7.280411667001918</v>
+        <v>7.202960479055088</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9227,22 +9227,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1106608321556964</v>
+        <v>0.1104196100148976</v>
       </c>
       <c r="C96">
-        <v>6.282696534514841</v>
+        <v>6.039740629384593</v>
       </c>
       <c r="D96">
-        <v>32.84869653451484</v>
+        <v>32.90974062938459</v>
       </c>
       <c r="E96">
-        <v>12.976</v>
+        <v>13.28</v>
       </c>
       <c r="F96">
-        <v>28.576</v>
+        <v>28.88</v>
       </c>
       <c r="G96">
         <v>2.01</v>
@@ -9263,28 +9263,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M96">
-        <v>1.5516768</v>
+        <v>1.568184</v>
       </c>
       <c r="N96">
-        <v>9.624989866666667</v>
+        <v>9.608482666666665</v>
       </c>
       <c r="O96">
-        <v>2.213747669333333</v>
+        <v>2.209951013333333</v>
       </c>
       <c r="P96">
-        <v>7.411242197333333</v>
+        <v>7.398531653333333</v>
       </c>
       <c r="Q96">
-        <v>8.451242197333332</v>
+        <v>8.438531653333332</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.18930820259494</v>
+        <v>1.413983200297953</v>
       </c>
       <c r="T96">
-        <v>17.68970821495567</v>
+        <v>21.16535897420954</v>
       </c>
       <c r="U96">
         <v>0.0543</v>
@@ -9301,7 +9301,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>7.202960479055088</v>
+        <v>7.127139842433455</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9309,22 +9309,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1104196100148976</v>
+        <v>0.1101783878740988</v>
       </c>
       <c r="C97">
-        <v>6.039740629384593</v>
+        <v>5.79701202820819</v>
       </c>
       <c r="D97">
-        <v>32.90974062938459</v>
+        <v>32.97101202820819</v>
       </c>
       <c r="E97">
-        <v>13.28</v>
+        <v>13.584</v>
       </c>
       <c r="F97">
-        <v>28.88</v>
+        <v>29.184</v>
       </c>
       <c r="G97">
         <v>2.01</v>
@@ -9345,28 +9345,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M97">
-        <v>1.568184</v>
+        <v>1.5846912</v>
       </c>
       <c r="N97">
-        <v>9.608482666666665</v>
+        <v>9.591975466666666</v>
       </c>
       <c r="O97">
-        <v>2.209951013333333</v>
+        <v>2.206154357333333</v>
       </c>
       <c r="P97">
-        <v>7.398531653333333</v>
+        <v>7.385821109333333</v>
       </c>
       <c r="Q97">
-        <v>8.438531653333332</v>
+        <v>8.425821109333333</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.413983200297953</v>
+        <v>1.750995696852472</v>
       </c>
       <c r="T97">
-        <v>21.16535897420954</v>
+        <v>26.37883511309034</v>
       </c>
       <c r="U97">
         <v>0.0543</v>
@@ -9383,7 +9383,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>7.127139842433455</v>
+        <v>7.052898802408106</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9391,22 +9391,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1101783878740988</v>
+        <v>0.1099371657333</v>
       </c>
       <c r="C98">
-        <v>5.797012028208194</v>
+        <v>5.554512002938182</v>
       </c>
       <c r="D98">
-        <v>32.97101202820819</v>
+        <v>33.03251200293818</v>
       </c>
       <c r="E98">
-        <v>13.584</v>
+        <v>13.888</v>
       </c>
       <c r="F98">
-        <v>29.184</v>
+        <v>29.488</v>
       </c>
       <c r="G98">
         <v>2.01</v>
@@ -9427,28 +9427,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M98">
-        <v>1.5846912</v>
+        <v>1.6011984</v>
       </c>
       <c r="N98">
-        <v>9.591975466666666</v>
+        <v>9.575468266666666</v>
       </c>
       <c r="O98">
-        <v>2.206154357333333</v>
+        <v>2.202357701333333</v>
       </c>
       <c r="P98">
-        <v>7.385821109333333</v>
+        <v>7.373110565333333</v>
       </c>
       <c r="Q98">
-        <v>8.425821109333333</v>
+        <v>8.413110565333334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.750995696852467</v>
+        <v>2.312683191109997</v>
       </c>
       <c r="T98">
-        <v>26.37883511309027</v>
+        <v>35.0679620112249</v>
       </c>
       <c r="U98">
         <v>0.0543</v>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>7.052898802408107</v>
+        <v>6.980188505476066</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9473,22 +9473,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1099371657333</v>
+        <v>0.1096959435925011</v>
       </c>
       <c r="C99">
-        <v>5.554512002938182</v>
+        <v>5.312241835034971</v>
       </c>
       <c r="D99">
-        <v>33.03251200293818</v>
+        <v>33.09424183503497</v>
       </c>
       <c r="E99">
-        <v>13.888</v>
+        <v>14.192</v>
       </c>
       <c r="F99">
-        <v>29.488</v>
+        <v>29.792</v>
       </c>
       <c r="G99">
         <v>2.01</v>
@@ -9509,28 +9509,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M99">
-        <v>1.6011984</v>
+        <v>1.6177056</v>
       </c>
       <c r="N99">
-        <v>9.575468266666666</v>
+        <v>9.558961066666665</v>
       </c>
       <c r="O99">
-        <v>2.202357701333333</v>
+        <v>2.198561045333333</v>
       </c>
       <c r="P99">
-        <v>7.373110565333333</v>
+        <v>7.360400021333332</v>
       </c>
       <c r="Q99">
-        <v>8.413110565333334</v>
+        <v>8.400400021333333</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.312683191109997</v>
+        <v>3.436058179625054</v>
       </c>
       <c r="T99">
-        <v>35.0679620112249</v>
+        <v>52.44621580749416</v>
       </c>
       <c r="U99">
         <v>0.0543</v>
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>6.980188505476066</v>
+        <v>6.90896209215488</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9555,22 +9555,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1096959435925011</v>
+        <v>0.1094547214517024</v>
       </c>
       <c r="C100">
-        <v>5.312241835034971</v>
+        <v>5.070202815555906</v>
       </c>
       <c r="D100">
-        <v>33.09424183503497</v>
+        <v>33.15620281555591</v>
       </c>
       <c r="E100">
-        <v>14.192</v>
+        <v>14.496</v>
       </c>
       <c r="F100">
-        <v>29.792</v>
+        <v>30.096</v>
       </c>
       <c r="G100">
         <v>2.01</v>
@@ -9591,28 +9591,28 @@
         <v>11.17666666666667</v>
       </c>
       <c r="M100">
-        <v>1.6177056</v>
+        <v>1.6342128</v>
       </c>
       <c r="N100">
-        <v>9.558961066666665</v>
+        <v>9.542453866666666</v>
       </c>
       <c r="O100">
-        <v>2.198561045333333</v>
+        <v>2.194764389333333</v>
       </c>
       <c r="P100">
-        <v>7.360400021333332</v>
+        <v>7.347689477333333</v>
       </c>
       <c r="Q100">
-        <v>8.400400021333333</v>
+        <v>8.387689477333332</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.436058179625054</v>
+        <v>6.806183145170229</v>
       </c>
       <c r="T100">
-        <v>52.44621580749416</v>
+        <v>104.5809771963019</v>
       </c>
       <c r="U100">
         <v>0.0543</v>
@@ -9629,91 +9629,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>6.90896209215488</v>
+        <v>6.839174596274527</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1094547214517024</v>
-      </c>
-      <c r="C101">
-        <v>5.070202815555906</v>
-      </c>
-      <c r="D101">
-        <v>33.15620281555591</v>
-      </c>
-      <c r="E101">
-        <v>14.496</v>
-      </c>
-      <c r="F101">
-        <v>30.096</v>
-      </c>
-      <c r="G101">
-        <v>2.01</v>
-      </c>
-      <c r="H101">
-        <v>14.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>12.21666666666667</v>
-      </c>
-      <c r="K101">
-        <v>1.04</v>
-      </c>
-      <c r="L101">
-        <v>11.17666666666667</v>
-      </c>
-      <c r="M101">
-        <v>1.6342128</v>
-      </c>
-      <c r="N101">
-        <v>9.542453866666666</v>
-      </c>
-      <c r="O101">
-        <v>2.194764389333333</v>
-      </c>
-      <c r="P101">
-        <v>7.347689477333333</v>
-      </c>
-      <c r="Q101">
-        <v>8.387689477333332</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.806183145170229</v>
-      </c>
-      <c r="T101">
-        <v>104.5809771963019</v>
-      </c>
-      <c r="U101">
-        <v>0.0543</v>
-      </c>
-      <c r="V101">
-        <v>0.23</v>
-      </c>
-      <c r="W101">
-        <v>0.041811</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A2/A</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>6.839174596274527</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
